--- a/プロジェクト型演習_成果物_TasBo_コメント閲覧.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_コメント閲覧.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Desktop\プロジェクト演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\TasBoドキュメント\コメント閲覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7913C074-9410-4384-BFA8-F628622C2847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED1362-C597-46DF-9F1E-E7C2ACD9D8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="11" r:id="rId1"/>
-    <sheet name="ユースケース記述" sheetId="18" r:id="rId2"/>
+    <sheet name="ユースケース記述 " sheetId="22" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図 " sheetId="21" r:id="rId4"/>
     <sheet name="画面設計書 (コメント閲覧コメントあり)" sheetId="17" r:id="rId5"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="111">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -467,10 +467,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユースケース名</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>コメント閲覧</t>
     <rPh sb="4" eb="6">
       <t>エツラン</t>
@@ -520,6 +516,92 @@
   </si>
   <si>
     <t>commentId</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユースケース名</t>
+  </si>
+  <si>
+    <t>コメント閲覧</t>
+    <rPh sb="4" eb="6">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザがタスクに投稿されたコメントを閲覧する。</t>
+    <rPh sb="8" eb="10">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザ　　　</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザがシステムにログインしている/ユーザがタスク一覧を表示している</t>
+    <rPh sb="25" eb="27">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク一覧画面を表示する。
+2.ユーザは対象タスクの「コメント閲覧」欄にある「コメント」リンクをクリックする。
+3.システムは対象タスクに投稿されたコメントを取得する。
+4.システムはコメント一覧画面を表示する。
+5.システムは各コメントについて以下の項目を一覧表示する。
+　・選択（ラジオボタン）
+　・コメント投稿者
+　・コメント
+　・コメント投稿日時
+6.ユーザはコメント内容を閲覧する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1. 対象タスクが削除されている場合（基本フロー3から分岐）
+a. システムは対象タスクが存在しないことを検出する。
+b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
+c. システムはタスク一覧画面を表示する。
+d. ユースケースを終了する。
+A2. 対象タスクにコメントが存在しない場合（基本フロー3から分岐）
+a. システムはコメントが存在しないことを検出する。
+b. システムはコメント一覧画面を表示する。
+c. システムは「コメントが投稿されていません」とメッセージを表示する。
+d. ユーザはコメント未投稿であることを確認する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1. データベース接続エラーまたはコメント取得処理中にシステムエラーが発生した場合
+a. システムエラーが発生する。
+b. システムはエラーメッセージを表示する。
+c. システムは処理を終了する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・コメント一覧画面が表示されていること
+・対象タスクのコメント情報を確認できること
+・各コメントについて以下の情報を確認できること
+　　・コメント投稿者
+　　・コメント
+　　・コメント投稿日時</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・投稿されたコメントはすべてのユーザーが閲覧できる。
+・コメント一覧画面には以下の項目を表示する。
+　　・選択（ラジオボタン）
+　　・コメント投稿者
+　　・コメント
+　　・コメント投稿日時
+・ラジオボタンはコメントを選択するための項目であり、一度に1件のみ選択可能とする。</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1630,7 +1712,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1830,12 +1912,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1977,120 +2053,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2154,21 +2116,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2190,36 +2182,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2229,44 +2191,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2277,9 +2275,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2328,39 +2323,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2390,6 +2352,75 @@
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3470,85 +3501,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="112" t="s">
+      <c r="C2" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
       <c r="P2" s="65"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="109"/>
       <c r="P3" s="65"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="109"/>
+      <c r="O4" s="109"/>
       <c r="P4" s="65"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
       <c r="P5" s="65"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="111"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
       <c r="P6" s="65"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3568,46 +3599,46 @@
       <c r="P7" s="65"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="114" t="s">
+      <c r="E8" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
+      <c r="F8" s="109"/>
+      <c r="G8" s="109"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="107" t="s">
+      <c r="G13" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="109"/>
-      <c r="I13" s="115">
-        <v>46191</v>
-      </c>
-      <c r="J13" s="108"/>
-      <c r="K13" s="109"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="113">
+        <v>46198</v>
+      </c>
+      <c r="J13" s="106"/>
+      <c r="K13" s="107"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="107"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="109"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="106"/>
+      <c r="K14" s="107"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="107"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="107"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="109"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="107"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="64"/>
@@ -3616,13 +3647,13 @@
       <c r="J16" s="64"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="110" t="s">
+      <c r="G17" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="109"/>
+      <c r="K17" s="109"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4626,211 +4657,229 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C4D44D-FFA7-4AA2-948D-F8FC774EF950}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C741FE-71C4-424E-91A5-1FE2D3C29909}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="63" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="63" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="63" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="63"/>
+    <col min="1" max="3" width="5.140625" style="75" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="75" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="75" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="75"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="214" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="138" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="124"/>
-      <c r="F1" s="138" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="124"/>
-      <c r="H1" s="68" t="s">
+      <c r="G1" s="99"/>
+      <c r="H1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="68" t="s">
+      <c r="I1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="215" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="133"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="139" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="140"/>
-      <c r="F2" s="139" t="s">
+      <c r="E2" s="101"/>
+      <c r="F2" s="100" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="143">
-        <v>46191</v>
-      </c>
-      <c r="I2" s="116" t="s">
+      <c r="G2" s="101"/>
+      <c r="H2" s="216">
+        <v>46195</v>
+      </c>
+      <c r="I2" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="J2" s="119"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="133"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="120"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="87"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="135"/>
-      <c r="B4" s="136"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="121"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="88"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="122" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="123"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="126"/>
+      <c r="A5" s="217" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="218"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="219" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="218"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="220"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="221" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="129"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="224" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="222"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
+      <c r="J6" s="225"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="221" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="129"/>
-    </row>
-    <row r="8" spans="1:10" ht="58.5" customHeight="1">
-      <c r="A8" s="127" t="s">
+      <c r="B7" s="222"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="224" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="225"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="221" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="109"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="129"/>
-    </row>
-    <row r="9" spans="1:10" ht="141.75" customHeight="1">
-      <c r="A9" s="150" t="s">
+      <c r="B8" s="222"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="226" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="225"/>
+    </row>
+    <row r="9" spans="1:10" ht="148.5" customHeight="1">
+      <c r="A9" s="227" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="228" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="109"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="129"/>
-    </row>
-    <row r="10" spans="1:10" ht="295.5" customHeight="1">
-      <c r="A10" s="151"/>
-      <c r="B10" s="153" t="s">
+      <c r="C9" s="223"/>
+      <c r="D9" s="226" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="225"/>
+    </row>
+    <row r="10" spans="1:10" ht="156.75" customHeight="1">
+      <c r="A10" s="229"/>
+      <c r="B10" s="228" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="109"/>
-      <c r="D10" s="144"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="129"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="152"/>
-      <c r="B11" s="153" t="s">
+      <c r="C10" s="223"/>
+      <c r="D10" s="226" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="222"/>
+      <c r="H10" s="222"/>
+      <c r="I10" s="222"/>
+      <c r="J10" s="225"/>
+    </row>
+    <row r="11" spans="1:10" ht="61.5" customHeight="1">
+      <c r="A11" s="230"/>
+      <c r="B11" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="129"/>
-    </row>
-    <row r="12" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A12" s="127" t="s">
+      <c r="C11" s="223"/>
+      <c r="D11" s="226" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="222"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="222"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="225"/>
+    </row>
+    <row r="12" spans="1:10" ht="92.25" customHeight="1">
+      <c r="A12" s="221" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="108"/>
-      <c r="C12" s="109"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="129"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="145" t="s">
+      <c r="B12" s="222"/>
+      <c r="C12" s="223"/>
+      <c r="D12" s="226" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="222"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="225"/>
+    </row>
+    <row r="13" spans="1:10" ht="113.25" customHeight="1" thickBot="1">
+      <c r="A13" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="146"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="148"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="146"/>
-      <c r="G13" s="146"/>
-      <c r="H13" s="146"/>
-      <c r="I13" s="146"/>
-      <c r="J13" s="149"/>
+      <c r="B13" s="232"/>
+      <c r="C13" s="233"/>
+      <c r="D13" s="234" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="236"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5821,6 +5870,7 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5835,7 +5885,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -5851,7 +5900,7 @@
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5866,19 +5915,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="169" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="169" t="s">
+      <c r="E1" s="130"/>
+      <c r="F1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="130"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -5890,40 +5939,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="157"/>
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="117"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="163"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="158"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="118"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="166"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="168"/>
-      <c r="D4" s="174"/>
-      <c r="E4" s="168"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
-      <c r="J4" s="159"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="119"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -7273,523 +7322,523 @@
   <dimension ref="A1:J1008"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="5.140625" style="77" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" style="77" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" style="77" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="77"/>
+    <col min="1" max="3" width="5.140625" style="75" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" style="75" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" style="75" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="75"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="101"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="101"/>
-      <c r="H1" s="74" t="s">
+      <c r="G1" s="99"/>
+      <c r="H1" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="76" t="s">
+      <c r="J1" s="74" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="101"/>
+      <c r="F2" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="106">
+      <c r="G2" s="101"/>
+      <c r="H2" s="104">
         <v>46196</v>
       </c>
-      <c r="I2" s="85" t="s">
+      <c r="I2" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="88"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="89"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="87"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="90"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="88"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="78"/>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="80"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="78"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="80"/>
+      <c r="A6" s="76"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="78"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="80"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="78"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="78"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="80"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="78"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="80"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="80"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="78"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="80"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="78"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="80"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="78"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="80"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="80"/>
+      <c r="A14" s="76"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="78"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="78"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="80"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="78"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="78"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="80"/>
+      <c r="A16" s="76"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="78"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="78"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="80"/>
+      <c r="A17" s="76"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="78"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="80"/>
+      <c r="A18" s="76"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="78"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="80"/>
+      <c r="A19" s="76"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="78"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="80"/>
+      <c r="A20" s="76"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="78"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="80"/>
+      <c r="A21" s="76"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="78"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="80"/>
+      <c r="A22" s="76"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="78"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="78"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="80"/>
+      <c r="A23" s="76"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="78"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="78"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="80"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="78"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="78"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="80"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="78"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="78"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="80"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="78"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="78"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="80"/>
+      <c r="A27" s="76"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="78"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="78"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="80"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="78"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="78"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="80"/>
+      <c r="A29" s="76"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="78"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="78"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="80"/>
+      <c r="A30" s="76"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="78"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="78"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="80"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="78"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="78"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="80"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="78"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="78"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="80"/>
+      <c r="A33" s="76"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="78"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="78"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="80"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="78"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="78"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="79"/>
-      <c r="J35" s="80"/>
+      <c r="A35" s="76"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="78"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="78"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
-      <c r="J36" s="80"/>
+      <c r="A36" s="76"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="78"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="78"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
-      <c r="I37" s="79"/>
-      <c r="J37" s="80"/>
+      <c r="A37" s="76"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="78"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="78"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="80"/>
+      <c r="A38" s="76"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="78"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="78"/>
-      <c r="B39" s="79"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="80"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="78"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="78"/>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="80"/>
+      <c r="A40" s="76"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="78"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A41" s="81"/>
-      <c r="B41" s="82"/>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
-      <c r="H41" s="82"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="83"/>
+      <c r="A41" s="79"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80"/>
+      <c r="J41" s="81"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7802,7 +7851,7 @@
     <row r="50" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="51" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="52" spans="10:10" ht="12.75" customHeight="1">
-      <c r="J52" s="84"/>
+      <c r="J52" s="82"/>
     </row>
     <row r="53" spans="10:10" ht="12.75" customHeight="1"/>
     <row r="54" spans="10:10" ht="12.75" customHeight="1"/>
@@ -8792,19 +8841,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="169" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="169" t="s">
+      <c r="E1" s="130"/>
+      <c r="F1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="130"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -8816,203 +8865,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="171" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="172"/>
-      <c r="F2" s="171" t="s">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="192">
+      <c r="G2" s="132"/>
+      <c r="H2" s="143">
         <v>46198</v>
       </c>
-      <c r="I2" s="154" t="s">
+      <c r="I2" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="157"/>
+      <c r="J2" s="117"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="163"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="158"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="118"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="163"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="158"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="118"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="194"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="195" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="196"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="146" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="177"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="137"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="188"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="190"/>
+      <c r="A7" s="139"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="141"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="163"/>
-      <c r="B8" s="164"/>
-      <c r="C8" s="164"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="191"/>
+      <c r="A8" s="123"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="142"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="163"/>
-      <c r="B9" s="164"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="191"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="142"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="163"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="191"/>
+      <c r="A10" s="123"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="142"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="163"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="191"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="142"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="163"/>
-      <c r="B12" s="164"/>
-      <c r="C12" s="164"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="191"/>
+      <c r="A12" s="123"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="142"/>
     </row>
     <row r="13" spans="1:10" ht="54" customHeight="1">
-      <c r="A13" s="163"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="164"/>
-      <c r="I13" s="164"/>
-      <c r="J13" s="191"/>
+      <c r="A13" s="123"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="142"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="176"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="177"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="137"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="176"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="178" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="179"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="148" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="138"/>
       <c r="I15" s="11" t="s">
         <v>24</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="176"/>
-      <c r="C16" s="179"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="138"/>
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
@@ -9025,94 +9074,94 @@
       <c r="G16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="175" t="s">
+      <c r="H16" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="176"/>
-      <c r="J16" s="177"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="137"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="180">
+      <c r="A17" s="150">
         <v>1</v>
       </c>
-      <c r="B17" s="176"/>
-      <c r="C17" s="179"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="138"/>
       <c r="D17" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>101</v>
-      </c>
       <c r="G17" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="178"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="177"/>
+        <v>100</v>
+      </c>
+      <c r="H17" s="148"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="137"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="180">
+      <c r="A18" s="150">
         <v>2</v>
       </c>
-      <c r="B18" s="176"/>
-      <c r="C18" s="179"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="138"/>
       <c r="D18" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H18" s="178"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="177"/>
+        <v>94</v>
+      </c>
+      <c r="H18" s="148"/>
+      <c r="I18" s="136"/>
+      <c r="J18" s="137"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="187" t="s">
+      <c r="A19" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="176"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="177"/>
+      <c r="B19" s="136"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="137"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="187" t="s">
+      <c r="A20" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="176"/>
-      <c r="C20" s="179"/>
-      <c r="D20" s="178" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="179"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="148" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="138"/>
       <c r="I20" s="11" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="187" t="s">
+      <c r="A21" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="176"/>
-      <c r="C21" s="179"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="11" t="s">
         <v>26</v>
       </c>
@@ -9125,71 +9174,71 @@
       <c r="G21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="175" t="s">
+      <c r="H21" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="176"/>
-      <c r="J21" s="177"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="137"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="180">
+      <c r="A22" s="150">
         <v>3</v>
       </c>
-      <c r="B22" s="176"/>
-      <c r="C22" s="179"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="138"/>
       <c r="D22" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="178"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="177"/>
+        <v>95</v>
+      </c>
+      <c r="H22" s="148"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="137"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="69"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="71"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="69"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="14"/>
       <c r="G23" s="13"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="73"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="71"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="187" t="s">
+      <c r="A24" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="176"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="176"/>
-      <c r="E24" s="176"/>
-      <c r="F24" s="176"/>
-      <c r="G24" s="176"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="177"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="136"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="137"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="187" t="s">
+      <c r="A25" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="176"/>
-      <c r="C25" s="179"/>
-      <c r="D25" s="178" t="s">
+      <c r="B25" s="136"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="148" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="176"/>
-      <c r="F25" s="176"/>
-      <c r="G25" s="176"/>
-      <c r="H25" s="179"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="138"/>
       <c r="I25" s="11" t="s">
         <v>24</v>
       </c>
@@ -9198,11 +9247,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="187" t="s">
+      <c r="A26" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="176"/>
-      <c r="C26" s="179"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="11" t="s">
         <v>26</v>
       </c>
@@ -9215,43 +9264,43 @@
       <c r="G26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="175" t="s">
+      <c r="H26" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="176"/>
-      <c r="J26" s="177"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="137"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="180">
+      <c r="A27" s="150">
         <v>4</v>
       </c>
-      <c r="B27" s="176"/>
-      <c r="C27" s="179"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="138"/>
       <c r="D27" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H27" s="178"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="177"/>
+        <v>97</v>
+      </c>
+      <c r="H27" s="148"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="137"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A28" s="181"/>
-      <c r="B28" s="182"/>
-      <c r="C28" s="183"/>
+      <c r="A28" s="151"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="153"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="186"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="155"/>
+      <c r="J28" s="156"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10232,6 +10281,28 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -10247,28 +10318,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10291,19 +10340,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="169" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="170"/>
-      <c r="F1" s="169" t="s">
+      <c r="E1" s="130"/>
+      <c r="F1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="170"/>
+      <c r="G1" s="130"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -10315,203 +10364,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="171" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="172"/>
-      <c r="F2" s="171" t="s">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="172"/>
-      <c r="H2" s="192">
+      <c r="G2" s="132"/>
+      <c r="H2" s="143">
         <v>46189</v>
       </c>
-      <c r="I2" s="154" t="s">
+      <c r="I2" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="157"/>
+      <c r="J2" s="117"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="163"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="158"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="118"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="163"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="165"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="155"/>
-      <c r="J4" s="158"/>
+      <c r="A4" s="123"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="118"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="194"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="195" t="s">
+      <c r="B5" s="145"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="146" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="196"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="147"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="177"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="137"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="188"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="190"/>
+      <c r="A7" s="139"/>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="141"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="163"/>
-      <c r="B8" s="164"/>
-      <c r="C8" s="164"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="191"/>
+      <c r="A8" s="123"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="142"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="163"/>
-      <c r="B9" s="164"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="191"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="142"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="163"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="191"/>
+      <c r="A10" s="123"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="142"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="163"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="191"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="142"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="163"/>
-      <c r="B12" s="164"/>
-      <c r="C12" s="164"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="191"/>
+      <c r="A12" s="123"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="142"/>
     </row>
     <row r="13" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A13" s="163"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="164"/>
-      <c r="I13" s="164"/>
-      <c r="J13" s="191"/>
+      <c r="A13" s="123"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="142"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="176"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="176"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="177"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="137"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="176"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="178" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="179"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="148" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="138"/>
       <c r="I15" s="11" t="s">
         <v>24</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="176"/>
-      <c r="C16" s="179"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="138"/>
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
@@ -10524,71 +10573,71 @@
       <c r="G16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="175" t="s">
+      <c r="H16" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="176"/>
-      <c r="J16" s="177"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="137"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="180">
+      <c r="A17" s="150">
         <v>1</v>
       </c>
-      <c r="B17" s="176"/>
-      <c r="C17" s="179"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="138"/>
       <c r="D17" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" s="178"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="177"/>
+        <v>95</v>
+      </c>
+      <c r="H17" s="148"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="137"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="180"/>
-      <c r="B18" s="176"/>
-      <c r="C18" s="179"/>
+      <c r="A18" s="150"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="138"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="178"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="177"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="136"/>
+      <c r="J18" s="137"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="187" t="s">
+      <c r="A19" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="176"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="176"/>
-      <c r="F19" s="176"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="177"/>
+      <c r="B19" s="136"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="137"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="187" t="s">
+      <c r="A20" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="176"/>
-      <c r="C20" s="179"/>
-      <c r="D20" s="178" t="s">
+      <c r="B20" s="136"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="148" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="179"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="138"/>
       <c r="I20" s="11" t="s">
         <v>24</v>
       </c>
@@ -10597,11 +10646,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="187" t="s">
+      <c r="A21" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="176"/>
-      <c r="C21" s="179"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="11" t="s">
         <v>26</v>
       </c>
@@ -10614,31 +10663,31 @@
       <c r="G21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="175" t="s">
+      <c r="H21" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="176"/>
-      <c r="J21" s="177"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="137"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="181">
+      <c r="A22" s="151">
         <v>2</v>
       </c>
-      <c r="B22" s="197"/>
-      <c r="C22" s="198"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="158"/>
       <c r="D22" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>88</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="H22" s="184"/>
-      <c r="I22" s="197"/>
-      <c r="J22" s="199"/>
+        <v>97</v>
+      </c>
+      <c r="H22" s="154"/>
+      <c r="I22" s="157"/>
+      <c r="J22" s="159"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11619,19 +11668,6 @@
     <row r="999" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11647,6 +11683,19 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D20:H20"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11666,182 +11715,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="171" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="169" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="169" t="s">
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="169" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="169" t="s">
+      <c r="P1" s="130"/>
+      <c r="Q1" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="170"/>
-      <c r="S1" s="169" t="s">
+      <c r="R1" s="130"/>
+      <c r="S1" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="196"/>
+      <c r="T1" s="147"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="171" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="131" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="171" t="s">
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="189"/>
-      <c r="M2" s="189"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="171" t="s">
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="172"/>
-      <c r="S2" s="171"/>
-      <c r="T2" s="190"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="141"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="163"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="165"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="165"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="165"/>
-      <c r="Q3" s="173"/>
-      <c r="R3" s="165"/>
-      <c r="S3" s="173"/>
-      <c r="T3" s="191"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="133"/>
+      <c r="T3" s="142"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="166"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-      <c r="J4" s="168"/>
-      <c r="K4" s="174"/>
-      <c r="L4" s="167"/>
-      <c r="M4" s="167"/>
-      <c r="N4" s="168"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="168"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="168"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="205"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="127"/>
+      <c r="M4" s="127"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="134"/>
+      <c r="P4" s="128"/>
+      <c r="Q4" s="134"/>
+      <c r="R4" s="128"/>
+      <c r="S4" s="134"/>
+      <c r="T4" s="170"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="194"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="207"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="194"/>
-      <c r="K5" s="194"/>
-      <c r="L5" s="194"/>
-      <c r="M5" s="194"/>
-      <c r="N5" s="194"/>
-      <c r="O5" s="194"/>
-      <c r="P5" s="194"/>
-      <c r="Q5" s="194"/>
-      <c r="R5" s="194"/>
-      <c r="S5" s="194"/>
-      <c r="T5" s="196"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="145"/>
+      <c r="T5" s="147"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="176"/>
-      <c r="L6" s="176"/>
-      <c r="M6" s="176"/>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
-      <c r="P6" s="176"/>
-      <c r="Q6" s="176"/>
-      <c r="R6" s="176"/>
-      <c r="S6" s="176"/>
-      <c r="T6" s="177"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="137"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="176"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="176"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="178"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
-      <c r="P7" s="176"/>
-      <c r="Q7" s="176"/>
-      <c r="R7" s="176"/>
-      <c r="S7" s="176"/>
-      <c r="T7" s="177"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="136"/>
+      <c r="P7" s="136"/>
+      <c r="Q7" s="136"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="137"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -12040,37 +12089,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="179"/>
-      <c r="C15" s="210" t="s">
+      <c r="B15" s="138"/>
+      <c r="C15" s="168" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="179"/>
-      <c r="E15" s="175" t="s">
+      <c r="D15" s="138"/>
+      <c r="E15" s="149" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="179"/>
-      <c r="G15" s="175" t="s">
+      <c r="F15" s="138"/>
+      <c r="G15" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="176"/>
-      <c r="I15" s="179"/>
-      <c r="J15" s="175" t="s">
+      <c r="H15" s="136"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="179"/>
-      <c r="L15" s="175" t="s">
+      <c r="K15" s="138"/>
+      <c r="L15" s="149" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="176"/>
-      <c r="N15" s="179"/>
-      <c r="O15" s="175" t="s">
+      <c r="M15" s="136"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="176"/>
-      <c r="Q15" s="179"/>
+      <c r="P15" s="136"/>
+      <c r="Q15" s="138"/>
       <c r="R15" s="11" t="s">
         <v>46</v>
       </c>
@@ -12082,25 +12131,25 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="208">
+      <c r="A16" s="160">
         <v>1</v>
       </c>
-      <c r="B16" s="179"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="179"/>
-      <c r="E16" s="209"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="176"/>
-      <c r="I16" s="179"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="179"/>
-      <c r="L16" s="202"/>
-      <c r="M16" s="176"/>
-      <c r="N16" s="179"/>
-      <c r="O16" s="202"/>
-      <c r="P16" s="176"/>
-      <c r="Q16" s="179"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="167"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="167"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="164"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="164"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="138"/>
       <c r="R16" s="29"/>
       <c r="S16" s="29"/>
       <c r="T16" s="30"/>
@@ -12112,25 +12161,25 @@
       <c r="Z16" s="31"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="208">
+      <c r="A17" s="160">
         <v>2</v>
       </c>
-      <c r="B17" s="179"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="179"/>
-      <c r="E17" s="209"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="176"/>
-      <c r="I17" s="179"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="179"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="176"/>
-      <c r="N17" s="179"/>
-      <c r="O17" s="202"/>
-      <c r="P17" s="176"/>
-      <c r="Q17" s="179"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="161"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="167"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="167"/>
+      <c r="K17" s="138"/>
+      <c r="L17" s="164"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="138"/>
+      <c r="O17" s="164"/>
+      <c r="P17" s="136"/>
+      <c r="Q17" s="138"/>
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
       <c r="T17" s="30"/>
@@ -12142,23 +12191,23 @@
       <c r="Z17" s="31"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="208"/>
-      <c r="B18" s="179"/>
-      <c r="C18" s="209"/>
-      <c r="D18" s="179"/>
-      <c r="E18" s="209"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="179"/>
-      <c r="J18" s="200"/>
-      <c r="K18" s="179"/>
-      <c r="L18" s="202"/>
-      <c r="M18" s="176"/>
-      <c r="N18" s="179"/>
-      <c r="O18" s="202"/>
-      <c r="P18" s="176"/>
-      <c r="Q18" s="179"/>
+      <c r="A18" s="160"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="161"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="136"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="138"/>
+      <c r="L18" s="164"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="164"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="138"/>
       <c r="R18" s="29"/>
       <c r="S18" s="29"/>
       <c r="T18" s="30"/>
@@ -12170,23 +12219,23 @@
       <c r="Z18" s="31"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="208"/>
-      <c r="B19" s="179"/>
-      <c r="C19" s="209"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="209"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="176"/>
-      <c r="I19" s="179"/>
-      <c r="J19" s="200"/>
-      <c r="K19" s="179"/>
-      <c r="L19" s="202"/>
-      <c r="M19" s="176"/>
-      <c r="N19" s="179"/>
-      <c r="O19" s="202"/>
-      <c r="P19" s="176"/>
-      <c r="Q19" s="179"/>
+      <c r="A19" s="160"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="161"/>
+      <c r="D19" s="138"/>
+      <c r="E19" s="161"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="167"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="138"/>
+      <c r="L19" s="164"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="164"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="138"/>
       <c r="R19" s="29"/>
       <c r="S19" s="29"/>
       <c r="T19" s="30"/>
@@ -12198,23 +12247,23 @@
       <c r="Z19" s="31"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="208"/>
-      <c r="B20" s="179"/>
-      <c r="C20" s="209"/>
-      <c r="D20" s="179"/>
-      <c r="E20" s="209"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="176"/>
-      <c r="I20" s="179"/>
-      <c r="J20" s="200"/>
-      <c r="K20" s="179"/>
-      <c r="L20" s="202"/>
-      <c r="M20" s="176"/>
-      <c r="N20" s="179"/>
-      <c r="O20" s="202"/>
-      <c r="P20" s="176"/>
-      <c r="Q20" s="179"/>
+      <c r="A20" s="160"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="164"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="138"/>
+      <c r="O20" s="164"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="138"/>
       <c r="R20" s="29"/>
       <c r="S20" s="29"/>
       <c r="T20" s="30"/>
@@ -12226,23 +12275,23 @@
       <c r="Z20" s="31"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="208"/>
-      <c r="B21" s="179"/>
-      <c r="C21" s="209"/>
-      <c r="D21" s="179"/>
-      <c r="E21" s="209"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="176"/>
-      <c r="I21" s="179"/>
-      <c r="J21" s="200"/>
-      <c r="K21" s="179"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="176"/>
-      <c r="N21" s="179"/>
-      <c r="O21" s="202"/>
-      <c r="P21" s="176"/>
-      <c r="Q21" s="179"/>
+      <c r="A21" s="160"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="161"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="167"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="167"/>
+      <c r="K21" s="138"/>
+      <c r="L21" s="164"/>
+      <c r="M21" s="136"/>
+      <c r="N21" s="138"/>
+      <c r="O21" s="164"/>
+      <c r="P21" s="136"/>
+      <c r="Q21" s="138"/>
       <c r="R21" s="29"/>
       <c r="S21" s="29"/>
       <c r="T21" s="30"/>
@@ -12254,23 +12303,23 @@
       <c r="Z21" s="31"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="208"/>
-      <c r="B22" s="179"/>
-      <c r="C22" s="209"/>
-      <c r="D22" s="179"/>
-      <c r="E22" s="209"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="179"/>
-      <c r="J22" s="200"/>
-      <c r="K22" s="179"/>
-      <c r="L22" s="202"/>
-      <c r="M22" s="176"/>
-      <c r="N22" s="179"/>
-      <c r="O22" s="202"/>
-      <c r="P22" s="176"/>
-      <c r="Q22" s="179"/>
+      <c r="A22" s="160"/>
+      <c r="B22" s="138"/>
+      <c r="C22" s="161"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="167"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="167"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="164"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="138"/>
+      <c r="O22" s="164"/>
+      <c r="P22" s="136"/>
+      <c r="Q22" s="138"/>
       <c r="R22" s="29"/>
       <c r="S22" s="29"/>
       <c r="T22" s="30"/>
@@ -12282,23 +12331,23 @@
       <c r="Z22" s="31"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="208"/>
-      <c r="B23" s="179"/>
-      <c r="C23" s="209"/>
-      <c r="D23" s="179"/>
-      <c r="E23" s="209"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="176"/>
-      <c r="I23" s="179"/>
-      <c r="J23" s="200"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="202"/>
-      <c r="M23" s="176"/>
-      <c r="N23" s="179"/>
-      <c r="O23" s="202"/>
-      <c r="P23" s="176"/>
-      <c r="Q23" s="179"/>
+      <c r="A23" s="160"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="161"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="138"/>
+      <c r="G23" s="167"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="167"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="164"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="164"/>
+      <c r="P23" s="136"/>
+      <c r="Q23" s="138"/>
       <c r="R23" s="29"/>
       <c r="S23" s="29"/>
       <c r="T23" s="30"/>
@@ -12310,23 +12359,23 @@
       <c r="Z23" s="31"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="208"/>
-      <c r="B24" s="179"/>
-      <c r="C24" s="209"/>
-      <c r="D24" s="179"/>
-      <c r="E24" s="209"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="176"/>
-      <c r="I24" s="179"/>
-      <c r="J24" s="200"/>
-      <c r="K24" s="179"/>
-      <c r="L24" s="202"/>
-      <c r="M24" s="176"/>
-      <c r="N24" s="179"/>
-      <c r="O24" s="202"/>
-      <c r="P24" s="176"/>
-      <c r="Q24" s="179"/>
+      <c r="A24" s="160"/>
+      <c r="B24" s="138"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="167"/>
+      <c r="K24" s="138"/>
+      <c r="L24" s="164"/>
+      <c r="M24" s="136"/>
+      <c r="N24" s="138"/>
+      <c r="O24" s="164"/>
+      <c r="P24" s="136"/>
+      <c r="Q24" s="138"/>
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
       <c r="T24" s="30"/>
@@ -12338,23 +12387,23 @@
       <c r="Z24" s="31"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="208"/>
-      <c r="B25" s="179"/>
-      <c r="C25" s="209"/>
-      <c r="D25" s="179"/>
-      <c r="E25" s="209"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="176"/>
-      <c r="I25" s="179"/>
-      <c r="J25" s="200"/>
-      <c r="K25" s="179"/>
-      <c r="L25" s="202"/>
-      <c r="M25" s="176"/>
-      <c r="N25" s="179"/>
-      <c r="O25" s="202"/>
-      <c r="P25" s="176"/>
-      <c r="Q25" s="179"/>
+      <c r="A25" s="160"/>
+      <c r="B25" s="138"/>
+      <c r="C25" s="161"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="167"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="167"/>
+      <c r="K25" s="138"/>
+      <c r="L25" s="164"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="138"/>
+      <c r="O25" s="164"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="138"/>
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
       <c r="T25" s="30"/>
@@ -12366,23 +12415,23 @@
       <c r="Z25" s="31"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="208"/>
-      <c r="B26" s="179"/>
-      <c r="C26" s="209"/>
-      <c r="D26" s="179"/>
-      <c r="E26" s="209"/>
-      <c r="F26" s="179"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="176"/>
-      <c r="I26" s="179"/>
-      <c r="J26" s="200"/>
-      <c r="K26" s="179"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="176"/>
-      <c r="N26" s="179"/>
-      <c r="O26" s="202"/>
-      <c r="P26" s="176"/>
-      <c r="Q26" s="179"/>
+      <c r="A26" s="160"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="161"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="167"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="167"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="164"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="138"/>
+      <c r="O26" s="164"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="138"/>
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
       <c r="T26" s="30"/>
@@ -12394,23 +12443,23 @@
       <c r="Z26" s="31"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="208"/>
-      <c r="B27" s="179"/>
-      <c r="C27" s="209"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="209"/>
-      <c r="F27" s="179"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="176"/>
-      <c r="I27" s="179"/>
-      <c r="J27" s="200"/>
-      <c r="K27" s="179"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="176"/>
-      <c r="N27" s="179"/>
-      <c r="O27" s="202"/>
-      <c r="P27" s="176"/>
-      <c r="Q27" s="179"/>
+      <c r="A27" s="160"/>
+      <c r="B27" s="138"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="167"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="167"/>
+      <c r="K27" s="138"/>
+      <c r="L27" s="164"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="138"/>
+      <c r="O27" s="164"/>
+      <c r="P27" s="136"/>
+      <c r="Q27" s="138"/>
       <c r="R27" s="29"/>
       <c r="S27" s="29"/>
       <c r="T27" s="30"/>
@@ -12422,23 +12471,23 @@
       <c r="Z27" s="31"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="208"/>
-      <c r="B28" s="179"/>
-      <c r="C28" s="209"/>
-      <c r="D28" s="179"/>
-      <c r="E28" s="209"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="176"/>
-      <c r="I28" s="179"/>
-      <c r="J28" s="200"/>
-      <c r="K28" s="179"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="176"/>
-      <c r="N28" s="179"/>
-      <c r="O28" s="202"/>
-      <c r="P28" s="176"/>
-      <c r="Q28" s="179"/>
+      <c r="A28" s="160"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="161"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="167"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="167"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="164"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="138"/>
+      <c r="O28" s="164"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="138"/>
       <c r="R28" s="29"/>
       <c r="S28" s="29"/>
       <c r="T28" s="30"/>
@@ -12450,23 +12499,23 @@
       <c r="Z28" s="31"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="208"/>
-      <c r="B29" s="179"/>
-      <c r="C29" s="209"/>
-      <c r="D29" s="179"/>
-      <c r="E29" s="209"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="176"/>
-      <c r="I29" s="179"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="179"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="176"/>
-      <c r="N29" s="179"/>
-      <c r="O29" s="202"/>
-      <c r="P29" s="176"/>
-      <c r="Q29" s="179"/>
+      <c r="A29" s="160"/>
+      <c r="B29" s="138"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="167"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="167"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="164"/>
+      <c r="M29" s="136"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="164"/>
+      <c r="P29" s="136"/>
+      <c r="Q29" s="138"/>
       <c r="R29" s="29"/>
       <c r="S29" s="29"/>
       <c r="T29" s="30"/>
@@ -12478,23 +12527,23 @@
       <c r="Z29" s="31"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="208"/>
-      <c r="B30" s="179"/>
-      <c r="C30" s="209"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="209"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="179"/>
-      <c r="J30" s="200"/>
-      <c r="K30" s="179"/>
-      <c r="L30" s="202"/>
-      <c r="M30" s="176"/>
-      <c r="N30" s="179"/>
-      <c r="O30" s="202"/>
-      <c r="P30" s="176"/>
-      <c r="Q30" s="179"/>
+      <c r="A30" s="160"/>
+      <c r="B30" s="138"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="167"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="164"/>
+      <c r="M30" s="136"/>
+      <c r="N30" s="138"/>
+      <c r="O30" s="164"/>
+      <c r="P30" s="136"/>
+      <c r="Q30" s="138"/>
       <c r="R30" s="29"/>
       <c r="S30" s="29"/>
       <c r="T30" s="30"/>
@@ -12506,23 +12555,23 @@
       <c r="Z30" s="31"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="211"/>
-      <c r="B31" s="198"/>
-      <c r="C31" s="212"/>
-      <c r="D31" s="198"/>
-      <c r="E31" s="212"/>
-      <c r="F31" s="198"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="197"/>
-      <c r="I31" s="198"/>
-      <c r="J31" s="201"/>
-      <c r="K31" s="198"/>
-      <c r="L31" s="203"/>
-      <c r="M31" s="197"/>
-      <c r="N31" s="198"/>
-      <c r="O31" s="203"/>
-      <c r="P31" s="197"/>
-      <c r="Q31" s="198"/>
+      <c r="A31" s="162"/>
+      <c r="B31" s="158"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="163"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="172"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="172"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="165"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="158"/>
+      <c r="O31" s="165"/>
+      <c r="P31" s="157"/>
+      <c r="Q31" s="158"/>
       <c r="R31" s="32"/>
       <c r="S31" s="32"/>
       <c r="T31" s="33"/>
@@ -13520,6 +13569,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13544,118 +13705,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13678,70 +13727,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="193" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="223" t="s">
+      <c r="B1" s="193"/>
+      <c r="C1" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="224"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="226" t="s">
+      <c r="D1" s="195"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="197" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="228"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="199"/>
       <c r="N1" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="226" t="s">
+      <c r="O1" s="197" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="228"/>
+      <c r="P1" s="199"/>
       <c r="Q1" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="R1" s="226" t="s">
+      <c r="R1" s="197" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="228"/>
+      <c r="S1" s="199"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="222"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="223" t="s">
+      <c r="A2" s="193"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="194" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="224"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="227"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="227"/>
-      <c r="J2" s="227"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="227"/>
-      <c r="M2" s="228"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
+      <c r="M2" s="199"/>
       <c r="N2" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="O2" s="229">
+      <c r="O2" s="200">
         <v>46190</v>
       </c>
-      <c r="P2" s="230"/>
+      <c r="P2" s="201"/>
       <c r="Q2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="R2" s="231" t="s">
+      <c r="R2" s="202" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="232"/>
+      <c r="S2" s="203"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="36"/>
@@ -13771,1234 +13820,1046 @@
       <c r="B4" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="185" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="214"/>
-      <c r="E4" s="214"/>
-      <c r="F4" s="214"/>
-      <c r="G4" s="215"/>
-      <c r="H4" s="213" t="s">
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="185" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
-      <c r="K4" s="214"/>
-      <c r="L4" s="214"/>
-      <c r="M4" s="215"/>
-      <c r="N4" s="213" t="s">
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
+      <c r="M4" s="187"/>
+      <c r="N4" s="185" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="214"/>
-      <c r="P4" s="215"/>
+      <c r="O4" s="186"/>
+      <c r="P4" s="187"/>
       <c r="Q4" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="213" t="s">
+      <c r="R4" s="185" t="s">
         <v>72</v>
       </c>
-      <c r="S4" s="215"/>
+      <c r="S4" s="187"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="40">
         <v>1</v>
       </c>
       <c r="B5" s="40"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="216"/>
-      <c r="N5" s="217"/>
-      <c r="O5" s="218"/>
-      <c r="P5" s="219"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="181"/>
+      <c r="L5" s="181"/>
+      <c r="M5" s="181"/>
+      <c r="N5" s="188"/>
+      <c r="O5" s="189"/>
+      <c r="P5" s="190"/>
       <c r="Q5" s="41"/>
-      <c r="R5" s="220"/>
-      <c r="S5" s="221"/>
+      <c r="R5" s="191"/>
+      <c r="S5" s="192"/>
     </row>
     <row r="6" spans="1:19" ht="33" customHeight="1">
       <c r="A6" s="42"/>
       <c r="B6" s="42"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="216"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="216"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="239"/>
-      <c r="P6" s="240"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
+      <c r="G6" s="181"/>
+      <c r="H6" s="181"/>
+      <c r="I6" s="181"/>
+      <c r="J6" s="181"/>
+      <c r="K6" s="181"/>
+      <c r="L6" s="181"/>
+      <c r="M6" s="181"/>
+      <c r="N6" s="182"/>
+      <c r="O6" s="183"/>
+      <c r="P6" s="184"/>
       <c r="Q6" s="41"/>
-      <c r="R6" s="237"/>
-      <c r="S6" s="237"/>
+      <c r="R6" s="180"/>
+      <c r="S6" s="180"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="42"/>
       <c r="B7" s="42"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="233"/>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="238"/>
-      <c r="O7" s="235"/>
-      <c r="P7" s="236"/>
+      <c r="C7" s="181"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="181"/>
+      <c r="F7" s="181"/>
+      <c r="G7" s="181"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
+      <c r="L7" s="173"/>
+      <c r="M7" s="173"/>
+      <c r="N7" s="182"/>
+      <c r="O7" s="178"/>
+      <c r="P7" s="179"/>
       <c r="Q7" s="41"/>
-      <c r="R7" s="237"/>
-      <c r="S7" s="237"/>
+      <c r="R7" s="180"/>
+      <c r="S7" s="180"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="42"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="233"/>
-      <c r="D8" s="233"/>
-      <c r="E8" s="233"/>
-      <c r="F8" s="233"/>
-      <c r="G8" s="233"/>
-      <c r="H8" s="233"/>
-      <c r="I8" s="233"/>
-      <c r="J8" s="233"/>
-      <c r="K8" s="233"/>
-      <c r="L8" s="233"/>
-      <c r="M8" s="233"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="235"/>
-      <c r="P8" s="236"/>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
+      <c r="L8" s="173"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="177"/>
+      <c r="O8" s="178"/>
+      <c r="P8" s="179"/>
       <c r="Q8" s="43"/>
-      <c r="R8" s="237"/>
-      <c r="S8" s="237"/>
+      <c r="R8" s="180"/>
+      <c r="S8" s="180"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="42"/>
       <c r="B9" s="42"/>
-      <c r="C9" s="233"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
-      <c r="M9" s="233"/>
-      <c r="N9" s="234"/>
-      <c r="O9" s="235"/>
-      <c r="P9" s="236"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
+      <c r="L9" s="173"/>
+      <c r="M9" s="173"/>
+      <c r="N9" s="177"/>
+      <c r="O9" s="178"/>
+      <c r="P9" s="179"/>
       <c r="Q9" s="42"/>
-      <c r="R9" s="237"/>
-      <c r="S9" s="237"/>
+      <c r="R9" s="180"/>
+      <c r="S9" s="180"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="42"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="233"/>
-      <c r="E10" s="233"/>
-      <c r="F10" s="233"/>
-      <c r="G10" s="233"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="242"/>
-      <c r="K10" s="242"/>
-      <c r="L10" s="242"/>
-      <c r="M10" s="243"/>
-      <c r="N10" s="234"/>
-      <c r="O10" s="235"/>
-      <c r="P10" s="236"/>
+      <c r="C10" s="173"/>
+      <c r="D10" s="173"/>
+      <c r="E10" s="173"/>
+      <c r="F10" s="173"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="174"/>
+      <c r="I10" s="175"/>
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="175"/>
+      <c r="M10" s="176"/>
+      <c r="N10" s="177"/>
+      <c r="O10" s="178"/>
+      <c r="P10" s="179"/>
       <c r="Q10" s="43"/>
-      <c r="R10" s="237"/>
-      <c r="S10" s="237"/>
+      <c r="R10" s="180"/>
+      <c r="S10" s="180"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="42"/>
       <c r="B11" s="42"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
-      <c r="M11" s="243"/>
-      <c r="N11" s="234"/>
-      <c r="O11" s="235"/>
-      <c r="P11" s="236"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="173"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="174"/>
+      <c r="I11" s="175"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="176"/>
+      <c r="N11" s="177"/>
+      <c r="O11" s="178"/>
+      <c r="P11" s="179"/>
       <c r="Q11" s="42"/>
-      <c r="R11" s="237"/>
-      <c r="S11" s="237"/>
+      <c r="R11" s="180"/>
+      <c r="S11" s="180"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="42"/>
       <c r="B12" s="42"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="241"/>
-      <c r="I12" s="242"/>
-      <c r="J12" s="242"/>
-      <c r="K12" s="242"/>
-      <c r="L12" s="242"/>
-      <c r="M12" s="243"/>
-      <c r="N12" s="234"/>
-      <c r="O12" s="235"/>
-      <c r="P12" s="236"/>
+      <c r="C12" s="173"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="174"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
+      <c r="L12" s="175"/>
+      <c r="M12" s="176"/>
+      <c r="N12" s="177"/>
+      <c r="O12" s="178"/>
+      <c r="P12" s="179"/>
       <c r="Q12" s="42"/>
-      <c r="R12" s="237"/>
-      <c r="S12" s="237"/>
+      <c r="R12" s="180"/>
+      <c r="S12" s="180"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="42"/>
       <c r="B13" s="42"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
-      <c r="M13" s="243"/>
-      <c r="N13" s="234"/>
-      <c r="O13" s="235"/>
-      <c r="P13" s="236"/>
+      <c r="C13" s="173"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
+      <c r="L13" s="175"/>
+      <c r="M13" s="176"/>
+      <c r="N13" s="177"/>
+      <c r="O13" s="178"/>
+      <c r="P13" s="179"/>
       <c r="Q13" s="42"/>
-      <c r="R13" s="237"/>
-      <c r="S13" s="237"/>
+      <c r="R13" s="180"/>
+      <c r="S13" s="180"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="42"/>
       <c r="B14" s="42"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
-      <c r="M14" s="243"/>
-      <c r="N14" s="234"/>
-      <c r="O14" s="235"/>
-      <c r="P14" s="236"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="175"/>
+      <c r="L14" s="175"/>
+      <c r="M14" s="176"/>
+      <c r="N14" s="177"/>
+      <c r="O14" s="178"/>
+      <c r="P14" s="179"/>
       <c r="Q14" s="42"/>
-      <c r="R14" s="237"/>
-      <c r="S14" s="237"/>
+      <c r="R14" s="180"/>
+      <c r="S14" s="180"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="42"/>
       <c r="B15" s="42"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="233"/>
-      <c r="E15" s="233"/>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="241"/>
-      <c r="I15" s="242"/>
-      <c r="J15" s="242"/>
-      <c r="K15" s="242"/>
-      <c r="L15" s="242"/>
-      <c r="M15" s="243"/>
-      <c r="N15" s="234"/>
-      <c r="O15" s="235"/>
-      <c r="P15" s="236"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="174"/>
+      <c r="I15" s="175"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
+      <c r="L15" s="175"/>
+      <c r="M15" s="176"/>
+      <c r="N15" s="177"/>
+      <c r="O15" s="178"/>
+      <c r="P15" s="179"/>
       <c r="Q15" s="42"/>
-      <c r="R15" s="237"/>
-      <c r="S15" s="237"/>
+      <c r="R15" s="180"/>
+      <c r="S15" s="180"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="42"/>
       <c r="B16" s="42"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="233"/>
-      <c r="E16" s="233"/>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="242"/>
-      <c r="J16" s="242"/>
-      <c r="K16" s="242"/>
-      <c r="L16" s="242"/>
-      <c r="M16" s="243"/>
-      <c r="N16" s="234"/>
-      <c r="O16" s="235"/>
-      <c r="P16" s="236"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="174"/>
+      <c r="I16" s="175"/>
+      <c r="J16" s="175"/>
+      <c r="K16" s="175"/>
+      <c r="L16" s="175"/>
+      <c r="M16" s="176"/>
+      <c r="N16" s="177"/>
+      <c r="O16" s="178"/>
+      <c r="P16" s="179"/>
       <c r="Q16" s="42"/>
-      <c r="R16" s="237"/>
-      <c r="S16" s="237"/>
+      <c r="R16" s="180"/>
+      <c r="S16" s="180"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="42"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
-      <c r="M17" s="243"/>
-      <c r="N17" s="234"/>
-      <c r="O17" s="235"/>
-      <c r="P17" s="236"/>
+      <c r="C17" s="173"/>
+      <c r="D17" s="173"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="174"/>
+      <c r="I17" s="175"/>
+      <c r="J17" s="175"/>
+      <c r="K17" s="175"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="176"/>
+      <c r="N17" s="177"/>
+      <c r="O17" s="178"/>
+      <c r="P17" s="179"/>
       <c r="Q17" s="42"/>
-      <c r="R17" s="237"/>
-      <c r="S17" s="237"/>
+      <c r="R17" s="180"/>
+      <c r="S17" s="180"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="42"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
-      <c r="M18" s="243"/>
-      <c r="N18" s="234"/>
-      <c r="O18" s="235"/>
-      <c r="P18" s="236"/>
+      <c r="C18" s="173"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="174"/>
+      <c r="I18" s="175"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="175"/>
+      <c r="L18" s="175"/>
+      <c r="M18" s="176"/>
+      <c r="N18" s="177"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="179"/>
       <c r="Q18" s="42"/>
-      <c r="R18" s="237"/>
-      <c r="S18" s="237"/>
+      <c r="R18" s="180"/>
+      <c r="S18" s="180"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="42"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="233"/>
-      <c r="E19" s="233"/>
-      <c r="F19" s="233"/>
-      <c r="G19" s="233"/>
-      <c r="H19" s="241"/>
-      <c r="I19" s="242"/>
-      <c r="J19" s="242"/>
-      <c r="K19" s="242"/>
-      <c r="L19" s="242"/>
-      <c r="M19" s="243"/>
-      <c r="N19" s="234"/>
-      <c r="O19" s="235"/>
-      <c r="P19" s="236"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="174"/>
+      <c r="I19" s="175"/>
+      <c r="J19" s="175"/>
+      <c r="K19" s="175"/>
+      <c r="L19" s="175"/>
+      <c r="M19" s="176"/>
+      <c r="N19" s="177"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="179"/>
       <c r="Q19" s="42"/>
-      <c r="R19" s="237"/>
-      <c r="S19" s="237"/>
+      <c r="R19" s="180"/>
+      <c r="S19" s="180"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="42"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="233"/>
-      <c r="E20" s="233"/>
-      <c r="F20" s="233"/>
-      <c r="G20" s="233"/>
-      <c r="H20" s="241"/>
-      <c r="I20" s="242"/>
-      <c r="J20" s="242"/>
-      <c r="K20" s="242"/>
-      <c r="L20" s="242"/>
-      <c r="M20" s="243"/>
-      <c r="N20" s="234"/>
-      <c r="O20" s="235"/>
-      <c r="P20" s="236"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="174"/>
+      <c r="I20" s="175"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="175"/>
+      <c r="L20" s="175"/>
+      <c r="M20" s="176"/>
+      <c r="N20" s="177"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="179"/>
       <c r="Q20" s="42"/>
-      <c r="R20" s="237"/>
-      <c r="S20" s="237"/>
+      <c r="R20" s="180"/>
+      <c r="S20" s="180"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="42"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="233"/>
-      <c r="E21" s="233"/>
-      <c r="F21" s="233"/>
-      <c r="G21" s="233"/>
-      <c r="H21" s="241"/>
-      <c r="I21" s="242"/>
-      <c r="J21" s="242"/>
-      <c r="K21" s="242"/>
-      <c r="L21" s="242"/>
-      <c r="M21" s="243"/>
-      <c r="N21" s="234"/>
-      <c r="O21" s="235"/>
-      <c r="P21" s="236"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="173"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="173"/>
+      <c r="H21" s="174"/>
+      <c r="I21" s="175"/>
+      <c r="J21" s="175"/>
+      <c r="K21" s="175"/>
+      <c r="L21" s="175"/>
+      <c r="M21" s="176"/>
+      <c r="N21" s="177"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="179"/>
       <c r="Q21" s="42"/>
-      <c r="R21" s="237"/>
-      <c r="S21" s="237"/>
+      <c r="R21" s="180"/>
+      <c r="S21" s="180"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="233"/>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="233"/>
-      <c r="G22" s="233"/>
-      <c r="H22" s="241"/>
-      <c r="I22" s="242"/>
-      <c r="J22" s="242"/>
-      <c r="K22" s="242"/>
-      <c r="L22" s="242"/>
-      <c r="M22" s="243"/>
-      <c r="N22" s="234"/>
-      <c r="O22" s="235"/>
-      <c r="P22" s="236"/>
+      <c r="C22" s="173"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="174"/>
+      <c r="I22" s="175"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="175"/>
+      <c r="L22" s="175"/>
+      <c r="M22" s="176"/>
+      <c r="N22" s="177"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="179"/>
       <c r="Q22" s="42"/>
-      <c r="R22" s="237"/>
-      <c r="S22" s="237"/>
+      <c r="R22" s="180"/>
+      <c r="S22" s="180"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="42"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="233"/>
-      <c r="D23" s="233"/>
-      <c r="E23" s="233"/>
-      <c r="F23" s="233"/>
-      <c r="G23" s="233"/>
-      <c r="H23" s="241"/>
-      <c r="I23" s="242"/>
-      <c r="J23" s="242"/>
-      <c r="K23" s="242"/>
-      <c r="L23" s="242"/>
-      <c r="M23" s="243"/>
-      <c r="N23" s="234"/>
-      <c r="O23" s="235"/>
-      <c r="P23" s="236"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="174"/>
+      <c r="I23" s="175"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="175"/>
+      <c r="L23" s="175"/>
+      <c r="M23" s="176"/>
+      <c r="N23" s="177"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="179"/>
       <c r="Q23" s="42"/>
-      <c r="R23" s="237"/>
-      <c r="S23" s="237"/>
+      <c r="R23" s="180"/>
+      <c r="S23" s="180"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="42"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="233"/>
-      <c r="D24" s="233"/>
-      <c r="E24" s="233"/>
-      <c r="F24" s="233"/>
-      <c r="G24" s="233"/>
-      <c r="H24" s="241"/>
-      <c r="I24" s="242"/>
-      <c r="J24" s="242"/>
-      <c r="K24" s="242"/>
-      <c r="L24" s="242"/>
-      <c r="M24" s="243"/>
-      <c r="N24" s="234"/>
-      <c r="O24" s="235"/>
-      <c r="P24" s="236"/>
+      <c r="C24" s="173"/>
+      <c r="D24" s="173"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="173"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="174"/>
+      <c r="I24" s="175"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="175"/>
+      <c r="L24" s="175"/>
+      <c r="M24" s="176"/>
+      <c r="N24" s="177"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="179"/>
       <c r="Q24" s="42"/>
-      <c r="R24" s="237"/>
-      <c r="S24" s="237"/>
+      <c r="R24" s="180"/>
+      <c r="S24" s="180"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="42"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="233"/>
-      <c r="D25" s="233"/>
-      <c r="E25" s="233"/>
-      <c r="F25" s="233"/>
-      <c r="G25" s="233"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
-      <c r="M25" s="243"/>
-      <c r="N25" s="234"/>
-      <c r="O25" s="235"/>
-      <c r="P25" s="236"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="173"/>
+      <c r="H25" s="174"/>
+      <c r="I25" s="175"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="175"/>
+      <c r="L25" s="175"/>
+      <c r="M25" s="176"/>
+      <c r="N25" s="177"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="179"/>
       <c r="Q25" s="42"/>
-      <c r="R25" s="237"/>
-      <c r="S25" s="237"/>
+      <c r="R25" s="180"/>
+      <c r="S25" s="180"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="233"/>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="233"/>
-      <c r="G26" s="233"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
-      <c r="M26" s="243"/>
-      <c r="N26" s="234"/>
-      <c r="O26" s="235"/>
-      <c r="P26" s="236"/>
+      <c r="C26" s="173"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="174"/>
+      <c r="I26" s="175"/>
+      <c r="J26" s="175"/>
+      <c r="K26" s="175"/>
+      <c r="L26" s="175"/>
+      <c r="M26" s="176"/>
+      <c r="N26" s="177"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="179"/>
       <c r="Q26" s="42"/>
-      <c r="R26" s="237"/>
-      <c r="S26" s="237"/>
+      <c r="R26" s="180"/>
+      <c r="S26" s="180"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="233"/>
-      <c r="D27" s="233"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="233"/>
-      <c r="H27" s="241"/>
-      <c r="I27" s="242"/>
-      <c r="J27" s="242"/>
-      <c r="K27" s="242"/>
-      <c r="L27" s="242"/>
-      <c r="M27" s="243"/>
-      <c r="N27" s="234"/>
-      <c r="O27" s="235"/>
-      <c r="P27" s="236"/>
+      <c r="C27" s="173"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="175"/>
+      <c r="M27" s="176"/>
+      <c r="N27" s="177"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="179"/>
       <c r="Q27" s="42"/>
-      <c r="R27" s="237"/>
-      <c r="S27" s="237"/>
+      <c r="R27" s="180"/>
+      <c r="S27" s="180"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="42"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="233"/>
-      <c r="D28" s="233"/>
-      <c r="E28" s="233"/>
-      <c r="F28" s="233"/>
-      <c r="G28" s="233"/>
-      <c r="H28" s="241"/>
-      <c r="I28" s="242"/>
-      <c r="J28" s="242"/>
-      <c r="K28" s="242"/>
-      <c r="L28" s="242"/>
-      <c r="M28" s="243"/>
-      <c r="N28" s="234"/>
-      <c r="O28" s="235"/>
-      <c r="P28" s="236"/>
+      <c r="C28" s="173"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="175"/>
+      <c r="J28" s="175"/>
+      <c r="K28" s="175"/>
+      <c r="L28" s="175"/>
+      <c r="M28" s="176"/>
+      <c r="N28" s="177"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="179"/>
       <c r="Q28" s="42"/>
-      <c r="R28" s="237"/>
-      <c r="S28" s="237"/>
+      <c r="R28" s="180"/>
+      <c r="S28" s="180"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="42"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="233"/>
-      <c r="D29" s="233"/>
-      <c r="E29" s="233"/>
-      <c r="F29" s="233"/>
-      <c r="G29" s="233"/>
-      <c r="H29" s="241"/>
-      <c r="I29" s="242"/>
-      <c r="J29" s="242"/>
-      <c r="K29" s="242"/>
-      <c r="L29" s="242"/>
-      <c r="M29" s="243"/>
-      <c r="N29" s="234"/>
-      <c r="O29" s="235"/>
-      <c r="P29" s="236"/>
+      <c r="C29" s="173"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="176"/>
+      <c r="N29" s="177"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="179"/>
       <c r="Q29" s="42"/>
-      <c r="R29" s="237"/>
-      <c r="S29" s="237"/>
+      <c r="R29" s="180"/>
+      <c r="S29" s="180"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="42"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="233"/>
-      <c r="D30" s="233"/>
-      <c r="E30" s="233"/>
-      <c r="F30" s="233"/>
-      <c r="G30" s="233"/>
-      <c r="H30" s="241"/>
-      <c r="I30" s="242"/>
-      <c r="J30" s="242"/>
-      <c r="K30" s="242"/>
-      <c r="L30" s="242"/>
-      <c r="M30" s="243"/>
-      <c r="N30" s="234"/>
-      <c r="O30" s="235"/>
-      <c r="P30" s="236"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="175"/>
+      <c r="L30" s="175"/>
+      <c r="M30" s="176"/>
+      <c r="N30" s="177"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="179"/>
       <c r="Q30" s="42"/>
-      <c r="R30" s="237"/>
-      <c r="S30" s="237"/>
+      <c r="R30" s="180"/>
+      <c r="S30" s="180"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="42"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="233"/>
-      <c r="D31" s="233"/>
-      <c r="E31" s="233"/>
-      <c r="F31" s="233"/>
-      <c r="G31" s="233"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="242"/>
-      <c r="J31" s="242"/>
-      <c r="K31" s="242"/>
-      <c r="L31" s="242"/>
-      <c r="M31" s="243"/>
-      <c r="N31" s="234"/>
-      <c r="O31" s="235"/>
-      <c r="P31" s="236"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="177"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="179"/>
       <c r="Q31" s="42"/>
-      <c r="R31" s="237"/>
-      <c r="S31" s="237"/>
+      <c r="R31" s="180"/>
+      <c r="S31" s="180"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="42"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="233"/>
-      <c r="D32" s="233"/>
-      <c r="E32" s="233"/>
-      <c r="F32" s="233"/>
-      <c r="G32" s="233"/>
-      <c r="H32" s="241"/>
-      <c r="I32" s="242"/>
-      <c r="J32" s="242"/>
-      <c r="K32" s="242"/>
-      <c r="L32" s="242"/>
-      <c r="M32" s="243"/>
-      <c r="N32" s="234"/>
-      <c r="O32" s="235"/>
-      <c r="P32" s="236"/>
+      <c r="C32" s="173"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="175"/>
+      <c r="J32" s="175"/>
+      <c r="K32" s="175"/>
+      <c r="L32" s="175"/>
+      <c r="M32" s="176"/>
+      <c r="N32" s="177"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="179"/>
       <c r="Q32" s="42"/>
-      <c r="R32" s="237"/>
-      <c r="S32" s="237"/>
+      <c r="R32" s="180"/>
+      <c r="S32" s="180"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="42"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="242"/>
-      <c r="J33" s="242"/>
-      <c r="K33" s="242"/>
-      <c r="L33" s="242"/>
-      <c r="M33" s="243"/>
-      <c r="N33" s="234"/>
-      <c r="O33" s="235"/>
-      <c r="P33" s="236"/>
+      <c r="C33" s="173"/>
+      <c r="D33" s="173"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="173"/>
+      <c r="G33" s="173"/>
+      <c r="H33" s="174"/>
+      <c r="I33" s="175"/>
+      <c r="J33" s="175"/>
+      <c r="K33" s="175"/>
+      <c r="L33" s="175"/>
+      <c r="M33" s="176"/>
+      <c r="N33" s="177"/>
+      <c r="O33" s="178"/>
+      <c r="P33" s="179"/>
       <c r="Q33" s="42"/>
-      <c r="R33" s="237"/>
-      <c r="S33" s="237"/>
+      <c r="R33" s="180"/>
+      <c r="S33" s="180"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="42"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="233"/>
-      <c r="D34" s="233"/>
-      <c r="E34" s="233"/>
-      <c r="F34" s="233"/>
-      <c r="G34" s="233"/>
-      <c r="H34" s="241"/>
-      <c r="I34" s="242"/>
-      <c r="J34" s="242"/>
-      <c r="K34" s="242"/>
-      <c r="L34" s="242"/>
-      <c r="M34" s="243"/>
-      <c r="N34" s="234"/>
-      <c r="O34" s="235"/>
-      <c r="P34" s="236"/>
+      <c r="C34" s="173"/>
+      <c r="D34" s="173"/>
+      <c r="E34" s="173"/>
+      <c r="F34" s="173"/>
+      <c r="G34" s="173"/>
+      <c r="H34" s="174"/>
+      <c r="I34" s="175"/>
+      <c r="J34" s="175"/>
+      <c r="K34" s="175"/>
+      <c r="L34" s="175"/>
+      <c r="M34" s="176"/>
+      <c r="N34" s="177"/>
+      <c r="O34" s="178"/>
+      <c r="P34" s="179"/>
       <c r="Q34" s="42"/>
-      <c r="R34" s="237"/>
-      <c r="S34" s="237"/>
+      <c r="R34" s="180"/>
+      <c r="S34" s="180"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="42"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="233"/>
-      <c r="D35" s="233"/>
-      <c r="E35" s="233"/>
-      <c r="F35" s="233"/>
-      <c r="G35" s="233"/>
-      <c r="H35" s="241"/>
-      <c r="I35" s="242"/>
-      <c r="J35" s="242"/>
-      <c r="K35" s="242"/>
-      <c r="L35" s="242"/>
-      <c r="M35" s="243"/>
-      <c r="N35" s="234"/>
-      <c r="O35" s="235"/>
-      <c r="P35" s="236"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="173"/>
+      <c r="G35" s="173"/>
+      <c r="H35" s="174"/>
+      <c r="I35" s="175"/>
+      <c r="J35" s="175"/>
+      <c r="K35" s="175"/>
+      <c r="L35" s="175"/>
+      <c r="M35" s="176"/>
+      <c r="N35" s="177"/>
+      <c r="O35" s="178"/>
+      <c r="P35" s="179"/>
       <c r="Q35" s="42"/>
-      <c r="R35" s="237"/>
-      <c r="S35" s="237"/>
+      <c r="R35" s="180"/>
+      <c r="S35" s="180"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="42"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="233"/>
-      <c r="D36" s="233"/>
-      <c r="E36" s="233"/>
-      <c r="F36" s="233"/>
-      <c r="G36" s="233"/>
-      <c r="H36" s="241"/>
-      <c r="I36" s="242"/>
-      <c r="J36" s="242"/>
-      <c r="K36" s="242"/>
-      <c r="L36" s="242"/>
-      <c r="M36" s="243"/>
-      <c r="N36" s="234"/>
-      <c r="O36" s="235"/>
-      <c r="P36" s="236"/>
+      <c r="C36" s="173"/>
+      <c r="D36" s="173"/>
+      <c r="E36" s="173"/>
+      <c r="F36" s="173"/>
+      <c r="G36" s="173"/>
+      <c r="H36" s="174"/>
+      <c r="I36" s="175"/>
+      <c r="J36" s="175"/>
+      <c r="K36" s="175"/>
+      <c r="L36" s="175"/>
+      <c r="M36" s="176"/>
+      <c r="N36" s="177"/>
+      <c r="O36" s="178"/>
+      <c r="P36" s="179"/>
       <c r="Q36" s="42"/>
-      <c r="R36" s="237"/>
-      <c r="S36" s="237"/>
+      <c r="R36" s="180"/>
+      <c r="S36" s="180"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="42"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="233"/>
-      <c r="D37" s="233"/>
-      <c r="E37" s="233"/>
-      <c r="F37" s="233"/>
-      <c r="G37" s="233"/>
-      <c r="H37" s="241"/>
-      <c r="I37" s="242"/>
-      <c r="J37" s="242"/>
-      <c r="K37" s="242"/>
-      <c r="L37" s="242"/>
-      <c r="M37" s="243"/>
-      <c r="N37" s="234"/>
-      <c r="O37" s="235"/>
-      <c r="P37" s="236"/>
+      <c r="C37" s="173"/>
+      <c r="D37" s="173"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="174"/>
+      <c r="I37" s="175"/>
+      <c r="J37" s="175"/>
+      <c r="K37" s="175"/>
+      <c r="L37" s="175"/>
+      <c r="M37" s="176"/>
+      <c r="N37" s="177"/>
+      <c r="O37" s="178"/>
+      <c r="P37" s="179"/>
       <c r="Q37" s="42"/>
-      <c r="R37" s="237"/>
-      <c r="S37" s="237"/>
+      <c r="R37" s="180"/>
+      <c r="S37" s="180"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="42"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="233"/>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="233"/>
-      <c r="G38" s="233"/>
-      <c r="H38" s="241"/>
-      <c r="I38" s="242"/>
-      <c r="J38" s="242"/>
-      <c r="K38" s="242"/>
-      <c r="L38" s="242"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="234"/>
-      <c r="O38" s="235"/>
-      <c r="P38" s="236"/>
+      <c r="C38" s="173"/>
+      <c r="D38" s="173"/>
+      <c r="E38" s="173"/>
+      <c r="F38" s="173"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="174"/>
+      <c r="I38" s="175"/>
+      <c r="J38" s="175"/>
+      <c r="K38" s="175"/>
+      <c r="L38" s="175"/>
+      <c r="M38" s="176"/>
+      <c r="N38" s="177"/>
+      <c r="O38" s="178"/>
+      <c r="P38" s="179"/>
       <c r="Q38" s="42"/>
-      <c r="R38" s="237"/>
-      <c r="S38" s="237"/>
+      <c r="R38" s="180"/>
+      <c r="S38" s="180"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="42"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="241"/>
-      <c r="I39" s="242"/>
-      <c r="J39" s="242"/>
-      <c r="K39" s="242"/>
-      <c r="L39" s="242"/>
-      <c r="M39" s="243"/>
-      <c r="N39" s="234"/>
-      <c r="O39" s="235"/>
-      <c r="P39" s="236"/>
+      <c r="C39" s="173"/>
+      <c r="D39" s="173"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="174"/>
+      <c r="I39" s="175"/>
+      <c r="J39" s="175"/>
+      <c r="K39" s="175"/>
+      <c r="L39" s="175"/>
+      <c r="M39" s="176"/>
+      <c r="N39" s="177"/>
+      <c r="O39" s="178"/>
+      <c r="P39" s="179"/>
       <c r="Q39" s="42"/>
-      <c r="R39" s="237"/>
-      <c r="S39" s="237"/>
+      <c r="R39" s="180"/>
+      <c r="S39" s="180"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="42"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="233"/>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
-      <c r="K40" s="242"/>
-      <c r="L40" s="242"/>
-      <c r="M40" s="243"/>
-      <c r="N40" s="234"/>
-      <c r="O40" s="235"/>
-      <c r="P40" s="236"/>
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="174"/>
+      <c r="I40" s="175"/>
+      <c r="J40" s="175"/>
+      <c r="K40" s="175"/>
+      <c r="L40" s="175"/>
+      <c r="M40" s="176"/>
+      <c r="N40" s="177"/>
+      <c r="O40" s="178"/>
+      <c r="P40" s="179"/>
       <c r="Q40" s="42"/>
-      <c r="R40" s="237"/>
-      <c r="S40" s="237"/>
+      <c r="R40" s="180"/>
+      <c r="S40" s="180"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="42"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="233"/>
-      <c r="D41" s="233"/>
-      <c r="E41" s="233"/>
-      <c r="F41" s="233"/>
-      <c r="G41" s="233"/>
-      <c r="H41" s="241"/>
-      <c r="I41" s="242"/>
-      <c r="J41" s="242"/>
-      <c r="K41" s="242"/>
-      <c r="L41" s="242"/>
-      <c r="M41" s="243"/>
-      <c r="N41" s="234"/>
-      <c r="O41" s="235"/>
-      <c r="P41" s="236"/>
+      <c r="C41" s="173"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="174"/>
+      <c r="I41" s="175"/>
+      <c r="J41" s="175"/>
+      <c r="K41" s="175"/>
+      <c r="L41" s="175"/>
+      <c r="M41" s="176"/>
+      <c r="N41" s="177"/>
+      <c r="O41" s="178"/>
+      <c r="P41" s="179"/>
       <c r="Q41" s="42"/>
-      <c r="R41" s="237"/>
-      <c r="S41" s="237"/>
+      <c r="R41" s="180"/>
+      <c r="S41" s="180"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="42"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="241"/>
-      <c r="I42" s="242"/>
-      <c r="J42" s="242"/>
-      <c r="K42" s="242"/>
-      <c r="L42" s="242"/>
-      <c r="M42" s="243"/>
-      <c r="N42" s="234"/>
-      <c r="O42" s="235"/>
-      <c r="P42" s="236"/>
+      <c r="C42" s="173"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="173"/>
+      <c r="F42" s="173"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="174"/>
+      <c r="I42" s="175"/>
+      <c r="J42" s="175"/>
+      <c r="K42" s="175"/>
+      <c r="L42" s="175"/>
+      <c r="M42" s="176"/>
+      <c r="N42" s="177"/>
+      <c r="O42" s="178"/>
+      <c r="P42" s="179"/>
       <c r="Q42" s="42"/>
-      <c r="R42" s="237"/>
-      <c r="S42" s="237"/>
+      <c r="R42" s="180"/>
+      <c r="S42" s="180"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="42"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="233"/>
-      <c r="D43" s="233"/>
-      <c r="E43" s="233"/>
-      <c r="F43" s="233"/>
-      <c r="G43" s="233"/>
-      <c r="H43" s="241"/>
-      <c r="I43" s="242"/>
-      <c r="J43" s="242"/>
-      <c r="K43" s="242"/>
-      <c r="L43" s="242"/>
-      <c r="M43" s="243"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="235"/>
-      <c r="P43" s="236"/>
+      <c r="C43" s="173"/>
+      <c r="D43" s="173"/>
+      <c r="E43" s="173"/>
+      <c r="F43" s="173"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="174"/>
+      <c r="I43" s="175"/>
+      <c r="J43" s="175"/>
+      <c r="K43" s="175"/>
+      <c r="L43" s="175"/>
+      <c r="M43" s="176"/>
+      <c r="N43" s="177"/>
+      <c r="O43" s="178"/>
+      <c r="P43" s="179"/>
       <c r="Q43" s="42"/>
-      <c r="R43" s="237"/>
-      <c r="S43" s="237"/>
+      <c r="R43" s="180"/>
+      <c r="S43" s="180"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="42"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="233"/>
-      <c r="D44" s="233"/>
-      <c r="E44" s="233"/>
-      <c r="F44" s="233"/>
-      <c r="G44" s="233"/>
-      <c r="H44" s="241"/>
-      <c r="I44" s="242"/>
-      <c r="J44" s="242"/>
-      <c r="K44" s="242"/>
-      <c r="L44" s="242"/>
-      <c r="M44" s="243"/>
-      <c r="N44" s="234"/>
-      <c r="O44" s="235"/>
-      <c r="P44" s="236"/>
+      <c r="C44" s="173"/>
+      <c r="D44" s="173"/>
+      <c r="E44" s="173"/>
+      <c r="F44" s="173"/>
+      <c r="G44" s="173"/>
+      <c r="H44" s="174"/>
+      <c r="I44" s="175"/>
+      <c r="J44" s="175"/>
+      <c r="K44" s="175"/>
+      <c r="L44" s="175"/>
+      <c r="M44" s="176"/>
+      <c r="N44" s="177"/>
+      <c r="O44" s="178"/>
+      <c r="P44" s="179"/>
       <c r="Q44" s="42"/>
-      <c r="R44" s="237"/>
-      <c r="S44" s="237"/>
+      <c r="R44" s="180"/>
+      <c r="S44" s="180"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="42"/>
       <c r="B45" s="42"/>
-      <c r="C45" s="233"/>
-      <c r="D45" s="233"/>
-      <c r="E45" s="233"/>
-      <c r="F45" s="233"/>
-      <c r="G45" s="233"/>
-      <c r="H45" s="241"/>
-      <c r="I45" s="242"/>
-      <c r="J45" s="242"/>
-      <c r="K45" s="242"/>
-      <c r="L45" s="242"/>
-      <c r="M45" s="243"/>
-      <c r="N45" s="234"/>
-      <c r="O45" s="235"/>
-      <c r="P45" s="236"/>
+      <c r="C45" s="173"/>
+      <c r="D45" s="173"/>
+      <c r="E45" s="173"/>
+      <c r="F45" s="173"/>
+      <c r="G45" s="173"/>
+      <c r="H45" s="174"/>
+      <c r="I45" s="175"/>
+      <c r="J45" s="175"/>
+      <c r="K45" s="175"/>
+      <c r="L45" s="175"/>
+      <c r="M45" s="176"/>
+      <c r="N45" s="177"/>
+      <c r="O45" s="178"/>
+      <c r="P45" s="179"/>
       <c r="Q45" s="42"/>
-      <c r="R45" s="237"/>
-      <c r="S45" s="237"/>
+      <c r="R45" s="180"/>
+      <c r="S45" s="180"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="42"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="233"/>
-      <c r="D46" s="233"/>
-      <c r="E46" s="233"/>
-      <c r="F46" s="233"/>
-      <c r="G46" s="233"/>
-      <c r="H46" s="241"/>
-      <c r="I46" s="242"/>
-      <c r="J46" s="242"/>
-      <c r="K46" s="242"/>
-      <c r="L46" s="242"/>
-      <c r="M46" s="243"/>
-      <c r="N46" s="234"/>
-      <c r="O46" s="235"/>
-      <c r="P46" s="236"/>
+      <c r="C46" s="173"/>
+      <c r="D46" s="173"/>
+      <c r="E46" s="173"/>
+      <c r="F46" s="173"/>
+      <c r="G46" s="173"/>
+      <c r="H46" s="174"/>
+      <c r="I46" s="175"/>
+      <c r="J46" s="175"/>
+      <c r="K46" s="175"/>
+      <c r="L46" s="175"/>
+      <c r="M46" s="176"/>
+      <c r="N46" s="177"/>
+      <c r="O46" s="178"/>
+      <c r="P46" s="179"/>
       <c r="Q46" s="42"/>
-      <c r="R46" s="237"/>
-      <c r="S46" s="237"/>
+      <c r="R46" s="180"/>
+      <c r="S46" s="180"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="42"/>
       <c r="B47" s="42"/>
-      <c r="C47" s="233"/>
-      <c r="D47" s="233"/>
-      <c r="E47" s="233"/>
-      <c r="F47" s="233"/>
-      <c r="G47" s="233"/>
-      <c r="H47" s="241"/>
-      <c r="I47" s="242"/>
-      <c r="J47" s="242"/>
-      <c r="K47" s="242"/>
-      <c r="L47" s="242"/>
-      <c r="M47" s="243"/>
-      <c r="N47" s="234"/>
-      <c r="O47" s="235"/>
-      <c r="P47" s="236"/>
+      <c r="C47" s="173"/>
+      <c r="D47" s="173"/>
+      <c r="E47" s="173"/>
+      <c r="F47" s="173"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="174"/>
+      <c r="I47" s="175"/>
+      <c r="J47" s="175"/>
+      <c r="K47" s="175"/>
+      <c r="L47" s="175"/>
+      <c r="M47" s="176"/>
+      <c r="N47" s="177"/>
+      <c r="O47" s="178"/>
+      <c r="P47" s="179"/>
       <c r="Q47" s="42"/>
-      <c r="R47" s="237"/>
-      <c r="S47" s="237"/>
+      <c r="R47" s="180"/>
+      <c r="S47" s="180"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="42"/>
       <c r="B48" s="42"/>
-      <c r="C48" s="233"/>
-      <c r="D48" s="233"/>
-      <c r="E48" s="233"/>
-      <c r="F48" s="233"/>
-      <c r="G48" s="233"/>
-      <c r="H48" s="241"/>
-      <c r="I48" s="242"/>
-      <c r="J48" s="242"/>
-      <c r="K48" s="242"/>
-      <c r="L48" s="242"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="234"/>
-      <c r="O48" s="235"/>
-      <c r="P48" s="236"/>
+      <c r="C48" s="173"/>
+      <c r="D48" s="173"/>
+      <c r="E48" s="173"/>
+      <c r="F48" s="173"/>
+      <c r="G48" s="173"/>
+      <c r="H48" s="174"/>
+      <c r="I48" s="175"/>
+      <c r="J48" s="175"/>
+      <c r="K48" s="175"/>
+      <c r="L48" s="175"/>
+      <c r="M48" s="176"/>
+      <c r="N48" s="177"/>
+      <c r="O48" s="178"/>
+      <c r="P48" s="179"/>
       <c r="Q48" s="42"/>
-      <c r="R48" s="237"/>
-      <c r="S48" s="237"/>
+      <c r="R48" s="180"/>
+      <c r="S48" s="180"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="42"/>
       <c r="B49" s="42"/>
-      <c r="C49" s="233"/>
-      <c r="D49" s="233"/>
-      <c r="E49" s="233"/>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="241"/>
-      <c r="I49" s="242"/>
-      <c r="J49" s="242"/>
-      <c r="K49" s="242"/>
-      <c r="L49" s="242"/>
-      <c r="M49" s="243"/>
-      <c r="N49" s="234"/>
-      <c r="O49" s="235"/>
-      <c r="P49" s="236"/>
+      <c r="C49" s="173"/>
+      <c r="D49" s="173"/>
+      <c r="E49" s="173"/>
+      <c r="F49" s="173"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="174"/>
+      <c r="I49" s="175"/>
+      <c r="J49" s="175"/>
+      <c r="K49" s="175"/>
+      <c r="L49" s="175"/>
+      <c r="M49" s="176"/>
+      <c r="N49" s="177"/>
+      <c r="O49" s="178"/>
+      <c r="P49" s="179"/>
       <c r="Q49" s="42"/>
-      <c r="R49" s="237"/>
-      <c r="S49" s="237"/>
+      <c r="R49" s="180"/>
+      <c r="S49" s="180"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="42"/>
       <c r="B50" s="42"/>
-      <c r="C50" s="233"/>
-      <c r="D50" s="233"/>
-      <c r="E50" s="233"/>
-      <c r="F50" s="233"/>
-      <c r="G50" s="233"/>
-      <c r="H50" s="241"/>
-      <c r="I50" s="242"/>
-      <c r="J50" s="242"/>
-      <c r="K50" s="242"/>
-      <c r="L50" s="242"/>
-      <c r="M50" s="243"/>
-      <c r="N50" s="234"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="236"/>
+      <c r="C50" s="173"/>
+      <c r="D50" s="173"/>
+      <c r="E50" s="173"/>
+      <c r="F50" s="173"/>
+      <c r="G50" s="173"/>
+      <c r="H50" s="174"/>
+      <c r="I50" s="175"/>
+      <c r="J50" s="175"/>
+      <c r="K50" s="175"/>
+      <c r="L50" s="175"/>
+      <c r="M50" s="176"/>
+      <c r="N50" s="177"/>
+      <c r="O50" s="178"/>
+      <c r="P50" s="179"/>
       <c r="Q50" s="42"/>
-      <c r="R50" s="237"/>
-      <c r="S50" s="237"/>
+      <c r="R50" s="180"/>
+      <c r="S50" s="180"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="42"/>
       <c r="B51" s="42"/>
-      <c r="C51" s="233"/>
-      <c r="D51" s="233"/>
-      <c r="E51" s="233"/>
-      <c r="F51" s="233"/>
-      <c r="G51" s="233"/>
-      <c r="H51" s="241"/>
-      <c r="I51" s="242"/>
-      <c r="J51" s="242"/>
-      <c r="K51" s="242"/>
-      <c r="L51" s="242"/>
-      <c r="M51" s="243"/>
-      <c r="N51" s="234"/>
-      <c r="O51" s="235"/>
-      <c r="P51" s="236"/>
+      <c r="C51" s="173"/>
+      <c r="D51" s="173"/>
+      <c r="E51" s="173"/>
+      <c r="F51" s="173"/>
+      <c r="G51" s="173"/>
+      <c r="H51" s="174"/>
+      <c r="I51" s="175"/>
+      <c r="J51" s="175"/>
+      <c r="K51" s="175"/>
+      <c r="L51" s="175"/>
+      <c r="M51" s="176"/>
+      <c r="N51" s="177"/>
+      <c r="O51" s="178"/>
+      <c r="P51" s="179"/>
       <c r="Q51" s="42"/>
-      <c r="R51" s="237"/>
-      <c r="S51" s="237"/>
+      <c r="R51" s="180"/>
+      <c r="S51" s="180"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="42"/>
       <c r="B52" s="42"/>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="241"/>
-      <c r="I52" s="242"/>
-      <c r="J52" s="242"/>
-      <c r="K52" s="242"/>
-      <c r="L52" s="242"/>
-      <c r="M52" s="243"/>
-      <c r="N52" s="234"/>
-      <c r="O52" s="235"/>
-      <c r="P52" s="236"/>
+      <c r="C52" s="173"/>
+      <c r="D52" s="173"/>
+      <c r="E52" s="173"/>
+      <c r="F52" s="173"/>
+      <c r="G52" s="173"/>
+      <c r="H52" s="174"/>
+      <c r="I52" s="175"/>
+      <c r="J52" s="175"/>
+      <c r="K52" s="175"/>
+      <c r="L52" s="175"/>
+      <c r="M52" s="176"/>
+      <c r="N52" s="177"/>
+      <c r="O52" s="178"/>
+      <c r="P52" s="179"/>
       <c r="Q52" s="42"/>
-      <c r="R52" s="237"/>
-      <c r="S52" s="237"/>
+      <c r="R52" s="180"/>
+      <c r="S52" s="180"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -15016,6 +14877,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -15079,23 +15128,23 @@
       <c r="AL1" s="49"/>
       <c r="AM1" s="49"/>
       <c r="AN1" s="49"/>
-      <c r="AO1" s="247" t="s">
+      <c r="AO1" s="207" t="s">
         <v>80</v>
       </c>
-      <c r="AP1" s="247"/>
-      <c r="AQ1" s="247"/>
-      <c r="AR1" s="247"/>
-      <c r="AS1" s="247"/>
-      <c r="AT1" s="248">
+      <c r="AP1" s="207"/>
+      <c r="AQ1" s="207"/>
+      <c r="AR1" s="207"/>
+      <c r="AS1" s="207"/>
+      <c r="AT1" s="208">
         <v>46191</v>
       </c>
-      <c r="AU1" s="249"/>
-      <c r="AV1" s="249"/>
-      <c r="AW1" s="249"/>
-      <c r="AX1" s="249"/>
-      <c r="AY1" s="249"/>
-      <c r="AZ1" s="249"/>
-      <c r="BA1" s="249"/>
+      <c r="AU1" s="209"/>
+      <c r="AV1" s="209"/>
+      <c r="AW1" s="209"/>
+      <c r="AX1" s="209"/>
+      <c r="AY1" s="209"/>
+      <c r="AZ1" s="209"/>
+      <c r="BA1" s="209"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -15141,52 +15190,52 @@
       <c r="AK4" s="57"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="244" t="s">
+      <c r="A5" s="204" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="245"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="250"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="251"/>
-      <c r="L5" s="251"/>
-      <c r="M5" s="251"/>
-      <c r="N5" s="251"/>
-      <c r="O5" s="251"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="252"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="210"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="M5" s="211"/>
+      <c r="N5" s="211"/>
+      <c r="O5" s="211"/>
+      <c r="P5" s="211"/>
+      <c r="Q5" s="211"/>
+      <c r="R5" s="211"/>
+      <c r="S5" s="212"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="244" t="s">
+      <c r="A6" s="204" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="245"/>
-      <c r="C6" s="245"/>
-      <c r="D6" s="245"/>
-      <c r="E6" s="245"/>
-      <c r="F6" s="246"/>
-      <c r="G6" s="253">
+      <c r="B6" s="205"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="213">
         <v>1</v>
       </c>
-      <c r="H6" s="251"/>
-      <c r="I6" s="251"/>
-      <c r="J6" s="251"/>
-      <c r="K6" s="251"/>
-      <c r="L6" s="251"/>
-      <c r="M6" s="251"/>
-      <c r="N6" s="251"/>
-      <c r="O6" s="251"/>
-      <c r="P6" s="251"/>
-      <c r="Q6" s="251"/>
-      <c r="R6" s="251"/>
-      <c r="S6" s="252"/>
+      <c r="H6" s="211"/>
+      <c r="I6" s="211"/>
+      <c r="J6" s="211"/>
+      <c r="K6" s="211"/>
+      <c r="L6" s="211"/>
+      <c r="M6" s="211"/>
+      <c r="N6" s="211"/>
+      <c r="O6" s="211"/>
+      <c r="P6" s="211"/>
+      <c r="Q6" s="211"/>
+      <c r="R6" s="211"/>
+      <c r="S6" s="212"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -15195,61 +15244,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="244" t="s">
+      <c r="A9" s="204" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="245"/>
-      <c r="C9" s="245"/>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="245"/>
-      <c r="H9" s="245"/>
-      <c r="I9" s="245"/>
-      <c r="J9" s="245"/>
-      <c r="K9" s="245"/>
-      <c r="L9" s="245"/>
-      <c r="M9" s="245"/>
-      <c r="N9" s="245"/>
-      <c r="O9" s="245"/>
-      <c r="P9" s="245"/>
-      <c r="Q9" s="245"/>
-      <c r="R9" s="245"/>
-      <c r="S9" s="245"/>
-      <c r="T9" s="245"/>
-      <c r="U9" s="245"/>
-      <c r="V9" s="245"/>
-      <c r="W9" s="245"/>
-      <c r="X9" s="245"/>
-      <c r="Y9" s="245"/>
-      <c r="Z9" s="245"/>
-      <c r="AA9" s="245"/>
-      <c r="AB9" s="245"/>
-      <c r="AC9" s="245"/>
-      <c r="AD9" s="245"/>
-      <c r="AE9" s="245"/>
-      <c r="AF9" s="245"/>
-      <c r="AG9" s="245"/>
-      <c r="AH9" s="245"/>
-      <c r="AI9" s="245"/>
-      <c r="AJ9" s="245"/>
-      <c r="AK9" s="245"/>
-      <c r="AL9" s="245"/>
-      <c r="AM9" s="245"/>
-      <c r="AN9" s="245"/>
-      <c r="AO9" s="245"/>
-      <c r="AP9" s="245"/>
-      <c r="AQ9" s="245"/>
-      <c r="AR9" s="245"/>
-      <c r="AS9" s="245"/>
-      <c r="AT9" s="245"/>
-      <c r="AU9" s="245"/>
-      <c r="AV9" s="245"/>
-      <c r="AW9" s="245"/>
-      <c r="AX9" s="245"/>
-      <c r="AY9" s="245"/>
-      <c r="AZ9" s="245"/>
-      <c r="BA9" s="246"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205"/>
+      <c r="I9" s="205"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="205"/>
+      <c r="L9" s="205"/>
+      <c r="M9" s="205"/>
+      <c r="N9" s="205"/>
+      <c r="O9" s="205"/>
+      <c r="P9" s="205"/>
+      <c r="Q9" s="205"/>
+      <c r="R9" s="205"/>
+      <c r="S9" s="205"/>
+      <c r="T9" s="205"/>
+      <c r="U9" s="205"/>
+      <c r="V9" s="205"/>
+      <c r="W9" s="205"/>
+      <c r="X9" s="205"/>
+      <c r="Y9" s="205"/>
+      <c r="Z9" s="205"/>
+      <c r="AA9" s="205"/>
+      <c r="AB9" s="205"/>
+      <c r="AC9" s="205"/>
+      <c r="AD9" s="205"/>
+      <c r="AE9" s="205"/>
+      <c r="AF9" s="205"/>
+      <c r="AG9" s="205"/>
+      <c r="AH9" s="205"/>
+      <c r="AI9" s="205"/>
+      <c r="AJ9" s="205"/>
+      <c r="AK9" s="205"/>
+      <c r="AL9" s="205"/>
+      <c r="AM9" s="205"/>
+      <c r="AN9" s="205"/>
+      <c r="AO9" s="205"/>
+      <c r="AP9" s="205"/>
+      <c r="AQ9" s="205"/>
+      <c r="AR9" s="205"/>
+      <c r="AS9" s="205"/>
+      <c r="AT9" s="205"/>
+      <c r="AU9" s="205"/>
+      <c r="AV9" s="205"/>
+      <c r="AW9" s="205"/>
+      <c r="AX9" s="205"/>
+      <c r="AY9" s="205"/>
+      <c r="AZ9" s="205"/>
+      <c r="BA9" s="206"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="54"/>
@@ -16052,61 +16101,61 @@
       <c r="BA29" s="52"/>
     </row>
     <row r="30" spans="1:53" ht="18" customHeight="1">
-      <c r="A30" s="244" t="s">
+      <c r="A30" s="204" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="245"/>
-      <c r="C30" s="245"/>
-      <c r="D30" s="245"/>
-      <c r="E30" s="245"/>
-      <c r="F30" s="245"/>
-      <c r="G30" s="245"/>
-      <c r="H30" s="245"/>
-      <c r="I30" s="245"/>
-      <c r="J30" s="245"/>
-      <c r="K30" s="245"/>
-      <c r="L30" s="245"/>
-      <c r="M30" s="245"/>
-      <c r="N30" s="245"/>
-      <c r="O30" s="245"/>
-      <c r="P30" s="245"/>
-      <c r="Q30" s="245"/>
-      <c r="R30" s="245"/>
-      <c r="S30" s="245"/>
-      <c r="T30" s="245"/>
-      <c r="U30" s="245"/>
-      <c r="V30" s="245"/>
-      <c r="W30" s="245"/>
-      <c r="X30" s="245"/>
-      <c r="Y30" s="245"/>
-      <c r="Z30" s="245"/>
-      <c r="AA30" s="245"/>
-      <c r="AB30" s="245"/>
-      <c r="AC30" s="245"/>
-      <c r="AD30" s="245"/>
-      <c r="AE30" s="245"/>
-      <c r="AF30" s="245"/>
-      <c r="AG30" s="245"/>
-      <c r="AH30" s="245"/>
-      <c r="AI30" s="245"/>
-      <c r="AJ30" s="245"/>
-      <c r="AK30" s="245"/>
-      <c r="AL30" s="245"/>
-      <c r="AM30" s="245"/>
-      <c r="AN30" s="245"/>
-      <c r="AO30" s="245"/>
-      <c r="AP30" s="245"/>
-      <c r="AQ30" s="245"/>
-      <c r="AR30" s="245"/>
-      <c r="AS30" s="245"/>
-      <c r="AT30" s="245"/>
-      <c r="AU30" s="245"/>
-      <c r="AV30" s="245"/>
-      <c r="AW30" s="245"/>
-      <c r="AX30" s="245"/>
-      <c r="AY30" s="245"/>
-      <c r="AZ30" s="245"/>
-      <c r="BA30" s="246"/>
+      <c r="B30" s="205"/>
+      <c r="C30" s="205"/>
+      <c r="D30" s="205"/>
+      <c r="E30" s="205"/>
+      <c r="F30" s="205"/>
+      <c r="G30" s="205"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="205"/>
+      <c r="L30" s="205"/>
+      <c r="M30" s="205"/>
+      <c r="N30" s="205"/>
+      <c r="O30" s="205"/>
+      <c r="P30" s="205"/>
+      <c r="Q30" s="205"/>
+      <c r="R30" s="205"/>
+      <c r="S30" s="205"/>
+      <c r="T30" s="205"/>
+      <c r="U30" s="205"/>
+      <c r="V30" s="205"/>
+      <c r="W30" s="205"/>
+      <c r="X30" s="205"/>
+      <c r="Y30" s="205"/>
+      <c r="Z30" s="205"/>
+      <c r="AA30" s="205"/>
+      <c r="AB30" s="205"/>
+      <c r="AC30" s="205"/>
+      <c r="AD30" s="205"/>
+      <c r="AE30" s="205"/>
+      <c r="AF30" s="205"/>
+      <c r="AG30" s="205"/>
+      <c r="AH30" s="205"/>
+      <c r="AI30" s="205"/>
+      <c r="AJ30" s="205"/>
+      <c r="AK30" s="205"/>
+      <c r="AL30" s="205"/>
+      <c r="AM30" s="205"/>
+      <c r="AN30" s="205"/>
+      <c r="AO30" s="205"/>
+      <c r="AP30" s="205"/>
+      <c r="AQ30" s="205"/>
+      <c r="AR30" s="205"/>
+      <c r="AS30" s="205"/>
+      <c r="AT30" s="205"/>
+      <c r="AU30" s="205"/>
+      <c r="AV30" s="205"/>
+      <c r="AW30" s="205"/>
+      <c r="AX30" s="205"/>
+      <c r="AY30" s="205"/>
+      <c r="AZ30" s="205"/>
+      <c r="BA30" s="206"/>
     </row>
     <row r="31" spans="1:53" ht="21.95" customHeight="1">
       <c r="A31" s="56"/>
@@ -16429,61 +16478,61 @@
       <c r="BA38" s="52"/>
     </row>
     <row r="39" spans="1:53" ht="18" customHeight="1">
-      <c r="A39" s="244" t="s">
+      <c r="A39" s="204" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="245"/>
-      <c r="C39" s="245"/>
-      <c r="D39" s="245"/>
-      <c r="E39" s="245"/>
-      <c r="F39" s="245"/>
-      <c r="G39" s="245"/>
-      <c r="H39" s="245"/>
-      <c r="I39" s="245"/>
-      <c r="J39" s="245"/>
-      <c r="K39" s="245"/>
-      <c r="L39" s="245"/>
-      <c r="M39" s="245"/>
-      <c r="N39" s="245"/>
-      <c r="O39" s="245"/>
-      <c r="P39" s="245"/>
-      <c r="Q39" s="245"/>
-      <c r="R39" s="245"/>
-      <c r="S39" s="245"/>
-      <c r="T39" s="245"/>
-      <c r="U39" s="245"/>
-      <c r="V39" s="245"/>
-      <c r="W39" s="245"/>
-      <c r="X39" s="245"/>
-      <c r="Y39" s="245"/>
-      <c r="Z39" s="245"/>
-      <c r="AA39" s="245"/>
-      <c r="AB39" s="245"/>
-      <c r="AC39" s="245"/>
-      <c r="AD39" s="245"/>
-      <c r="AE39" s="245"/>
-      <c r="AF39" s="245"/>
-      <c r="AG39" s="245"/>
-      <c r="AH39" s="245"/>
-      <c r="AI39" s="245"/>
-      <c r="AJ39" s="245"/>
-      <c r="AK39" s="245"/>
-      <c r="AL39" s="245"/>
-      <c r="AM39" s="245"/>
-      <c r="AN39" s="245"/>
-      <c r="AO39" s="245"/>
-      <c r="AP39" s="245"/>
-      <c r="AQ39" s="245"/>
-      <c r="AR39" s="245"/>
-      <c r="AS39" s="245"/>
-      <c r="AT39" s="245"/>
-      <c r="AU39" s="245"/>
-      <c r="AV39" s="245"/>
-      <c r="AW39" s="245"/>
-      <c r="AX39" s="245"/>
-      <c r="AY39" s="245"/>
-      <c r="AZ39" s="245"/>
-      <c r="BA39" s="245"/>
+      <c r="B39" s="205"/>
+      <c r="C39" s="205"/>
+      <c r="D39" s="205"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="205"/>
+      <c r="G39" s="205"/>
+      <c r="H39" s="205"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="205"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="205"/>
+      <c r="M39" s="205"/>
+      <c r="N39" s="205"/>
+      <c r="O39" s="205"/>
+      <c r="P39" s="205"/>
+      <c r="Q39" s="205"/>
+      <c r="R39" s="205"/>
+      <c r="S39" s="205"/>
+      <c r="T39" s="205"/>
+      <c r="U39" s="205"/>
+      <c r="V39" s="205"/>
+      <c r="W39" s="205"/>
+      <c r="X39" s="205"/>
+      <c r="Y39" s="205"/>
+      <c r="Z39" s="205"/>
+      <c r="AA39" s="205"/>
+      <c r="AB39" s="205"/>
+      <c r="AC39" s="205"/>
+      <c r="AD39" s="205"/>
+      <c r="AE39" s="205"/>
+      <c r="AF39" s="205"/>
+      <c r="AG39" s="205"/>
+      <c r="AH39" s="205"/>
+      <c r="AI39" s="205"/>
+      <c r="AJ39" s="205"/>
+      <c r="AK39" s="205"/>
+      <c r="AL39" s="205"/>
+      <c r="AM39" s="205"/>
+      <c r="AN39" s="205"/>
+      <c r="AO39" s="205"/>
+      <c r="AP39" s="205"/>
+      <c r="AQ39" s="205"/>
+      <c r="AR39" s="205"/>
+      <c r="AS39" s="205"/>
+      <c r="AT39" s="205"/>
+      <c r="AU39" s="205"/>
+      <c r="AV39" s="205"/>
+      <c r="AW39" s="205"/>
+      <c r="AX39" s="205"/>
+      <c r="AY39" s="205"/>
+      <c r="AZ39" s="205"/>
+      <c r="BA39" s="205"/>
     </row>
     <row r="40" spans="1:53" ht="21.95" customHeight="1">
       <c r="A40" s="56"/>

--- a/プロジェクト型演習_成果物_TasBo_コメント閲覧.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_コメント閲覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\TasBoドキュメント\コメント閲覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED1362-C597-46DF-9F1E-E7C2ACD9D8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950CDA40-D9C1-48BC-B079-3A162C0312D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="11" r:id="rId1"/>
@@ -553,39 +553,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザはタスク一覧画面を表示する。
-2.ユーザは対象タスクの「コメント閲覧」欄にある「コメント」リンクをクリックする。
-3.システムは対象タスクに投稿されたコメントを取得する。
-4.システムはコメント一覧画面を表示する。
-5.システムは各コメントについて以下の項目を一覧表示する。
-　・選択（ラジオボタン）
-　・コメント投稿者
-　・コメント
-　・コメント投稿日時
-6.ユーザはコメント内容を閲覧する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1. 対象タスクが削除されている場合（基本フロー3から分岐）
-a. システムは対象タスクが存在しないことを検出する。
-b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
-c. システムはタスク一覧画面を表示する。
-d. ユースケースを終了する。
-A2. 対象タスクにコメントが存在しない場合（基本フロー3から分岐）
-a. システムはコメントが存在しないことを検出する。
-b. システムはコメント一覧画面を表示する。
-c. システムは「コメントが投稿されていません」とメッセージを表示する。
-d. ユーザはコメント未投稿であることを確認する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>E1. データベース接続エラーまたはコメント取得処理中にシステムエラーが発生した場合
-a. システムエラーが発生する。
-b. システムはエラーメッセージを表示する。
-c. システムは処理を終了する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>・コメント一覧画面が表示されていること
 ・対象タスクのコメント情報を確認できること
 ・各コメントについて以下の情報を確認できること
@@ -602,6 +569,50 @@
 　　・コメント
 　　・コメント投稿日時
 ・ラジオボタンはコメントを選択するための項目であり、一度に1件のみ選択可能とする。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザは対象タスクの「コメント閲覧」欄にある「コメント」リンクをクリックする。
+2.システムは対象タスクに投稿されたコメントを取得する。
+3.システムはコメント一覧画面を表示する。
+4.システムは各コメントについて以下の項目を一覧表示する。
+　・選択（ラジオボタン）
+　・コメント投稿者
+　・コメント
+　・コメント投稿日時
+5.ユーザはコメント内容を閲覧する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1. 対象タスクが削除されている場合（基本フロー2から分岐）
+a. システムは対象タスクが存在しないことを検出する。
+b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
+c. システムはタスク一覧画面を表示する。
+d. ユースケースを終了する。
+A2. 対象タスクにコメントが存在しない場合（基本フロー2から分岐）
+a. システムはコメントが存在しないことを検出する。
+b. システムはコメント一覧画面を表示する。
+c. システムは「コメントが投稿されていません」とメッセージを表示する。
+d. ユーザはコメント未投稿であることを確認する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1. データベース接続エラーまたはコメント取得処理中にシステムエラーが発生した場合
+a. システムエラーが発生する。
+b. システムは「エラーが発生しました」とエラーメッセージを表示する。
+c. システムはタスク一覧画面へ遷移する。</t>
+    <rPh sb="73" eb="75">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>センイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1960,6 +1971,84 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1978,156 +2067,174 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2155,33 +2262,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2191,49 +2271,130 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2242,87 +2403,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="60" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2352,75 +2432,6 @@
     </xf>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3501,85 +3512,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
       <c r="P2" s="65"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
       <c r="P3" s="65"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="109"/>
-      <c r="N4" s="109"/>
-      <c r="O4" s="109"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
       <c r="P4" s="65"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
       <c r="P5" s="65"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109"/>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="88"/>
       <c r="P6" s="65"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3599,46 +3610,46 @@
       <c r="P7" s="65"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="112" t="s">
+      <c r="E8" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="109"/>
-      <c r="G8" s="109"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="105" t="s">
+      <c r="G13" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="107"/>
-      <c r="I13" s="113">
+      <c r="H13" s="86"/>
+      <c r="I13" s="92">
         <v>46198</v>
       </c>
-      <c r="J13" s="106"/>
-      <c r="K13" s="107"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="86"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="105"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="107"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="86"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="105"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="107"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="86"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="64"/>
@@ -3647,13 +3658,13 @@
       <c r="J16" s="64"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="108" t="s">
+      <c r="G17" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="109"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="88"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4668,218 +4679,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="214" t="s">
+      <c r="A1" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="98" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="98" t="s">
+      <c r="E1" s="117"/>
+      <c r="F1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="117"/>
       <c r="H1" s="73" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="215" t="s">
+      <c r="J1" s="83" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="100" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="101"/>
-      <c r="F2" s="100" t="s">
+      <c r="E2" s="131"/>
+      <c r="F2" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="216">
+      <c r="G2" s="131"/>
+      <c r="H2" s="134">
         <v>46195</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="109" t="s">
         <v>90</v>
       </c>
-      <c r="J2" s="86"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="87"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="88"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="217" t="s">
+      <c r="A5" s="115" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="218"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="219" t="s">
+      <c r="B5" s="116"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="218"/>
-      <c r="F5" s="218"/>
-      <c r="G5" s="218"/>
-      <c r="H5" s="218"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="220"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="119"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="222"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="224" t="s">
+      <c r="B6" s="94"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="104" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="222"/>
-      <c r="F6" s="222"/>
-      <c r="G6" s="222"/>
-      <c r="H6" s="222"/>
-      <c r="I6" s="222"/>
-      <c r="J6" s="225"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="95"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="221" t="s">
+      <c r="A7" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="222"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="224" t="s">
+      <c r="B7" s="94"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="222"/>
-      <c r="I7" s="222"/>
-      <c r="J7" s="225"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="221" t="s">
+      <c r="A8" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="222"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="226" t="s">
+      <c r="B8" s="94"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="222"/>
-      <c r="F8" s="222"/>
-      <c r="G8" s="222"/>
-      <c r="H8" s="222"/>
-      <c r="I8" s="222"/>
-      <c r="J8" s="225"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="148.5" customHeight="1">
-      <c r="A9" s="227" t="s">
+      <c r="A9" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="228" t="s">
+      <c r="B9" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="223"/>
-      <c r="D9" s="226" t="s">
+      <c r="C9" s="97"/>
+      <c r="D9" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="95"/>
+    </row>
+    <row r="10" spans="1:10" ht="156.75" customHeight="1">
+      <c r="A10" s="106"/>
+      <c r="B10" s="108" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="97"/>
+      <c r="D10" s="93" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="95"/>
+    </row>
+    <row r="11" spans="1:10" ht="61.5" customHeight="1">
+      <c r="A11" s="107"/>
+      <c r="B11" s="108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="97"/>
+      <c r="D11" s="93" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="95"/>
+    </row>
+    <row r="12" spans="1:10" ht="92.25" customHeight="1">
+      <c r="A12" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="94"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="93" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="225"/>
-    </row>
-    <row r="10" spans="1:10" ht="156.75" customHeight="1">
-      <c r="A10" s="229"/>
-      <c r="B10" s="228" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="223"/>
-      <c r="D10" s="226" t="s">
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="95"/>
+    </row>
+    <row r="13" spans="1:10" ht="113.25" customHeight="1" thickBot="1">
+      <c r="A13" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="99"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="222"/>
-      <c r="F10" s="222"/>
-      <c r="G10" s="222"/>
-      <c r="H10" s="222"/>
-      <c r="I10" s="222"/>
-      <c r="J10" s="225"/>
-    </row>
-    <row r="11" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A11" s="230"/>
-      <c r="B11" s="228" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="223"/>
-      <c r="D11" s="226" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="222"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="222"/>
-      <c r="H11" s="222"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="225"/>
-    </row>
-    <row r="12" spans="1:10" ht="92.25" customHeight="1">
-      <c r="A12" s="221" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="222"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="226" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="225"/>
-    </row>
-    <row r="13" spans="1:10" ht="113.25" customHeight="1" thickBot="1">
-      <c r="A13" s="231" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="232"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="235"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="236"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5870,21 +5881,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -5897,6 +5893,21 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5915,19 +5926,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="130"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="151"/>
+      <c r="F1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="130"/>
+      <c r="G1" s="151"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -5939,40 +5950,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="117"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="138"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="118"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="139"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="119"/>
+      <c r="A4" s="147"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="140"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="5"/>
@@ -7329,19 +7340,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="98" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="98" t="s">
+      <c r="E1" s="117"/>
+      <c r="F1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="117"/>
       <c r="H1" s="72" t="s">
         <v>5</v>
       </c>
@@ -7353,48 +7364,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="100" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="101"/>
-      <c r="F2" s="100" t="s">
+      <c r="E2" s="131"/>
+      <c r="F2" s="130" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="104">
+      <c r="G2" s="131"/>
+      <c r="H2" s="157">
         <v>46196</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="86"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="87"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="113"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="88"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="76"/>
@@ -8841,19 +8852,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="130"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="151"/>
+      <c r="F1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="130"/>
+      <c r="G1" s="151"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -8865,190 +8876,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131" t="s">
+      <c r="E2" s="153"/>
+      <c r="F2" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="143">
+      <c r="G2" s="153"/>
+      <c r="H2" s="175">
         <v>46198</v>
       </c>
-      <c r="I2" s="114" t="s">
+      <c r="I2" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="117"/>
+      <c r="J2" s="138"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="118"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="139"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="123"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="118"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="139"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="176" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="146" t="s">
+      <c r="B5" s="177"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="178" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="179"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="137"/>
+      <c r="B6" s="159"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
+      <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="139"/>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="141"/>
+      <c r="A7" s="171"/>
+      <c r="B7" s="172"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="172"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="173"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="123"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="142"/>
+      <c r="A8" s="144"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="174"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="123"/>
-      <c r="B9" s="124"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="142"/>
+      <c r="A9" s="144"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="174"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="123"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="142"/>
+      <c r="A10" s="144"/>
+      <c r="B10" s="145"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="174"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="142"/>
+      <c r="A11" s="144"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="174"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="123"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="142"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="174"/>
     </row>
     <row r="13" spans="1:10" ht="54" customHeight="1">
-      <c r="A13" s="123"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="142"/>
+      <c r="A13" s="144"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="174"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="135" t="s">
+      <c r="A14" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="137"/>
+      <c r="B14" s="159"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="148" t="s">
+      <c r="B15" s="159"/>
+      <c r="C15" s="162"/>
+      <c r="D15" s="161" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="138"/>
+      <c r="E15" s="159"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="159"/>
+      <c r="H15" s="162"/>
       <c r="I15" s="11" t="s">
         <v>24</v>
       </c>
@@ -9057,11 +9068,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="136"/>
-      <c r="C16" s="138"/>
+      <c r="B16" s="159"/>
+      <c r="C16" s="162"/>
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
@@ -9074,18 +9085,18 @@
       <c r="G16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="149" t="s">
+      <c r="H16" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="136"/>
-      <c r="J16" s="137"/>
+      <c r="I16" s="159"/>
+      <c r="J16" s="160"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="150">
+      <c r="A17" s="163">
         <v>1</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="159"/>
+      <c r="C17" s="162"/>
       <c r="D17" s="13" t="s">
         <v>98</v>
       </c>
@@ -9098,16 +9109,16 @@
       <c r="G17" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="148"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="137"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="159"/>
+      <c r="J17" s="160"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="150">
+      <c r="A18" s="163">
         <v>2</v>
       </c>
-      <c r="B18" s="136"/>
-      <c r="C18" s="138"/>
+      <c r="B18" s="159"/>
+      <c r="C18" s="162"/>
       <c r="D18" s="13" t="s">
         <v>94</v>
       </c>
@@ -9118,37 +9129,37 @@
       <c r="G18" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="148"/>
-      <c r="I18" s="136"/>
-      <c r="J18" s="137"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="159"/>
+      <c r="J18" s="160"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="135" t="s">
+      <c r="A19" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="137"/>
+      <c r="B19" s="159"/>
+      <c r="C19" s="159"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="159"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="160"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="148" t="s">
+      <c r="B20" s="159"/>
+      <c r="C20" s="162"/>
+      <c r="D20" s="161" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="136"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="138"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="159"/>
+      <c r="H20" s="162"/>
       <c r="I20" s="11" t="s">
         <v>24</v>
       </c>
@@ -9157,11 +9168,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="135" t="s">
+      <c r="A21" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="136"/>
-      <c r="C21" s="138"/>
+      <c r="B21" s="159"/>
+      <c r="C21" s="162"/>
       <c r="D21" s="11" t="s">
         <v>26</v>
       </c>
@@ -9174,18 +9185,18 @@
       <c r="G21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="149" t="s">
+      <c r="H21" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="136"/>
-      <c r="J21" s="137"/>
+      <c r="I21" s="159"/>
+      <c r="J21" s="160"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="150">
+      <c r="A22" s="163">
         <v>3</v>
       </c>
-      <c r="B22" s="136"/>
-      <c r="C22" s="138"/>
+      <c r="B22" s="159"/>
+      <c r="C22" s="162"/>
       <c r="D22" s="13" t="s">
         <v>95</v>
       </c>
@@ -9196,9 +9207,9 @@
       <c r="G22" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H22" s="148"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="137"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="159"/>
+      <c r="J22" s="160"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="67"/>
@@ -9213,32 +9224,32 @@
       <c r="J23" s="71"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="135" t="s">
+      <c r="A24" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="136"/>
-      <c r="C24" s="136"/>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="136"/>
-      <c r="G24" s="136"/>
-      <c r="H24" s="136"/>
-      <c r="I24" s="136"/>
-      <c r="J24" s="137"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="159"/>
+      <c r="H24" s="159"/>
+      <c r="I24" s="159"/>
+      <c r="J24" s="160"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="135" t="s">
+      <c r="A25" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="136"/>
-      <c r="C25" s="138"/>
-      <c r="D25" s="148" t="s">
+      <c r="B25" s="159"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="161" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="136"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="136"/>
-      <c r="H25" s="138"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="162"/>
       <c r="I25" s="11" t="s">
         <v>24</v>
       </c>
@@ -9247,11 +9258,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="135" t="s">
+      <c r="A26" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="136"/>
-      <c r="C26" s="138"/>
+      <c r="B26" s="159"/>
+      <c r="C26" s="162"/>
       <c r="D26" s="11" t="s">
         <v>26</v>
       </c>
@@ -9264,18 +9275,18 @@
       <c r="G26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="149" t="s">
+      <c r="H26" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="136"/>
-      <c r="J26" s="137"/>
+      <c r="I26" s="159"/>
+      <c r="J26" s="160"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="150">
+      <c r="A27" s="163">
         <v>4</v>
       </c>
-      <c r="B27" s="136"/>
-      <c r="C27" s="138"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="162"/>
       <c r="D27" s="13" t="s">
         <v>97</v>
       </c>
@@ -9286,21 +9297,21 @@
       <c r="G27" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="148"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="137"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="159"/>
+      <c r="J27" s="160"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A28" s="151"/>
-      <c r="B28" s="152"/>
-      <c r="C28" s="153"/>
+      <c r="A28" s="164"/>
+      <c r="B28" s="165"/>
+      <c r="C28" s="166"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
-      <c r="H28" s="154"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="156"/>
+      <c r="H28" s="167"/>
+      <c r="I28" s="168"/>
+      <c r="J28" s="169"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10281,13 +10292,21 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A16:C16"/>
@@ -10303,21 +10322,13 @@
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10340,19 +10351,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="130"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="151"/>
+      <c r="F1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="130"/>
+      <c r="G1" s="151"/>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
@@ -10364,190 +10375,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131" t="s">
+      <c r="E2" s="153"/>
+      <c r="F2" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="143">
+      <c r="G2" s="153"/>
+      <c r="H2" s="175">
         <v>46189</v>
       </c>
-      <c r="I2" s="114" t="s">
+      <c r="I2" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="117"/>
+      <c r="J2" s="138"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="118"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="139"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="123"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="118"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="139"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="176" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="146" t="s">
+      <c r="B5" s="177"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="178" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="147"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="179"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="137"/>
+      <c r="B6" s="159"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
+      <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="139"/>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="141"/>
+      <c r="A7" s="171"/>
+      <c r="B7" s="172"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="172"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="173"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="123"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="142"/>
+      <c r="A8" s="144"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="174"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="123"/>
-      <c r="B9" s="124"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="142"/>
+      <c r="A9" s="144"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="174"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="123"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="142"/>
+      <c r="A10" s="144"/>
+      <c r="B10" s="145"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="174"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="123"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="142"/>
+      <c r="A11" s="144"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="174"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="123"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="142"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="174"/>
     </row>
     <row r="13" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A13" s="123"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="142"/>
+      <c r="A13" s="144"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="174"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="135" t="s">
+      <c r="A14" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="137"/>
+      <c r="B14" s="159"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="148" t="s">
+      <c r="B15" s="159"/>
+      <c r="C15" s="162"/>
+      <c r="D15" s="161" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="138"/>
+      <c r="E15" s="159"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="159"/>
+      <c r="H15" s="162"/>
       <c r="I15" s="11" t="s">
         <v>24</v>
       </c>
@@ -10556,11 +10567,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="136"/>
-      <c r="C16" s="138"/>
+      <c r="B16" s="159"/>
+      <c r="C16" s="162"/>
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
@@ -10573,18 +10584,18 @@
       <c r="G16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="149" t="s">
+      <c r="H16" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="136"/>
-      <c r="J16" s="137"/>
+      <c r="I16" s="159"/>
+      <c r="J16" s="160"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="150">
+      <c r="A17" s="163">
         <v>1</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="159"/>
+      <c r="C17" s="162"/>
       <c r="D17" s="13" t="s">
         <v>95</v>
       </c>
@@ -10595,49 +10606,49 @@
       <c r="G17" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="148"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="137"/>
+      <c r="H17" s="161"/>
+      <c r="I17" s="159"/>
+      <c r="J17" s="160"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="150"/>
-      <c r="B18" s="136"/>
-      <c r="C18" s="138"/>
+      <c r="A18" s="163"/>
+      <c r="B18" s="159"/>
+      <c r="C18" s="162"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="136"/>
-      <c r="J18" s="137"/>
+      <c r="H18" s="161"/>
+      <c r="I18" s="159"/>
+      <c r="J18" s="160"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="135" t="s">
+      <c r="A19" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="137"/>
+      <c r="B19" s="159"/>
+      <c r="C19" s="159"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="159"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="160"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="148" t="s">
+      <c r="B20" s="159"/>
+      <c r="C20" s="162"/>
+      <c r="D20" s="161" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="136"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="138"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="159"/>
+      <c r="H20" s="162"/>
       <c r="I20" s="11" t="s">
         <v>24</v>
       </c>
@@ -10646,11 +10657,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="135" t="s">
+      <c r="A21" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="136"/>
-      <c r="C21" s="138"/>
+      <c r="B21" s="159"/>
+      <c r="C21" s="162"/>
       <c r="D21" s="11" t="s">
         <v>26</v>
       </c>
@@ -10663,18 +10674,18 @@
       <c r="G21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="149" t="s">
+      <c r="H21" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="136"/>
-      <c r="J21" s="137"/>
+      <c r="I21" s="159"/>
+      <c r="J21" s="160"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="151">
+      <c r="A22" s="164">
         <v>2</v>
       </c>
-      <c r="B22" s="157"/>
-      <c r="C22" s="158"/>
+      <c r="B22" s="180"/>
+      <c r="C22" s="181"/>
       <c r="D22" s="15" t="s">
         <v>97</v>
       </c>
@@ -10685,9 +10696,9 @@
       <c r="G22" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="H22" s="154"/>
-      <c r="I22" s="157"/>
-      <c r="J22" s="159"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="180"/>
+      <c r="J22" s="182"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11668,6 +11679,19 @@
     <row r="999" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11683,19 +11707,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D20:H20"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11715,182 +11726,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="189" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="129" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="129" t="s">
+      <c r="H1" s="177"/>
+      <c r="I1" s="177"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="129" t="s">
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="129" t="s">
+      <c r="P1" s="151"/>
+      <c r="Q1" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="130"/>
-      <c r="S1" s="129" t="s">
+      <c r="R1" s="151"/>
+      <c r="S1" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="147"/>
+      <c r="T1" s="179"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="131" t="s">
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="131" t="s">
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="131" t="s">
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="187"/>
+      <c r="P2" s="153"/>
+      <c r="Q2" s="152" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="132"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="141"/>
+      <c r="R2" s="153"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="173"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="125"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="125"/>
-      <c r="Q3" s="133"/>
-      <c r="R3" s="125"/>
-      <c r="S3" s="133"/>
-      <c r="T3" s="142"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="154"/>
+      <c r="P3" s="146"/>
+      <c r="Q3" s="154"/>
+      <c r="R3" s="146"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="174"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="134"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="134"/>
-      <c r="R4" s="128"/>
-      <c r="S4" s="134"/>
-      <c r="T4" s="170"/>
+      <c r="A4" s="147"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="155"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="155"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="155"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="155"/>
+      <c r="R4" s="149"/>
+      <c r="S4" s="155"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="176" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145"/>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="145"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145"/>
-      <c r="T5" s="147"/>
+      <c r="B5" s="177"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="177"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="177"/>
+      <c r="O5" s="177"/>
+      <c r="P5" s="177"/>
+      <c r="Q5" s="177"/>
+      <c r="R5" s="177"/>
+      <c r="S5" s="177"/>
+      <c r="T5" s="179"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="136"/>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="137"/>
+      <c r="B6" s="159"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="159"/>
+      <c r="I6" s="159"/>
+      <c r="J6" s="159"/>
+      <c r="K6" s="159"/>
+      <c r="L6" s="159"/>
+      <c r="M6" s="159"/>
+      <c r="N6" s="159"/>
+      <c r="O6" s="159"/>
+      <c r="P6" s="159"/>
+      <c r="Q6" s="159"/>
+      <c r="R6" s="159"/>
+      <c r="S6" s="159"/>
+      <c r="T6" s="160"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="135" t="s">
+      <c r="A7" s="170" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="136"/>
-      <c r="P7" s="136"/>
-      <c r="Q7" s="136"/>
-      <c r="R7" s="136"/>
-      <c r="S7" s="136"/>
-      <c r="T7" s="137"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="159"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="159"/>
+      <c r="K7" s="159"/>
+      <c r="L7" s="159"/>
+      <c r="M7" s="159"/>
+      <c r="N7" s="159"/>
+      <c r="O7" s="159"/>
+      <c r="P7" s="159"/>
+      <c r="Q7" s="159"/>
+      <c r="R7" s="159"/>
+      <c r="S7" s="159"/>
+      <c r="T7" s="160"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="5"/>
@@ -12089,37 +12100,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="168" t="s">
+      <c r="B15" s="162"/>
+      <c r="C15" s="193" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="138"/>
-      <c r="E15" s="149" t="s">
+      <c r="D15" s="162"/>
+      <c r="E15" s="158" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="138"/>
-      <c r="G15" s="149" t="s">
+      <c r="F15" s="162"/>
+      <c r="G15" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="136"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="149" t="s">
+      <c r="H15" s="159"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="158" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="138"/>
-      <c r="L15" s="149" t="s">
+      <c r="K15" s="162"/>
+      <c r="L15" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="136"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="149" t="s">
+      <c r="M15" s="159"/>
+      <c r="N15" s="162"/>
+      <c r="O15" s="158" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="136"/>
-      <c r="Q15" s="138"/>
+      <c r="P15" s="159"/>
+      <c r="Q15" s="162"/>
       <c r="R15" s="11" t="s">
         <v>46</v>
       </c>
@@ -12131,25 +12142,25 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="160">
+      <c r="A16" s="191">
         <v>1</v>
       </c>
-      <c r="B16" s="138"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="161"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="167"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="167"/>
-      <c r="K16" s="138"/>
-      <c r="L16" s="164"/>
-      <c r="M16" s="136"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="164"/>
-      <c r="P16" s="136"/>
-      <c r="Q16" s="138"/>
+      <c r="B16" s="162"/>
+      <c r="C16" s="192"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="192"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="159"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="162"/>
+      <c r="L16" s="185"/>
+      <c r="M16" s="159"/>
+      <c r="N16" s="162"/>
+      <c r="O16" s="185"/>
+      <c r="P16" s="159"/>
+      <c r="Q16" s="162"/>
       <c r="R16" s="29"/>
       <c r="S16" s="29"/>
       <c r="T16" s="30"/>
@@ -12161,25 +12172,25 @@
       <c r="Z16" s="31"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="160">
+      <c r="A17" s="191">
         <v>2</v>
       </c>
-      <c r="B17" s="138"/>
-      <c r="C17" s="161"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="161"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="167"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="167"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="164"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="164"/>
-      <c r="P17" s="136"/>
-      <c r="Q17" s="138"/>
+      <c r="B17" s="162"/>
+      <c r="C17" s="192"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="192"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="183"/>
+      <c r="H17" s="159"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="183"/>
+      <c r="K17" s="162"/>
+      <c r="L17" s="185"/>
+      <c r="M17" s="159"/>
+      <c r="N17" s="162"/>
+      <c r="O17" s="185"/>
+      <c r="P17" s="159"/>
+      <c r="Q17" s="162"/>
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
       <c r="T17" s="30"/>
@@ -12191,23 +12202,23 @@
       <c r="Z17" s="31"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="160"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="161"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="161"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="167"/>
-      <c r="H18" s="136"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="167"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="164"/>
-      <c r="M18" s="136"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="164"/>
-      <c r="P18" s="136"/>
-      <c r="Q18" s="138"/>
+      <c r="A18" s="191"/>
+      <c r="B18" s="162"/>
+      <c r="C18" s="192"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="192"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="159"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="183"/>
+      <c r="K18" s="162"/>
+      <c r="L18" s="185"/>
+      <c r="M18" s="159"/>
+      <c r="N18" s="162"/>
+      <c r="O18" s="185"/>
+      <c r="P18" s="159"/>
+      <c r="Q18" s="162"/>
       <c r="R18" s="29"/>
       <c r="S18" s="29"/>
       <c r="T18" s="30"/>
@@ -12219,23 +12230,23 @@
       <c r="Z18" s="31"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="160"/>
-      <c r="B19" s="138"/>
-      <c r="C19" s="161"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="161"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="167"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="167"/>
-      <c r="K19" s="138"/>
-      <c r="L19" s="164"/>
-      <c r="M19" s="136"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="164"/>
-      <c r="P19" s="136"/>
-      <c r="Q19" s="138"/>
+      <c r="A19" s="191"/>
+      <c r="B19" s="162"/>
+      <c r="C19" s="192"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="192"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="183"/>
+      <c r="K19" s="162"/>
+      <c r="L19" s="185"/>
+      <c r="M19" s="159"/>
+      <c r="N19" s="162"/>
+      <c r="O19" s="185"/>
+      <c r="P19" s="159"/>
+      <c r="Q19" s="162"/>
       <c r="R19" s="29"/>
       <c r="S19" s="29"/>
       <c r="T19" s="30"/>
@@ -12247,23 +12258,23 @@
       <c r="Z19" s="31"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="160"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="167"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="138"/>
-      <c r="O20" s="164"/>
-      <c r="P20" s="136"/>
-      <c r="Q20" s="138"/>
+      <c r="A20" s="191"/>
+      <c r="B20" s="162"/>
+      <c r="C20" s="192"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="192"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="159"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="183"/>
+      <c r="K20" s="162"/>
+      <c r="L20" s="185"/>
+      <c r="M20" s="159"/>
+      <c r="N20" s="162"/>
+      <c r="O20" s="185"/>
+      <c r="P20" s="159"/>
+      <c r="Q20" s="162"/>
       <c r="R20" s="29"/>
       <c r="S20" s="29"/>
       <c r="T20" s="30"/>
@@ -12275,23 +12286,23 @@
       <c r="Z20" s="31"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="160"/>
-      <c r="B21" s="138"/>
-      <c r="C21" s="161"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="161"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="167"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="167"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="136"/>
-      <c r="N21" s="138"/>
-      <c r="O21" s="164"/>
-      <c r="P21" s="136"/>
-      <c r="Q21" s="138"/>
+      <c r="A21" s="191"/>
+      <c r="B21" s="162"/>
+      <c r="C21" s="192"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="192"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="159"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="183"/>
+      <c r="K21" s="162"/>
+      <c r="L21" s="185"/>
+      <c r="M21" s="159"/>
+      <c r="N21" s="162"/>
+      <c r="O21" s="185"/>
+      <c r="P21" s="159"/>
+      <c r="Q21" s="162"/>
       <c r="R21" s="29"/>
       <c r="S21" s="29"/>
       <c r="T21" s="30"/>
@@ -12303,23 +12314,23 @@
       <c r="Z21" s="31"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="160"/>
-      <c r="B22" s="138"/>
-      <c r="C22" s="161"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="167"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="136"/>
-      <c r="N22" s="138"/>
-      <c r="O22" s="164"/>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="138"/>
+      <c r="A22" s="191"/>
+      <c r="B22" s="162"/>
+      <c r="C22" s="192"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="192"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="159"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="183"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="185"/>
+      <c r="M22" s="159"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="185"/>
+      <c r="P22" s="159"/>
+      <c r="Q22" s="162"/>
       <c r="R22" s="29"/>
       <c r="S22" s="29"/>
       <c r="T22" s="30"/>
@@ -12331,23 +12342,23 @@
       <c r="Z22" s="31"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="160"/>
-      <c r="B23" s="138"/>
-      <c r="C23" s="161"/>
-      <c r="D23" s="138"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="167"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="138"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="138"/>
-      <c r="L23" s="164"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="138"/>
-      <c r="O23" s="164"/>
-      <c r="P23" s="136"/>
-      <c r="Q23" s="138"/>
+      <c r="A23" s="191"/>
+      <c r="B23" s="162"/>
+      <c r="C23" s="192"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="192"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="159"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="183"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="185"/>
+      <c r="M23" s="159"/>
+      <c r="N23" s="162"/>
+      <c r="O23" s="185"/>
+      <c r="P23" s="159"/>
+      <c r="Q23" s="162"/>
       <c r="R23" s="29"/>
       <c r="S23" s="29"/>
       <c r="T23" s="30"/>
@@ -12359,23 +12370,23 @@
       <c r="Z23" s="31"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="138"/>
-      <c r="C24" s="161"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="167"/>
-      <c r="H24" s="136"/>
-      <c r="I24" s="138"/>
-      <c r="J24" s="167"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="164"/>
-      <c r="M24" s="136"/>
-      <c r="N24" s="138"/>
-      <c r="O24" s="164"/>
-      <c r="P24" s="136"/>
-      <c r="Q24" s="138"/>
+      <c r="A24" s="191"/>
+      <c r="B24" s="162"/>
+      <c r="C24" s="192"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="192"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="159"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="183"/>
+      <c r="K24" s="162"/>
+      <c r="L24" s="185"/>
+      <c r="M24" s="159"/>
+      <c r="N24" s="162"/>
+      <c r="O24" s="185"/>
+      <c r="P24" s="159"/>
+      <c r="Q24" s="162"/>
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
       <c r="T24" s="30"/>
@@ -12387,23 +12398,23 @@
       <c r="Z24" s="31"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="160"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="161"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="167"/>
-      <c r="H25" s="136"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="167"/>
-      <c r="K25" s="138"/>
-      <c r="L25" s="164"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="138"/>
-      <c r="O25" s="164"/>
-      <c r="P25" s="136"/>
-      <c r="Q25" s="138"/>
+      <c r="A25" s="191"/>
+      <c r="B25" s="162"/>
+      <c r="C25" s="192"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="192"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="183"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="183"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="185"/>
+      <c r="M25" s="159"/>
+      <c r="N25" s="162"/>
+      <c r="O25" s="185"/>
+      <c r="P25" s="159"/>
+      <c r="Q25" s="162"/>
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
       <c r="T25" s="30"/>
@@ -12415,23 +12426,23 @@
       <c r="Z25" s="31"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="160"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="161"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="161"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="167"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="138"/>
-      <c r="J26" s="167"/>
-      <c r="K26" s="138"/>
-      <c r="L26" s="164"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="138"/>
-      <c r="O26" s="164"/>
-      <c r="P26" s="136"/>
-      <c r="Q26" s="138"/>
+      <c r="A26" s="191"/>
+      <c r="B26" s="162"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="192"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="183"/>
+      <c r="H26" s="159"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="183"/>
+      <c r="K26" s="162"/>
+      <c r="L26" s="185"/>
+      <c r="M26" s="159"/>
+      <c r="N26" s="162"/>
+      <c r="O26" s="185"/>
+      <c r="P26" s="159"/>
+      <c r="Q26" s="162"/>
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
       <c r="T26" s="30"/>
@@ -12443,23 +12454,23 @@
       <c r="Z26" s="31"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="160"/>
-      <c r="B27" s="138"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="161"/>
-      <c r="F27" s="138"/>
-      <c r="G27" s="167"/>
-      <c r="H27" s="136"/>
-      <c r="I27" s="138"/>
-      <c r="J27" s="167"/>
-      <c r="K27" s="138"/>
-      <c r="L27" s="164"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="138"/>
-      <c r="O27" s="164"/>
-      <c r="P27" s="136"/>
-      <c r="Q27" s="138"/>
+      <c r="A27" s="191"/>
+      <c r="B27" s="162"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="192"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="159"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="183"/>
+      <c r="K27" s="162"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="159"/>
+      <c r="N27" s="162"/>
+      <c r="O27" s="185"/>
+      <c r="P27" s="159"/>
+      <c r="Q27" s="162"/>
       <c r="R27" s="29"/>
       <c r="S27" s="29"/>
       <c r="T27" s="30"/>
@@ -12471,23 +12482,23 @@
       <c r="Z27" s="31"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="160"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="161"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="161"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="167"/>
-      <c r="H28" s="136"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="167"/>
-      <c r="K28" s="138"/>
-      <c r="L28" s="164"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="138"/>
-      <c r="O28" s="164"/>
-      <c r="P28" s="136"/>
-      <c r="Q28" s="138"/>
+      <c r="A28" s="191"/>
+      <c r="B28" s="162"/>
+      <c r="C28" s="192"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="192"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="183"/>
+      <c r="H28" s="159"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="183"/>
+      <c r="K28" s="162"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="159"/>
+      <c r="N28" s="162"/>
+      <c r="O28" s="185"/>
+      <c r="P28" s="159"/>
+      <c r="Q28" s="162"/>
       <c r="R28" s="29"/>
       <c r="S28" s="29"/>
       <c r="T28" s="30"/>
@@ -12499,23 +12510,23 @@
       <c r="Z28" s="31"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="160"/>
-      <c r="B29" s="138"/>
-      <c r="C29" s="161"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="167"/>
-      <c r="H29" s="136"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="167"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="164"/>
-      <c r="M29" s="136"/>
-      <c r="N29" s="138"/>
-      <c r="O29" s="164"/>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="138"/>
+      <c r="A29" s="191"/>
+      <c r="B29" s="162"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="159"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="183"/>
+      <c r="K29" s="162"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="159"/>
+      <c r="N29" s="162"/>
+      <c r="O29" s="185"/>
+      <c r="P29" s="159"/>
+      <c r="Q29" s="162"/>
       <c r="R29" s="29"/>
       <c r="S29" s="29"/>
       <c r="T29" s="30"/>
@@ -12527,23 +12538,23 @@
       <c r="Z29" s="31"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="160"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="161"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="167"/>
-      <c r="H30" s="136"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="136"/>
-      <c r="N30" s="138"/>
-      <c r="O30" s="164"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="138"/>
+      <c r="A30" s="191"/>
+      <c r="B30" s="162"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="192"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="183"/>
+      <c r="H30" s="159"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="183"/>
+      <c r="K30" s="162"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="159"/>
+      <c r="N30" s="162"/>
+      <c r="O30" s="185"/>
+      <c r="P30" s="159"/>
+      <c r="Q30" s="162"/>
       <c r="R30" s="29"/>
       <c r="S30" s="29"/>
       <c r="T30" s="30"/>
@@ -12555,23 +12566,23 @@
       <c r="Z30" s="31"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="162"/>
-      <c r="B31" s="158"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="158"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="172"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="172"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="165"/>
-      <c r="M31" s="157"/>
-      <c r="N31" s="158"/>
-      <c r="O31" s="165"/>
-      <c r="P31" s="157"/>
-      <c r="Q31" s="158"/>
+      <c r="A31" s="194"/>
+      <c r="B31" s="181"/>
+      <c r="C31" s="195"/>
+      <c r="D31" s="181"/>
+      <c r="E31" s="195"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="184"/>
+      <c r="H31" s="180"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="184"/>
+      <c r="K31" s="181"/>
+      <c r="L31" s="186"/>
+      <c r="M31" s="180"/>
+      <c r="N31" s="181"/>
+      <c r="O31" s="186"/>
+      <c r="P31" s="180"/>
+      <c r="Q31" s="181"/>
       <c r="R31" s="32"/>
       <c r="S31" s="32"/>
       <c r="T31" s="33"/>
@@ -13569,62 +13580,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13649,62 +13660,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13727,70 +13738,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="205" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="194" t="s">
+      <c r="B1" s="205"/>
+      <c r="C1" s="206" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="195"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="197" t="s">
+      <c r="D1" s="207"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="209" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
-      <c r="I1" s="198"/>
-      <c r="J1" s="198"/>
-      <c r="K1" s="198"/>
-      <c r="L1" s="198"/>
-      <c r="M1" s="199"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="211"/>
       <c r="N1" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="197" t="s">
+      <c r="O1" s="209" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="199"/>
+      <c r="P1" s="211"/>
       <c r="Q1" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="R1" s="197" t="s">
+      <c r="R1" s="209" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="199"/>
+      <c r="S1" s="211"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="193"/>
-      <c r="B2" s="193"/>
-      <c r="C2" s="194" t="s">
+      <c r="A2" s="205"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="206" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="195"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="198"/>
-      <c r="M2" s="199"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="210"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="210"/>
+      <c r="M2" s="211"/>
       <c r="N2" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="O2" s="200">
+      <c r="O2" s="212">
         <v>46190</v>
       </c>
-      <c r="P2" s="201"/>
+      <c r="P2" s="213"/>
       <c r="Q2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="R2" s="202" t="s">
+      <c r="R2" s="214" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="203"/>
+      <c r="S2" s="215"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="36"/>
@@ -13820,1046 +13831,1234 @@
       <c r="B4" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="185" t="s">
+      <c r="C4" s="196" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="185" t="s">
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="197"/>
+      <c r="G4" s="198"/>
+      <c r="H4" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="185" t="s">
+      <c r="I4" s="197"/>
+      <c r="J4" s="197"/>
+      <c r="K4" s="197"/>
+      <c r="L4" s="197"/>
+      <c r="M4" s="198"/>
+      <c r="N4" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="186"/>
-      <c r="P4" s="187"/>
+      <c r="O4" s="197"/>
+      <c r="P4" s="198"/>
       <c r="Q4" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="185" t="s">
+      <c r="R4" s="196" t="s">
         <v>72</v>
       </c>
-      <c r="S4" s="187"/>
+      <c r="S4" s="198"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="40">
         <v>1</v>
       </c>
       <c r="B5" s="40"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="181"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="188"/>
-      <c r="O5" s="189"/>
-      <c r="P5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="199"/>
+      <c r="M5" s="199"/>
+      <c r="N5" s="200"/>
+      <c r="O5" s="201"/>
+      <c r="P5" s="202"/>
       <c r="Q5" s="41"/>
-      <c r="R5" s="191"/>
-      <c r="S5" s="192"/>
+      <c r="R5" s="203"/>
+      <c r="S5" s="204"/>
     </row>
     <row r="6" spans="1:19" ht="33" customHeight="1">
       <c r="A6" s="42"/>
       <c r="B6" s="42"/>
-      <c r="C6" s="181"/>
-      <c r="D6" s="181"/>
-      <c r="E6" s="181"/>
-      <c r="F6" s="181"/>
-      <c r="G6" s="181"/>
-      <c r="H6" s="181"/>
-      <c r="I6" s="181"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="181"/>
-      <c r="L6" s="181"/>
-      <c r="M6" s="181"/>
-      <c r="N6" s="182"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="184"/>
+      <c r="C6" s="199"/>
+      <c r="D6" s="199"/>
+      <c r="E6" s="199"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="199"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="199"/>
+      <c r="J6" s="199"/>
+      <c r="K6" s="199"/>
+      <c r="L6" s="199"/>
+      <c r="M6" s="199"/>
+      <c r="N6" s="221"/>
+      <c r="O6" s="222"/>
+      <c r="P6" s="223"/>
       <c r="Q6" s="41"/>
-      <c r="R6" s="180"/>
-      <c r="S6" s="180"/>
+      <c r="R6" s="220"/>
+      <c r="S6" s="220"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="42"/>
       <c r="B7" s="42"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="181"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="181"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
-      <c r="L7" s="173"/>
-      <c r="M7" s="173"/>
-      <c r="N7" s="182"/>
-      <c r="O7" s="178"/>
-      <c r="P7" s="179"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
+      <c r="L7" s="216"/>
+      <c r="M7" s="216"/>
+      <c r="N7" s="221"/>
+      <c r="O7" s="218"/>
+      <c r="P7" s="219"/>
       <c r="Q7" s="41"/>
-      <c r="R7" s="180"/>
-      <c r="S7" s="180"/>
+      <c r="R7" s="220"/>
+      <c r="S7" s="220"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="42"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="173"/>
-      <c r="D8" s="173"/>
-      <c r="E8" s="173"/>
-      <c r="F8" s="173"/>
-      <c r="G8" s="173"/>
-      <c r="H8" s="173"/>
-      <c r="I8" s="173"/>
-      <c r="J8" s="173"/>
-      <c r="K8" s="173"/>
-      <c r="L8" s="173"/>
-      <c r="M8" s="173"/>
-      <c r="N8" s="177"/>
-      <c r="O8" s="178"/>
-      <c r="P8" s="179"/>
+      <c r="C8" s="216"/>
+      <c r="D8" s="216"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+      <c r="I8" s="216"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="216"/>
+      <c r="L8" s="216"/>
+      <c r="M8" s="216"/>
+      <c r="N8" s="217"/>
+      <c r="O8" s="218"/>
+      <c r="P8" s="219"/>
       <c r="Q8" s="43"/>
-      <c r="R8" s="180"/>
-      <c r="S8" s="180"/>
+      <c r="R8" s="220"/>
+      <c r="S8" s="220"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="42"/>
       <c r="B9" s="42"/>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="173"/>
-      <c r="H9" s="173"/>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
-      <c r="L9" s="173"/>
-      <c r="M9" s="173"/>
-      <c r="N9" s="177"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="179"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
+      <c r="M9" s="216"/>
+      <c r="N9" s="217"/>
+      <c r="O9" s="218"/>
+      <c r="P9" s="219"/>
       <c r="Q9" s="42"/>
-      <c r="R9" s="180"/>
-      <c r="S9" s="180"/>
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="42"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="173"/>
-      <c r="D10" s="173"/>
-      <c r="E10" s="173"/>
-      <c r="F10" s="173"/>
-      <c r="G10" s="173"/>
-      <c r="H10" s="174"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="175"/>
-      <c r="K10" s="175"/>
-      <c r="L10" s="175"/>
-      <c r="M10" s="176"/>
-      <c r="N10" s="177"/>
-      <c r="O10" s="178"/>
-      <c r="P10" s="179"/>
+      <c r="C10" s="216"/>
+      <c r="D10" s="216"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="216"/>
+      <c r="H10" s="224"/>
+      <c r="I10" s="225"/>
+      <c r="J10" s="225"/>
+      <c r="K10" s="225"/>
+      <c r="L10" s="225"/>
+      <c r="M10" s="226"/>
+      <c r="N10" s="217"/>
+      <c r="O10" s="218"/>
+      <c r="P10" s="219"/>
       <c r="Q10" s="43"/>
-      <c r="R10" s="180"/>
-      <c r="S10" s="180"/>
+      <c r="R10" s="220"/>
+      <c r="S10" s="220"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="42"/>
       <c r="B11" s="42"/>
-      <c r="C11" s="173"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="173"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="174"/>
-      <c r="I11" s="175"/>
-      <c r="J11" s="175"/>
-      <c r="K11" s="175"/>
-      <c r="L11" s="175"/>
-      <c r="M11" s="176"/>
-      <c r="N11" s="177"/>
-      <c r="O11" s="178"/>
-      <c r="P11" s="179"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="224"/>
+      <c r="I11" s="225"/>
+      <c r="J11" s="225"/>
+      <c r="K11" s="225"/>
+      <c r="L11" s="225"/>
+      <c r="M11" s="226"/>
+      <c r="N11" s="217"/>
+      <c r="O11" s="218"/>
+      <c r="P11" s="219"/>
       <c r="Q11" s="42"/>
-      <c r="R11" s="180"/>
-      <c r="S11" s="180"/>
+      <c r="R11" s="220"/>
+      <c r="S11" s="220"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="42"/>
       <c r="B12" s="42"/>
-      <c r="C12" s="173"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="173"/>
-      <c r="F12" s="173"/>
-      <c r="G12" s="173"/>
-      <c r="H12" s="174"/>
-      <c r="I12" s="175"/>
-      <c r="J12" s="175"/>
-      <c r="K12" s="175"/>
-      <c r="L12" s="175"/>
-      <c r="M12" s="176"/>
-      <c r="N12" s="177"/>
-      <c r="O12" s="178"/>
-      <c r="P12" s="179"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="216"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="224"/>
+      <c r="I12" s="225"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
+      <c r="M12" s="226"/>
+      <c r="N12" s="217"/>
+      <c r="O12" s="218"/>
+      <c r="P12" s="219"/>
       <c r="Q12" s="42"/>
-      <c r="R12" s="180"/>
-      <c r="S12" s="180"/>
+      <c r="R12" s="220"/>
+      <c r="S12" s="220"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="42"/>
       <c r="B13" s="42"/>
-      <c r="C13" s="173"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="173"/>
-      <c r="F13" s="173"/>
-      <c r="G13" s="173"/>
-      <c r="H13" s="174"/>
-      <c r="I13" s="175"/>
-      <c r="J13" s="175"/>
-      <c r="K13" s="175"/>
-      <c r="L13" s="175"/>
-      <c r="M13" s="176"/>
-      <c r="N13" s="177"/>
-      <c r="O13" s="178"/>
-      <c r="P13" s="179"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="216"/>
+      <c r="F13" s="216"/>
+      <c r="G13" s="216"/>
+      <c r="H13" s="224"/>
+      <c r="I13" s="225"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="225"/>
+      <c r="M13" s="226"/>
+      <c r="N13" s="217"/>
+      <c r="O13" s="218"/>
+      <c r="P13" s="219"/>
       <c r="Q13" s="42"/>
-      <c r="R13" s="180"/>
-      <c r="S13" s="180"/>
+      <c r="R13" s="220"/>
+      <c r="S13" s="220"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="42"/>
       <c r="B14" s="42"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="173"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="173"/>
-      <c r="H14" s="174"/>
-      <c r="I14" s="175"/>
-      <c r="J14" s="175"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="175"/>
-      <c r="M14" s="176"/>
-      <c r="N14" s="177"/>
-      <c r="O14" s="178"/>
-      <c r="P14" s="179"/>
+      <c r="C14" s="216"/>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
+      <c r="F14" s="216"/>
+      <c r="G14" s="216"/>
+      <c r="H14" s="224"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="225"/>
+      <c r="M14" s="226"/>
+      <c r="N14" s="217"/>
+      <c r="O14" s="218"/>
+      <c r="P14" s="219"/>
       <c r="Q14" s="42"/>
-      <c r="R14" s="180"/>
-      <c r="S14" s="180"/>
+      <c r="R14" s="220"/>
+      <c r="S14" s="220"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="42"/>
       <c r="B15" s="42"/>
-      <c r="C15" s="173"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="173"/>
-      <c r="F15" s="173"/>
-      <c r="G15" s="173"/>
-      <c r="H15" s="174"/>
-      <c r="I15" s="175"/>
-      <c r="J15" s="175"/>
-      <c r="K15" s="175"/>
-      <c r="L15" s="175"/>
-      <c r="M15" s="176"/>
-      <c r="N15" s="177"/>
-      <c r="O15" s="178"/>
-      <c r="P15" s="179"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
+      <c r="F15" s="216"/>
+      <c r="G15" s="216"/>
+      <c r="H15" s="224"/>
+      <c r="I15" s="225"/>
+      <c r="J15" s="225"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="225"/>
+      <c r="M15" s="226"/>
+      <c r="N15" s="217"/>
+      <c r="O15" s="218"/>
+      <c r="P15" s="219"/>
       <c r="Q15" s="42"/>
-      <c r="R15" s="180"/>
-      <c r="S15" s="180"/>
+      <c r="R15" s="220"/>
+      <c r="S15" s="220"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="42"/>
       <c r="B16" s="42"/>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="173"/>
-      <c r="F16" s="173"/>
-      <c r="G16" s="173"/>
-      <c r="H16" s="174"/>
-      <c r="I16" s="175"/>
-      <c r="J16" s="175"/>
-      <c r="K16" s="175"/>
-      <c r="L16" s="175"/>
-      <c r="M16" s="176"/>
-      <c r="N16" s="177"/>
-      <c r="O16" s="178"/>
-      <c r="P16" s="179"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="224"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
+      <c r="M16" s="226"/>
+      <c r="N16" s="217"/>
+      <c r="O16" s="218"/>
+      <c r="P16" s="219"/>
       <c r="Q16" s="42"/>
-      <c r="R16" s="180"/>
-      <c r="S16" s="180"/>
+      <c r="R16" s="220"/>
+      <c r="S16" s="220"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="42"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="175"/>
-      <c r="J17" s="175"/>
-      <c r="K17" s="175"/>
-      <c r="L17" s="175"/>
-      <c r="M17" s="176"/>
-      <c r="N17" s="177"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="179"/>
+      <c r="C17" s="216"/>
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="216"/>
+      <c r="H17" s="224"/>
+      <c r="I17" s="225"/>
+      <c r="J17" s="225"/>
+      <c r="K17" s="225"/>
+      <c r="L17" s="225"/>
+      <c r="M17" s="226"/>
+      <c r="N17" s="217"/>
+      <c r="O17" s="218"/>
+      <c r="P17" s="219"/>
       <c r="Q17" s="42"/>
-      <c r="R17" s="180"/>
-      <c r="S17" s="180"/>
+      <c r="R17" s="220"/>
+      <c r="S17" s="220"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="42"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="173"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="173"/>
-      <c r="H18" s="174"/>
-      <c r="I18" s="175"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="175"/>
-      <c r="L18" s="175"/>
-      <c r="M18" s="176"/>
-      <c r="N18" s="177"/>
-      <c r="O18" s="178"/>
-      <c r="P18" s="179"/>
+      <c r="C18" s="216"/>
+      <c r="D18" s="216"/>
+      <c r="E18" s="216"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="216"/>
+      <c r="H18" s="224"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
+      <c r="M18" s="226"/>
+      <c r="N18" s="217"/>
+      <c r="O18" s="218"/>
+      <c r="P18" s="219"/>
       <c r="Q18" s="42"/>
-      <c r="R18" s="180"/>
-      <c r="S18" s="180"/>
+      <c r="R18" s="220"/>
+      <c r="S18" s="220"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="42"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="173"/>
-      <c r="H19" s="174"/>
-      <c r="I19" s="175"/>
-      <c r="J19" s="175"/>
-      <c r="K19" s="175"/>
-      <c r="L19" s="175"/>
-      <c r="M19" s="176"/>
-      <c r="N19" s="177"/>
-      <c r="O19" s="178"/>
-      <c r="P19" s="179"/>
+      <c r="C19" s="216"/>
+      <c r="D19" s="216"/>
+      <c r="E19" s="216"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="216"/>
+      <c r="H19" s="224"/>
+      <c r="I19" s="225"/>
+      <c r="J19" s="225"/>
+      <c r="K19" s="225"/>
+      <c r="L19" s="225"/>
+      <c r="M19" s="226"/>
+      <c r="N19" s="217"/>
+      <c r="O19" s="218"/>
+      <c r="P19" s="219"/>
       <c r="Q19" s="42"/>
-      <c r="R19" s="180"/>
-      <c r="S19" s="180"/>
+      <c r="R19" s="220"/>
+      <c r="S19" s="220"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="42"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="174"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="175"/>
-      <c r="L20" s="175"/>
-      <c r="M20" s="176"/>
-      <c r="N20" s="177"/>
-      <c r="O20" s="178"/>
-      <c r="P20" s="179"/>
+      <c r="C20" s="216"/>
+      <c r="D20" s="216"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="216"/>
+      <c r="H20" s="224"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="226"/>
+      <c r="N20" s="217"/>
+      <c r="O20" s="218"/>
+      <c r="P20" s="219"/>
       <c r="Q20" s="42"/>
-      <c r="R20" s="180"/>
-      <c r="S20" s="180"/>
+      <c r="R20" s="220"/>
+      <c r="S20" s="220"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="42"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="173"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="174"/>
-      <c r="I21" s="175"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="175"/>
-      <c r="L21" s="175"/>
-      <c r="M21" s="176"/>
-      <c r="N21" s="177"/>
-      <c r="O21" s="178"/>
-      <c r="P21" s="179"/>
+      <c r="C21" s="216"/>
+      <c r="D21" s="216"/>
+      <c r="E21" s="216"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="216"/>
+      <c r="H21" s="224"/>
+      <c r="I21" s="225"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
+      <c r="M21" s="226"/>
+      <c r="N21" s="217"/>
+      <c r="O21" s="218"/>
+      <c r="P21" s="219"/>
       <c r="Q21" s="42"/>
-      <c r="R21" s="180"/>
-      <c r="S21" s="180"/>
+      <c r="R21" s="220"/>
+      <c r="S21" s="220"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="173"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="174"/>
-      <c r="I22" s="175"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="175"/>
-      <c r="L22" s="175"/>
-      <c r="M22" s="176"/>
-      <c r="N22" s="177"/>
-      <c r="O22" s="178"/>
-      <c r="P22" s="179"/>
+      <c r="C22" s="216"/>
+      <c r="D22" s="216"/>
+      <c r="E22" s="216"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="216"/>
+      <c r="H22" s="224"/>
+      <c r="I22" s="225"/>
+      <c r="J22" s="225"/>
+      <c r="K22" s="225"/>
+      <c r="L22" s="225"/>
+      <c r="M22" s="226"/>
+      <c r="N22" s="217"/>
+      <c r="O22" s="218"/>
+      <c r="P22" s="219"/>
       <c r="Q22" s="42"/>
-      <c r="R22" s="180"/>
-      <c r="S22" s="180"/>
+      <c r="R22" s="220"/>
+      <c r="S22" s="220"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="42"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="173"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="173"/>
-      <c r="F23" s="173"/>
-      <c r="G23" s="173"/>
-      <c r="H23" s="174"/>
-      <c r="I23" s="175"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="175"/>
-      <c r="L23" s="175"/>
-      <c r="M23" s="176"/>
-      <c r="N23" s="177"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="179"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="216"/>
+      <c r="H23" s="224"/>
+      <c r="I23" s="225"/>
+      <c r="J23" s="225"/>
+      <c r="K23" s="225"/>
+      <c r="L23" s="225"/>
+      <c r="M23" s="226"/>
+      <c r="N23" s="217"/>
+      <c r="O23" s="218"/>
+      <c r="P23" s="219"/>
       <c r="Q23" s="42"/>
-      <c r="R23" s="180"/>
-      <c r="S23" s="180"/>
+      <c r="R23" s="220"/>
+      <c r="S23" s="220"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="42"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="173"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="173"/>
-      <c r="G24" s="173"/>
-      <c r="H24" s="174"/>
-      <c r="I24" s="175"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="175"/>
-      <c r="L24" s="175"/>
-      <c r="M24" s="176"/>
-      <c r="N24" s="177"/>
-      <c r="O24" s="178"/>
-      <c r="P24" s="179"/>
+      <c r="C24" s="216"/>
+      <c r="D24" s="216"/>
+      <c r="E24" s="216"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="216"/>
+      <c r="H24" s="224"/>
+      <c r="I24" s="225"/>
+      <c r="J24" s="225"/>
+      <c r="K24" s="225"/>
+      <c r="L24" s="225"/>
+      <c r="M24" s="226"/>
+      <c r="N24" s="217"/>
+      <c r="O24" s="218"/>
+      <c r="P24" s="219"/>
       <c r="Q24" s="42"/>
-      <c r="R24" s="180"/>
-      <c r="S24" s="180"/>
+      <c r="R24" s="220"/>
+      <c r="S24" s="220"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="42"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="173"/>
-      <c r="D25" s="173"/>
-      <c r="E25" s="173"/>
-      <c r="F25" s="173"/>
-      <c r="G25" s="173"/>
-      <c r="H25" s="174"/>
-      <c r="I25" s="175"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="175"/>
-      <c r="L25" s="175"/>
-      <c r="M25" s="176"/>
-      <c r="N25" s="177"/>
-      <c r="O25" s="178"/>
-      <c r="P25" s="179"/>
+      <c r="C25" s="216"/>
+      <c r="D25" s="216"/>
+      <c r="E25" s="216"/>
+      <c r="F25" s="216"/>
+      <c r="G25" s="216"/>
+      <c r="H25" s="224"/>
+      <c r="I25" s="225"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="225"/>
+      <c r="M25" s="226"/>
+      <c r="N25" s="217"/>
+      <c r="O25" s="218"/>
+      <c r="P25" s="219"/>
       <c r="Q25" s="42"/>
-      <c r="R25" s="180"/>
-      <c r="S25" s="180"/>
+      <c r="R25" s="220"/>
+      <c r="S25" s="220"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="173"/>
-      <c r="D26" s="173"/>
-      <c r="E26" s="173"/>
-      <c r="F26" s="173"/>
-      <c r="G26" s="173"/>
-      <c r="H26" s="174"/>
-      <c r="I26" s="175"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="175"/>
-      <c r="L26" s="175"/>
-      <c r="M26" s="176"/>
-      <c r="N26" s="177"/>
-      <c r="O26" s="178"/>
-      <c r="P26" s="179"/>
+      <c r="C26" s="216"/>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="216"/>
+      <c r="H26" s="224"/>
+      <c r="I26" s="225"/>
+      <c r="J26" s="225"/>
+      <c r="K26" s="225"/>
+      <c r="L26" s="225"/>
+      <c r="M26" s="226"/>
+      <c r="N26" s="217"/>
+      <c r="O26" s="218"/>
+      <c r="P26" s="219"/>
       <c r="Q26" s="42"/>
-      <c r="R26" s="180"/>
-      <c r="S26" s="180"/>
+      <c r="R26" s="220"/>
+      <c r="S26" s="220"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="173"/>
-      <c r="D27" s="173"/>
-      <c r="E27" s="173"/>
-      <c r="F27" s="173"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="174"/>
-      <c r="I27" s="175"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="175"/>
-      <c r="L27" s="175"/>
-      <c r="M27" s="176"/>
-      <c r="N27" s="177"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="179"/>
+      <c r="C27" s="216"/>
+      <c r="D27" s="216"/>
+      <c r="E27" s="216"/>
+      <c r="F27" s="216"/>
+      <c r="G27" s="216"/>
+      <c r="H27" s="224"/>
+      <c r="I27" s="225"/>
+      <c r="J27" s="225"/>
+      <c r="K27" s="225"/>
+      <c r="L27" s="225"/>
+      <c r="M27" s="226"/>
+      <c r="N27" s="217"/>
+      <c r="O27" s="218"/>
+      <c r="P27" s="219"/>
       <c r="Q27" s="42"/>
-      <c r="R27" s="180"/>
-      <c r="S27" s="180"/>
+      <c r="R27" s="220"/>
+      <c r="S27" s="220"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="42"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="173"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="173"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="175"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="175"/>
-      <c r="L28" s="175"/>
-      <c r="M28" s="176"/>
-      <c r="N28" s="177"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="179"/>
+      <c r="C28" s="216"/>
+      <c r="D28" s="216"/>
+      <c r="E28" s="216"/>
+      <c r="F28" s="216"/>
+      <c r="G28" s="216"/>
+      <c r="H28" s="224"/>
+      <c r="I28" s="225"/>
+      <c r="J28" s="225"/>
+      <c r="K28" s="225"/>
+      <c r="L28" s="225"/>
+      <c r="M28" s="226"/>
+      <c r="N28" s="217"/>
+      <c r="O28" s="218"/>
+      <c r="P28" s="219"/>
       <c r="Q28" s="42"/>
-      <c r="R28" s="180"/>
-      <c r="S28" s="180"/>
+      <c r="R28" s="220"/>
+      <c r="S28" s="220"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="42"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="175"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="175"/>
-      <c r="L29" s="175"/>
-      <c r="M29" s="176"/>
-      <c r="N29" s="177"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179"/>
+      <c r="C29" s="216"/>
+      <c r="D29" s="216"/>
+      <c r="E29" s="216"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="216"/>
+      <c r="H29" s="224"/>
+      <c r="I29" s="225"/>
+      <c r="J29" s="225"/>
+      <c r="K29" s="225"/>
+      <c r="L29" s="225"/>
+      <c r="M29" s="226"/>
+      <c r="N29" s="217"/>
+      <c r="O29" s="218"/>
+      <c r="P29" s="219"/>
       <c r="Q29" s="42"/>
-      <c r="R29" s="180"/>
-      <c r="S29" s="180"/>
+      <c r="R29" s="220"/>
+      <c r="S29" s="220"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="42"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="173"/>
-      <c r="D30" s="173"/>
-      <c r="E30" s="173"/>
-      <c r="F30" s="173"/>
-      <c r="G30" s="173"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="175"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="175"/>
-      <c r="L30" s="175"/>
-      <c r="M30" s="176"/>
-      <c r="N30" s="177"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="179"/>
+      <c r="C30" s="216"/>
+      <c r="D30" s="216"/>
+      <c r="E30" s="216"/>
+      <c r="F30" s="216"/>
+      <c r="G30" s="216"/>
+      <c r="H30" s="224"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
+      <c r="M30" s="226"/>
+      <c r="N30" s="217"/>
+      <c r="O30" s="218"/>
+      <c r="P30" s="219"/>
       <c r="Q30" s="42"/>
-      <c r="R30" s="180"/>
-      <c r="S30" s="180"/>
+      <c r="R30" s="220"/>
+      <c r="S30" s="220"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="42"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="173"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="173"/>
-      <c r="G31" s="173"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
-      <c r="L31" s="175"/>
-      <c r="M31" s="176"/>
-      <c r="N31" s="177"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="179"/>
+      <c r="C31" s="216"/>
+      <c r="D31" s="216"/>
+      <c r="E31" s="216"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="216"/>
+      <c r="H31" s="224"/>
+      <c r="I31" s="225"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="226"/>
+      <c r="N31" s="217"/>
+      <c r="O31" s="218"/>
+      <c r="P31" s="219"/>
       <c r="Q31" s="42"/>
-      <c r="R31" s="180"/>
-      <c r="S31" s="180"/>
+      <c r="R31" s="220"/>
+      <c r="S31" s="220"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="42"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="173"/>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="173"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="175"/>
-      <c r="J32" s="175"/>
-      <c r="K32" s="175"/>
-      <c r="L32" s="175"/>
-      <c r="M32" s="176"/>
-      <c r="N32" s="177"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="179"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="225"/>
+      <c r="K32" s="225"/>
+      <c r="L32" s="225"/>
+      <c r="M32" s="226"/>
+      <c r="N32" s="217"/>
+      <c r="O32" s="218"/>
+      <c r="P32" s="219"/>
       <c r="Q32" s="42"/>
-      <c r="R32" s="180"/>
-      <c r="S32" s="180"/>
+      <c r="R32" s="220"/>
+      <c r="S32" s="220"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="42"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="173"/>
-      <c r="D33" s="173"/>
-      <c r="E33" s="173"/>
-      <c r="F33" s="173"/>
-      <c r="G33" s="173"/>
-      <c r="H33" s="174"/>
-      <c r="I33" s="175"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="175"/>
-      <c r="L33" s="175"/>
-      <c r="M33" s="176"/>
-      <c r="N33" s="177"/>
-      <c r="O33" s="178"/>
-      <c r="P33" s="179"/>
+      <c r="C33" s="216"/>
+      <c r="D33" s="216"/>
+      <c r="E33" s="216"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="216"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="225"/>
+      <c r="J33" s="225"/>
+      <c r="K33" s="225"/>
+      <c r="L33" s="225"/>
+      <c r="M33" s="226"/>
+      <c r="N33" s="217"/>
+      <c r="O33" s="218"/>
+      <c r="P33" s="219"/>
       <c r="Q33" s="42"/>
-      <c r="R33" s="180"/>
-      <c r="S33" s="180"/>
+      <c r="R33" s="220"/>
+      <c r="S33" s="220"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="42"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="173"/>
-      <c r="D34" s="173"/>
-      <c r="E34" s="173"/>
-      <c r="F34" s="173"/>
-      <c r="G34" s="173"/>
-      <c r="H34" s="174"/>
-      <c r="I34" s="175"/>
-      <c r="J34" s="175"/>
-      <c r="K34" s="175"/>
-      <c r="L34" s="175"/>
-      <c r="M34" s="176"/>
-      <c r="N34" s="177"/>
-      <c r="O34" s="178"/>
-      <c r="P34" s="179"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="225"/>
+      <c r="K34" s="225"/>
+      <c r="L34" s="225"/>
+      <c r="M34" s="226"/>
+      <c r="N34" s="217"/>
+      <c r="O34" s="218"/>
+      <c r="P34" s="219"/>
       <c r="Q34" s="42"/>
-      <c r="R34" s="180"/>
-      <c r="S34" s="180"/>
+      <c r="R34" s="220"/>
+      <c r="S34" s="220"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="42"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="173"/>
-      <c r="D35" s="173"/>
-      <c r="E35" s="173"/>
-      <c r="F35" s="173"/>
-      <c r="G35" s="173"/>
-      <c r="H35" s="174"/>
-      <c r="I35" s="175"/>
-      <c r="J35" s="175"/>
-      <c r="K35" s="175"/>
-      <c r="L35" s="175"/>
-      <c r="M35" s="176"/>
-      <c r="N35" s="177"/>
-      <c r="O35" s="178"/>
-      <c r="P35" s="179"/>
+      <c r="C35" s="216"/>
+      <c r="D35" s="216"/>
+      <c r="E35" s="216"/>
+      <c r="F35" s="216"/>
+      <c r="G35" s="216"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
+      <c r="M35" s="226"/>
+      <c r="N35" s="217"/>
+      <c r="O35" s="218"/>
+      <c r="P35" s="219"/>
       <c r="Q35" s="42"/>
-      <c r="R35" s="180"/>
-      <c r="S35" s="180"/>
+      <c r="R35" s="220"/>
+      <c r="S35" s="220"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="42"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="173"/>
-      <c r="D36" s="173"/>
-      <c r="E36" s="173"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="173"/>
-      <c r="H36" s="174"/>
-      <c r="I36" s="175"/>
-      <c r="J36" s="175"/>
-      <c r="K36" s="175"/>
-      <c r="L36" s="175"/>
-      <c r="M36" s="176"/>
-      <c r="N36" s="177"/>
-      <c r="O36" s="178"/>
-      <c r="P36" s="179"/>
+      <c r="C36" s="216"/>
+      <c r="D36" s="216"/>
+      <c r="E36" s="216"/>
+      <c r="F36" s="216"/>
+      <c r="G36" s="216"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="225"/>
+      <c r="J36" s="225"/>
+      <c r="K36" s="225"/>
+      <c r="L36" s="225"/>
+      <c r="M36" s="226"/>
+      <c r="N36" s="217"/>
+      <c r="O36" s="218"/>
+      <c r="P36" s="219"/>
       <c r="Q36" s="42"/>
-      <c r="R36" s="180"/>
-      <c r="S36" s="180"/>
+      <c r="R36" s="220"/>
+      <c r="S36" s="220"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="42"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="173"/>
-      <c r="D37" s="173"/>
-      <c r="E37" s="173"/>
-      <c r="F37" s="173"/>
-      <c r="G37" s="173"/>
-      <c r="H37" s="174"/>
-      <c r="I37" s="175"/>
-      <c r="J37" s="175"/>
-      <c r="K37" s="175"/>
-      <c r="L37" s="175"/>
-      <c r="M37" s="176"/>
-      <c r="N37" s="177"/>
-      <c r="O37" s="178"/>
-      <c r="P37" s="179"/>
+      <c r="C37" s="216"/>
+      <c r="D37" s="216"/>
+      <c r="E37" s="216"/>
+      <c r="F37" s="216"/>
+      <c r="G37" s="216"/>
+      <c r="H37" s="224"/>
+      <c r="I37" s="225"/>
+      <c r="J37" s="225"/>
+      <c r="K37" s="225"/>
+      <c r="L37" s="225"/>
+      <c r="M37" s="226"/>
+      <c r="N37" s="217"/>
+      <c r="O37" s="218"/>
+      <c r="P37" s="219"/>
       <c r="Q37" s="42"/>
-      <c r="R37" s="180"/>
-      <c r="S37" s="180"/>
+      <c r="R37" s="220"/>
+      <c r="S37" s="220"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="42"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="173"/>
-      <c r="D38" s="173"/>
-      <c r="E38" s="173"/>
-      <c r="F38" s="173"/>
-      <c r="G38" s="173"/>
-      <c r="H38" s="174"/>
-      <c r="I38" s="175"/>
-      <c r="J38" s="175"/>
-      <c r="K38" s="175"/>
-      <c r="L38" s="175"/>
-      <c r="M38" s="176"/>
-      <c r="N38" s="177"/>
-      <c r="O38" s="178"/>
-      <c r="P38" s="179"/>
+      <c r="C38" s="216"/>
+      <c r="D38" s="216"/>
+      <c r="E38" s="216"/>
+      <c r="F38" s="216"/>
+      <c r="G38" s="216"/>
+      <c r="H38" s="224"/>
+      <c r="I38" s="225"/>
+      <c r="J38" s="225"/>
+      <c r="K38" s="225"/>
+      <c r="L38" s="225"/>
+      <c r="M38" s="226"/>
+      <c r="N38" s="217"/>
+      <c r="O38" s="218"/>
+      <c r="P38" s="219"/>
       <c r="Q38" s="42"/>
-      <c r="R38" s="180"/>
-      <c r="S38" s="180"/>
+      <c r="R38" s="220"/>
+      <c r="S38" s="220"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="42"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="173"/>
-      <c r="D39" s="173"/>
-      <c r="E39" s="173"/>
-      <c r="F39" s="173"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="174"/>
-      <c r="I39" s="175"/>
-      <c r="J39" s="175"/>
-      <c r="K39" s="175"/>
-      <c r="L39" s="175"/>
-      <c r="M39" s="176"/>
-      <c r="N39" s="177"/>
-      <c r="O39" s="178"/>
-      <c r="P39" s="179"/>
+      <c r="C39" s="216"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="224"/>
+      <c r="I39" s="225"/>
+      <c r="J39" s="225"/>
+      <c r="K39" s="225"/>
+      <c r="L39" s="225"/>
+      <c r="M39" s="226"/>
+      <c r="N39" s="217"/>
+      <c r="O39" s="218"/>
+      <c r="P39" s="219"/>
       <c r="Q39" s="42"/>
-      <c r="R39" s="180"/>
-      <c r="S39" s="180"/>
+      <c r="R39" s="220"/>
+      <c r="S39" s="220"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="42"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="173"/>
-      <c r="G40" s="173"/>
-      <c r="H40" s="174"/>
-      <c r="I40" s="175"/>
-      <c r="J40" s="175"/>
-      <c r="K40" s="175"/>
-      <c r="L40" s="175"/>
-      <c r="M40" s="176"/>
-      <c r="N40" s="177"/>
-      <c r="O40" s="178"/>
-      <c r="P40" s="179"/>
+      <c r="C40" s="216"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="216"/>
+      <c r="H40" s="224"/>
+      <c r="I40" s="225"/>
+      <c r="J40" s="225"/>
+      <c r="K40" s="225"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="226"/>
+      <c r="N40" s="217"/>
+      <c r="O40" s="218"/>
+      <c r="P40" s="219"/>
       <c r="Q40" s="42"/>
-      <c r="R40" s="180"/>
-      <c r="S40" s="180"/>
+      <c r="R40" s="220"/>
+      <c r="S40" s="220"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="42"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="173"/>
-      <c r="D41" s="173"/>
-      <c r="E41" s="173"/>
-      <c r="F41" s="173"/>
-      <c r="G41" s="173"/>
-      <c r="H41" s="174"/>
-      <c r="I41" s="175"/>
-      <c r="J41" s="175"/>
-      <c r="K41" s="175"/>
-      <c r="L41" s="175"/>
-      <c r="M41" s="176"/>
-      <c r="N41" s="177"/>
-      <c r="O41" s="178"/>
-      <c r="P41" s="179"/>
+      <c r="C41" s="216"/>
+      <c r="D41" s="216"/>
+      <c r="E41" s="216"/>
+      <c r="F41" s="216"/>
+      <c r="G41" s="216"/>
+      <c r="H41" s="224"/>
+      <c r="I41" s="225"/>
+      <c r="J41" s="225"/>
+      <c r="K41" s="225"/>
+      <c r="L41" s="225"/>
+      <c r="M41" s="226"/>
+      <c r="N41" s="217"/>
+      <c r="O41" s="218"/>
+      <c r="P41" s="219"/>
       <c r="Q41" s="42"/>
-      <c r="R41" s="180"/>
-      <c r="S41" s="180"/>
+      <c r="R41" s="220"/>
+      <c r="S41" s="220"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="42"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="173"/>
-      <c r="D42" s="173"/>
-      <c r="E42" s="173"/>
-      <c r="F42" s="173"/>
-      <c r="G42" s="173"/>
-      <c r="H42" s="174"/>
-      <c r="I42" s="175"/>
-      <c r="J42" s="175"/>
-      <c r="K42" s="175"/>
-      <c r="L42" s="175"/>
-      <c r="M42" s="176"/>
-      <c r="N42" s="177"/>
-      <c r="O42" s="178"/>
-      <c r="P42" s="179"/>
+      <c r="C42" s="216"/>
+      <c r="D42" s="216"/>
+      <c r="E42" s="216"/>
+      <c r="F42" s="216"/>
+      <c r="G42" s="216"/>
+      <c r="H42" s="224"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="225"/>
+      <c r="K42" s="225"/>
+      <c r="L42" s="225"/>
+      <c r="M42" s="226"/>
+      <c r="N42" s="217"/>
+      <c r="O42" s="218"/>
+      <c r="P42" s="219"/>
       <c r="Q42" s="42"/>
-      <c r="R42" s="180"/>
-      <c r="S42" s="180"/>
+      <c r="R42" s="220"/>
+      <c r="S42" s="220"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="42"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="173"/>
-      <c r="D43" s="173"/>
-      <c r="E43" s="173"/>
-      <c r="F43" s="173"/>
-      <c r="G43" s="173"/>
-      <c r="H43" s="174"/>
-      <c r="I43" s="175"/>
-      <c r="J43" s="175"/>
-      <c r="K43" s="175"/>
-      <c r="L43" s="175"/>
-      <c r="M43" s="176"/>
-      <c r="N43" s="177"/>
-      <c r="O43" s="178"/>
-      <c r="P43" s="179"/>
+      <c r="C43" s="216"/>
+      <c r="D43" s="216"/>
+      <c r="E43" s="216"/>
+      <c r="F43" s="216"/>
+      <c r="G43" s="216"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="225"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="225"/>
+      <c r="M43" s="226"/>
+      <c r="N43" s="217"/>
+      <c r="O43" s="218"/>
+      <c r="P43" s="219"/>
       <c r="Q43" s="42"/>
-      <c r="R43" s="180"/>
-      <c r="S43" s="180"/>
+      <c r="R43" s="220"/>
+      <c r="S43" s="220"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="42"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="173"/>
-      <c r="D44" s="173"/>
-      <c r="E44" s="173"/>
-      <c r="F44" s="173"/>
-      <c r="G44" s="173"/>
-      <c r="H44" s="174"/>
-      <c r="I44" s="175"/>
-      <c r="J44" s="175"/>
-      <c r="K44" s="175"/>
-      <c r="L44" s="175"/>
-      <c r="M44" s="176"/>
-      <c r="N44" s="177"/>
-      <c r="O44" s="178"/>
-      <c r="P44" s="179"/>
+      <c r="C44" s="216"/>
+      <c r="D44" s="216"/>
+      <c r="E44" s="216"/>
+      <c r="F44" s="216"/>
+      <c r="G44" s="216"/>
+      <c r="H44" s="224"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="225"/>
+      <c r="K44" s="225"/>
+      <c r="L44" s="225"/>
+      <c r="M44" s="226"/>
+      <c r="N44" s="217"/>
+      <c r="O44" s="218"/>
+      <c r="P44" s="219"/>
       <c r="Q44" s="42"/>
-      <c r="R44" s="180"/>
-      <c r="S44" s="180"/>
+      <c r="R44" s="220"/>
+      <c r="S44" s="220"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="42"/>
       <c r="B45" s="42"/>
-      <c r="C45" s="173"/>
-      <c r="D45" s="173"/>
-      <c r="E45" s="173"/>
-      <c r="F45" s="173"/>
-      <c r="G45" s="173"/>
-      <c r="H45" s="174"/>
-      <c r="I45" s="175"/>
-      <c r="J45" s="175"/>
-      <c r="K45" s="175"/>
-      <c r="L45" s="175"/>
-      <c r="M45" s="176"/>
-      <c r="N45" s="177"/>
-      <c r="O45" s="178"/>
-      <c r="P45" s="179"/>
+      <c r="C45" s="216"/>
+      <c r="D45" s="216"/>
+      <c r="E45" s="216"/>
+      <c r="F45" s="216"/>
+      <c r="G45" s="216"/>
+      <c r="H45" s="224"/>
+      <c r="I45" s="225"/>
+      <c r="J45" s="225"/>
+      <c r="K45" s="225"/>
+      <c r="L45" s="225"/>
+      <c r="M45" s="226"/>
+      <c r="N45" s="217"/>
+      <c r="O45" s="218"/>
+      <c r="P45" s="219"/>
       <c r="Q45" s="42"/>
-      <c r="R45" s="180"/>
-      <c r="S45" s="180"/>
+      <c r="R45" s="220"/>
+      <c r="S45" s="220"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="42"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="173"/>
-      <c r="D46" s="173"/>
-      <c r="E46" s="173"/>
-      <c r="F46" s="173"/>
-      <c r="G46" s="173"/>
-      <c r="H46" s="174"/>
-      <c r="I46" s="175"/>
-      <c r="J46" s="175"/>
-      <c r="K46" s="175"/>
-      <c r="L46" s="175"/>
-      <c r="M46" s="176"/>
-      <c r="N46" s="177"/>
-      <c r="O46" s="178"/>
-      <c r="P46" s="179"/>
+      <c r="C46" s="216"/>
+      <c r="D46" s="216"/>
+      <c r="E46" s="216"/>
+      <c r="F46" s="216"/>
+      <c r="G46" s="216"/>
+      <c r="H46" s="224"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="225"/>
+      <c r="K46" s="225"/>
+      <c r="L46" s="225"/>
+      <c r="M46" s="226"/>
+      <c r="N46" s="217"/>
+      <c r="O46" s="218"/>
+      <c r="P46" s="219"/>
       <c r="Q46" s="42"/>
-      <c r="R46" s="180"/>
-      <c r="S46" s="180"/>
+      <c r="R46" s="220"/>
+      <c r="S46" s="220"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="42"/>
       <c r="B47" s="42"/>
-      <c r="C47" s="173"/>
-      <c r="D47" s="173"/>
-      <c r="E47" s="173"/>
-      <c r="F47" s="173"/>
-      <c r="G47" s="173"/>
-      <c r="H47" s="174"/>
-      <c r="I47" s="175"/>
-      <c r="J47" s="175"/>
-      <c r="K47" s="175"/>
-      <c r="L47" s="175"/>
-      <c r="M47" s="176"/>
-      <c r="N47" s="177"/>
-      <c r="O47" s="178"/>
-      <c r="P47" s="179"/>
+      <c r="C47" s="216"/>
+      <c r="D47" s="216"/>
+      <c r="E47" s="216"/>
+      <c r="F47" s="216"/>
+      <c r="G47" s="216"/>
+      <c r="H47" s="224"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="225"/>
+      <c r="K47" s="225"/>
+      <c r="L47" s="225"/>
+      <c r="M47" s="226"/>
+      <c r="N47" s="217"/>
+      <c r="O47" s="218"/>
+      <c r="P47" s="219"/>
       <c r="Q47" s="42"/>
-      <c r="R47" s="180"/>
-      <c r="S47" s="180"/>
+      <c r="R47" s="220"/>
+      <c r="S47" s="220"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="42"/>
       <c r="B48" s="42"/>
-      <c r="C48" s="173"/>
-      <c r="D48" s="173"/>
-      <c r="E48" s="173"/>
-      <c r="F48" s="173"/>
-      <c r="G48" s="173"/>
-      <c r="H48" s="174"/>
-      <c r="I48" s="175"/>
-      <c r="J48" s="175"/>
-      <c r="K48" s="175"/>
-      <c r="L48" s="175"/>
-      <c r="M48" s="176"/>
-      <c r="N48" s="177"/>
-      <c r="O48" s="178"/>
-      <c r="P48" s="179"/>
+      <c r="C48" s="216"/>
+      <c r="D48" s="216"/>
+      <c r="E48" s="216"/>
+      <c r="F48" s="216"/>
+      <c r="G48" s="216"/>
+      <c r="H48" s="224"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="225"/>
+      <c r="K48" s="225"/>
+      <c r="L48" s="225"/>
+      <c r="M48" s="226"/>
+      <c r="N48" s="217"/>
+      <c r="O48" s="218"/>
+      <c r="P48" s="219"/>
       <c r="Q48" s="42"/>
-      <c r="R48" s="180"/>
-      <c r="S48" s="180"/>
+      <c r="R48" s="220"/>
+      <c r="S48" s="220"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="42"/>
       <c r="B49" s="42"/>
-      <c r="C49" s="173"/>
-      <c r="D49" s="173"/>
-      <c r="E49" s="173"/>
-      <c r="F49" s="173"/>
-      <c r="G49" s="173"/>
-      <c r="H49" s="174"/>
-      <c r="I49" s="175"/>
-      <c r="J49" s="175"/>
-      <c r="K49" s="175"/>
-      <c r="L49" s="175"/>
-      <c r="M49" s="176"/>
-      <c r="N49" s="177"/>
-      <c r="O49" s="178"/>
-      <c r="P49" s="179"/>
+      <c r="C49" s="216"/>
+      <c r="D49" s="216"/>
+      <c r="E49" s="216"/>
+      <c r="F49" s="216"/>
+      <c r="G49" s="216"/>
+      <c r="H49" s="224"/>
+      <c r="I49" s="225"/>
+      <c r="J49" s="225"/>
+      <c r="K49" s="225"/>
+      <c r="L49" s="225"/>
+      <c r="M49" s="226"/>
+      <c r="N49" s="217"/>
+      <c r="O49" s="218"/>
+      <c r="P49" s="219"/>
       <c r="Q49" s="42"/>
-      <c r="R49" s="180"/>
-      <c r="S49" s="180"/>
+      <c r="R49" s="220"/>
+      <c r="S49" s="220"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="42"/>
       <c r="B50" s="42"/>
-      <c r="C50" s="173"/>
-      <c r="D50" s="173"/>
-      <c r="E50" s="173"/>
-      <c r="F50" s="173"/>
-      <c r="G50" s="173"/>
-      <c r="H50" s="174"/>
-      <c r="I50" s="175"/>
-      <c r="J50" s="175"/>
-      <c r="K50" s="175"/>
-      <c r="L50" s="175"/>
-      <c r="M50" s="176"/>
-      <c r="N50" s="177"/>
-      <c r="O50" s="178"/>
-      <c r="P50" s="179"/>
+      <c r="C50" s="216"/>
+      <c r="D50" s="216"/>
+      <c r="E50" s="216"/>
+      <c r="F50" s="216"/>
+      <c r="G50" s="216"/>
+      <c r="H50" s="224"/>
+      <c r="I50" s="225"/>
+      <c r="J50" s="225"/>
+      <c r="K50" s="225"/>
+      <c r="L50" s="225"/>
+      <c r="M50" s="226"/>
+      <c r="N50" s="217"/>
+      <c r="O50" s="218"/>
+      <c r="P50" s="219"/>
       <c r="Q50" s="42"/>
-      <c r="R50" s="180"/>
-      <c r="S50" s="180"/>
+      <c r="R50" s="220"/>
+      <c r="S50" s="220"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="42"/>
       <c r="B51" s="42"/>
-      <c r="C51" s="173"/>
-      <c r="D51" s="173"/>
-      <c r="E51" s="173"/>
-      <c r="F51" s="173"/>
-      <c r="G51" s="173"/>
-      <c r="H51" s="174"/>
-      <c r="I51" s="175"/>
-      <c r="J51" s="175"/>
-      <c r="K51" s="175"/>
-      <c r="L51" s="175"/>
-      <c r="M51" s="176"/>
-      <c r="N51" s="177"/>
-      <c r="O51" s="178"/>
-      <c r="P51" s="179"/>
+      <c r="C51" s="216"/>
+      <c r="D51" s="216"/>
+      <c r="E51" s="216"/>
+      <c r="F51" s="216"/>
+      <c r="G51" s="216"/>
+      <c r="H51" s="224"/>
+      <c r="I51" s="225"/>
+      <c r="J51" s="225"/>
+      <c r="K51" s="225"/>
+      <c r="L51" s="225"/>
+      <c r="M51" s="226"/>
+      <c r="N51" s="217"/>
+      <c r="O51" s="218"/>
+      <c r="P51" s="219"/>
       <c r="Q51" s="42"/>
-      <c r="R51" s="180"/>
-      <c r="S51" s="180"/>
+      <c r="R51" s="220"/>
+      <c r="S51" s="220"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="42"/>
       <c r="B52" s="42"/>
-      <c r="C52" s="173"/>
-      <c r="D52" s="173"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="173"/>
-      <c r="H52" s="174"/>
-      <c r="I52" s="175"/>
-      <c r="J52" s="175"/>
-      <c r="K52" s="175"/>
-      <c r="L52" s="175"/>
-      <c r="M52" s="176"/>
-      <c r="N52" s="177"/>
-      <c r="O52" s="178"/>
-      <c r="P52" s="179"/>
+      <c r="C52" s="216"/>
+      <c r="D52" s="216"/>
+      <c r="E52" s="216"/>
+      <c r="F52" s="216"/>
+      <c r="G52" s="216"/>
+      <c r="H52" s="224"/>
+      <c r="I52" s="225"/>
+      <c r="J52" s="225"/>
+      <c r="K52" s="225"/>
+      <c r="L52" s="225"/>
+      <c r="M52" s="226"/>
+      <c r="N52" s="217"/>
+      <c r="O52" s="218"/>
+      <c r="P52" s="219"/>
       <c r="Q52" s="42"/>
-      <c r="R52" s="180"/>
-      <c r="S52" s="180"/>
+      <c r="R52" s="220"/>
+      <c r="S52" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -14877,194 +15076,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -15128,23 +15139,23 @@
       <c r="AL1" s="49"/>
       <c r="AM1" s="49"/>
       <c r="AN1" s="49"/>
-      <c r="AO1" s="207" t="s">
+      <c r="AO1" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="AP1" s="207"/>
-      <c r="AQ1" s="207"/>
-      <c r="AR1" s="207"/>
-      <c r="AS1" s="207"/>
-      <c r="AT1" s="208">
+      <c r="AP1" s="230"/>
+      <c r="AQ1" s="230"/>
+      <c r="AR1" s="230"/>
+      <c r="AS1" s="230"/>
+      <c r="AT1" s="231">
         <v>46191</v>
       </c>
-      <c r="AU1" s="209"/>
-      <c r="AV1" s="209"/>
-      <c r="AW1" s="209"/>
-      <c r="AX1" s="209"/>
-      <c r="AY1" s="209"/>
-      <c r="AZ1" s="209"/>
-      <c r="BA1" s="209"/>
+      <c r="AU1" s="232"/>
+      <c r="AV1" s="232"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="232"/>
+      <c r="AY1" s="232"/>
+      <c r="AZ1" s="232"/>
+      <c r="BA1" s="232"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -15190,52 +15201,52 @@
       <c r="AK4" s="57"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="205"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="210"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="211"/>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="211"/>
-      <c r="S5" s="212"/>
+      <c r="B5" s="228"/>
+      <c r="C5" s="228"/>
+      <c r="D5" s="228"/>
+      <c r="E5" s="228"/>
+      <c r="F5" s="229"/>
+      <c r="G5" s="233"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="234"/>
+      <c r="M5" s="234"/>
+      <c r="N5" s="234"/>
+      <c r="O5" s="234"/>
+      <c r="P5" s="234"/>
+      <c r="Q5" s="234"/>
+      <c r="R5" s="234"/>
+      <c r="S5" s="235"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="227" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="213">
+      <c r="B6" s="228"/>
+      <c r="C6" s="228"/>
+      <c r="D6" s="228"/>
+      <c r="E6" s="228"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="236">
         <v>1</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="211"/>
-      <c r="K6" s="211"/>
-      <c r="L6" s="211"/>
-      <c r="M6" s="211"/>
-      <c r="N6" s="211"/>
-      <c r="O6" s="211"/>
-      <c r="P6" s="211"/>
-      <c r="Q6" s="211"/>
-      <c r="R6" s="211"/>
-      <c r="S6" s="212"/>
+      <c r="H6" s="234"/>
+      <c r="I6" s="234"/>
+      <c r="J6" s="234"/>
+      <c r="K6" s="234"/>
+      <c r="L6" s="234"/>
+      <c r="M6" s="234"/>
+      <c r="N6" s="234"/>
+      <c r="O6" s="234"/>
+      <c r="P6" s="234"/>
+      <c r="Q6" s="234"/>
+      <c r="R6" s="234"/>
+      <c r="S6" s="235"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -15244,61 +15255,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="204" t="s">
+      <c r="A9" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="205"/>
-      <c r="H9" s="205"/>
-      <c r="I9" s="205"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="205"/>
-      <c r="L9" s="205"/>
-      <c r="M9" s="205"/>
-      <c r="N9" s="205"/>
-      <c r="O9" s="205"/>
-      <c r="P9" s="205"/>
-      <c r="Q9" s="205"/>
-      <c r="R9" s="205"/>
-      <c r="S9" s="205"/>
-      <c r="T9" s="205"/>
-      <c r="U9" s="205"/>
-      <c r="V9" s="205"/>
-      <c r="W9" s="205"/>
-      <c r="X9" s="205"/>
-      <c r="Y9" s="205"/>
-      <c r="Z9" s="205"/>
-      <c r="AA9" s="205"/>
-      <c r="AB9" s="205"/>
-      <c r="AC9" s="205"/>
-      <c r="AD9" s="205"/>
-      <c r="AE9" s="205"/>
-      <c r="AF9" s="205"/>
-      <c r="AG9" s="205"/>
-      <c r="AH9" s="205"/>
-      <c r="AI9" s="205"/>
-      <c r="AJ9" s="205"/>
-      <c r="AK9" s="205"/>
-      <c r="AL9" s="205"/>
-      <c r="AM9" s="205"/>
-      <c r="AN9" s="205"/>
-      <c r="AO9" s="205"/>
-      <c r="AP9" s="205"/>
-      <c r="AQ9" s="205"/>
-      <c r="AR9" s="205"/>
-      <c r="AS9" s="205"/>
-      <c r="AT9" s="205"/>
-      <c r="AU9" s="205"/>
-      <c r="AV9" s="205"/>
-      <c r="AW9" s="205"/>
-      <c r="AX9" s="205"/>
-      <c r="AY9" s="205"/>
-      <c r="AZ9" s="205"/>
-      <c r="BA9" s="206"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="228"/>
+      <c r="D9" s="228"/>
+      <c r="E9" s="228"/>
+      <c r="F9" s="228"/>
+      <c r="G9" s="228"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="228"/>
+      <c r="J9" s="228"/>
+      <c r="K9" s="228"/>
+      <c r="L9" s="228"/>
+      <c r="M9" s="228"/>
+      <c r="N9" s="228"/>
+      <c r="O9" s="228"/>
+      <c r="P9" s="228"/>
+      <c r="Q9" s="228"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="228"/>
+      <c r="T9" s="228"/>
+      <c r="U9" s="228"/>
+      <c r="V9" s="228"/>
+      <c r="W9" s="228"/>
+      <c r="X9" s="228"/>
+      <c r="Y9" s="228"/>
+      <c r="Z9" s="228"/>
+      <c r="AA9" s="228"/>
+      <c r="AB9" s="228"/>
+      <c r="AC9" s="228"/>
+      <c r="AD9" s="228"/>
+      <c r="AE9" s="228"/>
+      <c r="AF9" s="228"/>
+      <c r="AG9" s="228"/>
+      <c r="AH9" s="228"/>
+      <c r="AI9" s="228"/>
+      <c r="AJ9" s="228"/>
+      <c r="AK9" s="228"/>
+      <c r="AL9" s="228"/>
+      <c r="AM9" s="228"/>
+      <c r="AN9" s="228"/>
+      <c r="AO9" s="228"/>
+      <c r="AP9" s="228"/>
+      <c r="AQ9" s="228"/>
+      <c r="AR9" s="228"/>
+      <c r="AS9" s="228"/>
+      <c r="AT9" s="228"/>
+      <c r="AU9" s="228"/>
+      <c r="AV9" s="228"/>
+      <c r="AW9" s="228"/>
+      <c r="AX9" s="228"/>
+      <c r="AY9" s="228"/>
+      <c r="AZ9" s="228"/>
+      <c r="BA9" s="229"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="54"/>
@@ -16101,61 +16112,61 @@
       <c r="BA29" s="52"/>
     </row>
     <row r="30" spans="1:53" ht="18" customHeight="1">
-      <c r="A30" s="204" t="s">
+      <c r="A30" s="227" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="205"/>
-      <c r="C30" s="205"/>
-      <c r="D30" s="205"/>
-      <c r="E30" s="205"/>
-      <c r="F30" s="205"/>
-      <c r="G30" s="205"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="205"/>
-      <c r="L30" s="205"/>
-      <c r="M30" s="205"/>
-      <c r="N30" s="205"/>
-      <c r="O30" s="205"/>
-      <c r="P30" s="205"/>
-      <c r="Q30" s="205"/>
-      <c r="R30" s="205"/>
-      <c r="S30" s="205"/>
-      <c r="T30" s="205"/>
-      <c r="U30" s="205"/>
-      <c r="V30" s="205"/>
-      <c r="W30" s="205"/>
-      <c r="X30" s="205"/>
-      <c r="Y30" s="205"/>
-      <c r="Z30" s="205"/>
-      <c r="AA30" s="205"/>
-      <c r="AB30" s="205"/>
-      <c r="AC30" s="205"/>
-      <c r="AD30" s="205"/>
-      <c r="AE30" s="205"/>
-      <c r="AF30" s="205"/>
-      <c r="AG30" s="205"/>
-      <c r="AH30" s="205"/>
-      <c r="AI30" s="205"/>
-      <c r="AJ30" s="205"/>
-      <c r="AK30" s="205"/>
-      <c r="AL30" s="205"/>
-      <c r="AM30" s="205"/>
-      <c r="AN30" s="205"/>
-      <c r="AO30" s="205"/>
-      <c r="AP30" s="205"/>
-      <c r="AQ30" s="205"/>
-      <c r="AR30" s="205"/>
-      <c r="AS30" s="205"/>
-      <c r="AT30" s="205"/>
-      <c r="AU30" s="205"/>
-      <c r="AV30" s="205"/>
-      <c r="AW30" s="205"/>
-      <c r="AX30" s="205"/>
-      <c r="AY30" s="205"/>
-      <c r="AZ30" s="205"/>
-      <c r="BA30" s="206"/>
+      <c r="B30" s="228"/>
+      <c r="C30" s="228"/>
+      <c r="D30" s="228"/>
+      <c r="E30" s="228"/>
+      <c r="F30" s="228"/>
+      <c r="G30" s="228"/>
+      <c r="H30" s="228"/>
+      <c r="I30" s="228"/>
+      <c r="J30" s="228"/>
+      <c r="K30" s="228"/>
+      <c r="L30" s="228"/>
+      <c r="M30" s="228"/>
+      <c r="N30" s="228"/>
+      <c r="O30" s="228"/>
+      <c r="P30" s="228"/>
+      <c r="Q30" s="228"/>
+      <c r="R30" s="228"/>
+      <c r="S30" s="228"/>
+      <c r="T30" s="228"/>
+      <c r="U30" s="228"/>
+      <c r="V30" s="228"/>
+      <c r="W30" s="228"/>
+      <c r="X30" s="228"/>
+      <c r="Y30" s="228"/>
+      <c r="Z30" s="228"/>
+      <c r="AA30" s="228"/>
+      <c r="AB30" s="228"/>
+      <c r="AC30" s="228"/>
+      <c r="AD30" s="228"/>
+      <c r="AE30" s="228"/>
+      <c r="AF30" s="228"/>
+      <c r="AG30" s="228"/>
+      <c r="AH30" s="228"/>
+      <c r="AI30" s="228"/>
+      <c r="AJ30" s="228"/>
+      <c r="AK30" s="228"/>
+      <c r="AL30" s="228"/>
+      <c r="AM30" s="228"/>
+      <c r="AN30" s="228"/>
+      <c r="AO30" s="228"/>
+      <c r="AP30" s="228"/>
+      <c r="AQ30" s="228"/>
+      <c r="AR30" s="228"/>
+      <c r="AS30" s="228"/>
+      <c r="AT30" s="228"/>
+      <c r="AU30" s="228"/>
+      <c r="AV30" s="228"/>
+      <c r="AW30" s="228"/>
+      <c r="AX30" s="228"/>
+      <c r="AY30" s="228"/>
+      <c r="AZ30" s="228"/>
+      <c r="BA30" s="229"/>
     </row>
     <row r="31" spans="1:53" ht="21.95" customHeight="1">
       <c r="A31" s="56"/>
@@ -16478,61 +16489,61 @@
       <c r="BA38" s="52"/>
     </row>
     <row r="39" spans="1:53" ht="18" customHeight="1">
-      <c r="A39" s="204" t="s">
+      <c r="A39" s="227" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="205"/>
-      <c r="C39" s="205"/>
-      <c r="D39" s="205"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="205"/>
-      <c r="G39" s="205"/>
-      <c r="H39" s="205"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="205"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="205"/>
-      <c r="M39" s="205"/>
-      <c r="N39" s="205"/>
-      <c r="O39" s="205"/>
-      <c r="P39" s="205"/>
-      <c r="Q39" s="205"/>
-      <c r="R39" s="205"/>
-      <c r="S39" s="205"/>
-      <c r="T39" s="205"/>
-      <c r="U39" s="205"/>
-      <c r="V39" s="205"/>
-      <c r="W39" s="205"/>
-      <c r="X39" s="205"/>
-      <c r="Y39" s="205"/>
-      <c r="Z39" s="205"/>
-      <c r="AA39" s="205"/>
-      <c r="AB39" s="205"/>
-      <c r="AC39" s="205"/>
-      <c r="AD39" s="205"/>
-      <c r="AE39" s="205"/>
-      <c r="AF39" s="205"/>
-      <c r="AG39" s="205"/>
-      <c r="AH39" s="205"/>
-      <c r="AI39" s="205"/>
-      <c r="AJ39" s="205"/>
-      <c r="AK39" s="205"/>
-      <c r="AL39" s="205"/>
-      <c r="AM39" s="205"/>
-      <c r="AN39" s="205"/>
-      <c r="AO39" s="205"/>
-      <c r="AP39" s="205"/>
-      <c r="AQ39" s="205"/>
-      <c r="AR39" s="205"/>
-      <c r="AS39" s="205"/>
-      <c r="AT39" s="205"/>
-      <c r="AU39" s="205"/>
-      <c r="AV39" s="205"/>
-      <c r="AW39" s="205"/>
-      <c r="AX39" s="205"/>
-      <c r="AY39" s="205"/>
-      <c r="AZ39" s="205"/>
-      <c r="BA39" s="205"/>
+      <c r="B39" s="228"/>
+      <c r="C39" s="228"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="228"/>
+      <c r="F39" s="228"/>
+      <c r="G39" s="228"/>
+      <c r="H39" s="228"/>
+      <c r="I39" s="228"/>
+      <c r="J39" s="228"/>
+      <c r="K39" s="228"/>
+      <c r="L39" s="228"/>
+      <c r="M39" s="228"/>
+      <c r="N39" s="228"/>
+      <c r="O39" s="228"/>
+      <c r="P39" s="228"/>
+      <c r="Q39" s="228"/>
+      <c r="R39" s="228"/>
+      <c r="S39" s="228"/>
+      <c r="T39" s="228"/>
+      <c r="U39" s="228"/>
+      <c r="V39" s="228"/>
+      <c r="W39" s="228"/>
+      <c r="X39" s="228"/>
+      <c r="Y39" s="228"/>
+      <c r="Z39" s="228"/>
+      <c r="AA39" s="228"/>
+      <c r="AB39" s="228"/>
+      <c r="AC39" s="228"/>
+      <c r="AD39" s="228"/>
+      <c r="AE39" s="228"/>
+      <c r="AF39" s="228"/>
+      <c r="AG39" s="228"/>
+      <c r="AH39" s="228"/>
+      <c r="AI39" s="228"/>
+      <c r="AJ39" s="228"/>
+      <c r="AK39" s="228"/>
+      <c r="AL39" s="228"/>
+      <c r="AM39" s="228"/>
+      <c r="AN39" s="228"/>
+      <c r="AO39" s="228"/>
+      <c r="AP39" s="228"/>
+      <c r="AQ39" s="228"/>
+      <c r="AR39" s="228"/>
+      <c r="AS39" s="228"/>
+      <c r="AT39" s="228"/>
+      <c r="AU39" s="228"/>
+      <c r="AV39" s="228"/>
+      <c r="AW39" s="228"/>
+      <c r="AX39" s="228"/>
+      <c r="AY39" s="228"/>
+      <c r="AZ39" s="228"/>
+      <c r="BA39" s="228"/>
     </row>
     <row r="40" spans="1:53" ht="21.95" customHeight="1">
       <c r="A40" s="56"/>

--- a/プロジェクト型演習_成果物_TasBo_コメント閲覧.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_コメント閲覧.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\TasBoドキュメント\コメント閲覧\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER110\Desktop\プロジェクト演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950CDA40-D9C1-48BC-B079-3A162C0312D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE48EA82-A5CF-441E-86B0-7866EBC3D79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="11" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="115">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -613,6 +613,25 @@
     <rPh sb="112" eb="114">
       <t>センイ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>正常系</t>
+    <rPh sb="0" eb="3">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>CommentDAO</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>select()</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>正しくコメント一覧のリストが取得できることを確認する</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1974,6 +1993,132 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2001,132 +2146,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2196,21 +2215,51 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2232,36 +2281,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2271,44 +2290,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2319,9 +2374,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2369,39 +2421,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="70" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="58" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3304,6 +3323,111 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>194517</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>109484</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D312DE07-9DFA-AE6E-ABC6-9D66D08CABF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2069225"/>
+          <a:ext cx="10442103" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76638</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>65690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>98535</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>162303</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{710348C6-ACA3-20BC-D24B-2B331B3573E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1061983" y="7838966"/>
+          <a:ext cx="7904655" cy="2012561"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3512,85 +3636,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1" thickBot="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1" thickTop="1">
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
       <c r="P2" s="65"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
       <c r="P3" s="65"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
       <c r="P4" s="65"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="88"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="130"/>
+      <c r="O5" s="130"/>
       <c r="P5" s="65"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1" thickBot="1">
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
       <c r="P6" s="65"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1" thickTop="1">
@@ -3610,46 +3734,46 @@
       <c r="P7" s="65"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="130"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="92">
+      <c r="H13" s="128"/>
+      <c r="I13" s="134">
         <v>46198</v>
       </c>
-      <c r="J13" s="85"/>
-      <c r="K13" s="86"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="128"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="84"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="86"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="128"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="84"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="86"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="128"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="64"/>
@@ -3658,13 +3782,13 @@
       <c r="J16" s="64"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="87" t="s">
+      <c r="G17" s="129" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="88"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4679,19 +4803,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="92"/>
+      <c r="F1" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="117"/>
+      <c r="G1" s="92"/>
       <c r="H1" s="73" t="s">
         <v>5</v>
       </c>
@@ -4703,194 +4827,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="130" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="131"/>
-      <c r="F2" s="130" t="s">
+      <c r="E2" s="111"/>
+      <c r="F2" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="131"/>
-      <c r="H2" s="134">
+      <c r="G2" s="111"/>
+      <c r="H2" s="114">
         <v>46195</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="J2" s="112"/>
+      <c r="J2" s="87"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="113"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="88"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="89"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="118" t="s">
+      <c r="B5" s="91"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="119"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="94"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="94"/>
+      <c r="B6" s="96"/>
       <c r="C6" s="97"/>
-      <c r="D6" s="104" t="s">
+      <c r="D6" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="95"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="94"/>
+      <c r="B7" s="96"/>
       <c r="C7" s="97"/>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="94"/>
+      <c r="B8" s="96"/>
       <c r="C8" s="97"/>
-      <c r="D8" s="93" t="s">
+      <c r="D8" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="95"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="99"/>
     </row>
     <row r="9" spans="1:10" ht="148.5" customHeight="1">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="119" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="97"/>
-      <c r="D9" s="93" t="s">
+      <c r="D9" s="115" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="95"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="99"/>
     </row>
     <row r="10" spans="1:10" ht="156.75" customHeight="1">
-      <c r="A10" s="106"/>
-      <c r="B10" s="108" t="s">
+      <c r="A10" s="117"/>
+      <c r="B10" s="119" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="97"/>
-      <c r="D10" s="93" t="s">
+      <c r="D10" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="95"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="99"/>
     </row>
     <row r="11" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A11" s="107"/>
-      <c r="B11" s="108" t="s">
+      <c r="A11" s="118"/>
+      <c r="B11" s="119" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="97"/>
-      <c r="D11" s="93" t="s">
+      <c r="D11" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="99"/>
     </row>
     <row r="12" spans="1:10" ht="92.25" customHeight="1">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="94"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="97"/>
-      <c r="D12" s="93" t="s">
+      <c r="D12" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="95"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="99"/>
     </row>
     <row r="13" spans="1:10" ht="113.25" customHeight="1" thickBot="1">
-      <c r="A13" s="98" t="s">
+      <c r="A13" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="99"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101" t="s">
+      <c r="B13" s="121"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="103"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="125"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5881,6 +6005,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -5893,21 +6032,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7343,16 +7467,16 @@
       <c r="A1" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="92"/>
+      <c r="F1" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="117"/>
+      <c r="G1" s="92"/>
       <c r="H1" s="72" t="s">
         <v>5</v>
       </c>
@@ -7364,48 +7488,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="130" t="s">
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="131"/>
-      <c r="F2" s="130" t="s">
+      <c r="E2" s="111"/>
+      <c r="F2" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="131"/>
+      <c r="G2" s="111"/>
       <c r="H2" s="157">
         <v>46196</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="112"/>
+      <c r="J2" s="87"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="113"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="88"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="89"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="76"/>
@@ -8887,7 +9011,7 @@
         <v>53</v>
       </c>
       <c r="G2" s="153"/>
-      <c r="H2" s="175">
+      <c r="H2" s="166">
         <v>46198</v>
       </c>
       <c r="I2" s="135" t="s">
@@ -8920,23 +9044,23 @@
       <c r="J4" s="139"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="167" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="177"/>
+      <c r="B5" s="168"/>
       <c r="C5" s="151"/>
-      <c r="D5" s="178" t="s">
+      <c r="D5" s="169" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="179"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="170"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="158" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="159"/>
@@ -8950,16 +9074,16 @@
       <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="171"/>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
-      <c r="D7" s="172"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="172"/>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="173"/>
+      <c r="A7" s="162"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="164"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="144"/>
@@ -8971,7 +9095,7 @@
       <c r="G8" s="145"/>
       <c r="H8" s="145"/>
       <c r="I8" s="145"/>
-      <c r="J8" s="174"/>
+      <c r="J8" s="165"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="144"/>
@@ -8983,7 +9107,7 @@
       <c r="G9" s="145"/>
       <c r="H9" s="145"/>
       <c r="I9" s="145"/>
-      <c r="J9" s="174"/>
+      <c r="J9" s="165"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="144"/>
@@ -8995,7 +9119,7 @@
       <c r="G10" s="145"/>
       <c r="H10" s="145"/>
       <c r="I10" s="145"/>
-      <c r="J10" s="174"/>
+      <c r="J10" s="165"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="144"/>
@@ -9007,7 +9131,7 @@
       <c r="G11" s="145"/>
       <c r="H11" s="145"/>
       <c r="I11" s="145"/>
-      <c r="J11" s="174"/>
+      <c r="J11" s="165"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="144"/>
@@ -9019,7 +9143,7 @@
       <c r="G12" s="145"/>
       <c r="H12" s="145"/>
       <c r="I12" s="145"/>
-      <c r="J12" s="174"/>
+      <c r="J12" s="165"/>
     </row>
     <row r="13" spans="1:10" ht="54" customHeight="1">
       <c r="A13" s="144"/>
@@ -9031,10 +9155,10 @@
       <c r="G13" s="145"/>
       <c r="H13" s="145"/>
       <c r="I13" s="145"/>
-      <c r="J13" s="174"/>
+      <c r="J13" s="165"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="170" t="s">
+      <c r="A14" s="158" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="159"/>
@@ -9048,18 +9172,18 @@
       <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="170" t="s">
+      <c r="A15" s="158" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="159"/>
-      <c r="C15" s="162"/>
-      <c r="D15" s="161" t="s">
+      <c r="C15" s="161"/>
+      <c r="D15" s="171" t="s">
         <v>96</v>
       </c>
       <c r="E15" s="159"/>
       <c r="F15" s="159"/>
       <c r="G15" s="159"/>
-      <c r="H15" s="162"/>
+      <c r="H15" s="161"/>
       <c r="I15" s="11" t="s">
         <v>24</v>
       </c>
@@ -9068,11 +9192,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="170" t="s">
+      <c r="A16" s="158" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="159"/>
-      <c r="C16" s="162"/>
+      <c r="C16" s="161"/>
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
@@ -9085,18 +9209,18 @@
       <c r="G16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="172" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="159"/>
       <c r="J16" s="160"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="163">
+      <c r="A17" s="173">
         <v>1</v>
       </c>
       <c r="B17" s="159"/>
-      <c r="C17" s="162"/>
+      <c r="C17" s="161"/>
       <c r="D17" s="13" t="s">
         <v>98</v>
       </c>
@@ -9109,16 +9233,16 @@
       <c r="G17" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="161"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="159"/>
       <c r="J17" s="160"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="163">
+      <c r="A18" s="173">
         <v>2</v>
       </c>
       <c r="B18" s="159"/>
-      <c r="C18" s="162"/>
+      <c r="C18" s="161"/>
       <c r="D18" s="13" t="s">
         <v>94</v>
       </c>
@@ -9129,12 +9253,12 @@
       <c r="G18" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H18" s="161"/>
+      <c r="H18" s="171"/>
       <c r="I18" s="159"/>
       <c r="J18" s="160"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="170" t="s">
+      <c r="A19" s="158" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="159"/>
@@ -9148,18 +9272,18 @@
       <c r="J19" s="160"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="170" t="s">
+      <c r="A20" s="158" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="159"/>
-      <c r="C20" s="162"/>
-      <c r="D20" s="161" t="s">
+      <c r="C20" s="161"/>
+      <c r="D20" s="171" t="s">
         <v>92</v>
       </c>
       <c r="E20" s="159"/>
       <c r="F20" s="159"/>
       <c r="G20" s="159"/>
-      <c r="H20" s="162"/>
+      <c r="H20" s="161"/>
       <c r="I20" s="11" t="s">
         <v>24</v>
       </c>
@@ -9168,11 +9292,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="170" t="s">
+      <c r="A21" s="158" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="159"/>
-      <c r="C21" s="162"/>
+      <c r="C21" s="161"/>
       <c r="D21" s="11" t="s">
         <v>26</v>
       </c>
@@ -9185,18 +9309,18 @@
       <c r="G21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="158" t="s">
+      <c r="H21" s="172" t="s">
         <v>16</v>
       </c>
       <c r="I21" s="159"/>
       <c r="J21" s="160"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="163">
+      <c r="A22" s="173">
         <v>3</v>
       </c>
       <c r="B22" s="159"/>
-      <c r="C22" s="162"/>
+      <c r="C22" s="161"/>
       <c r="D22" s="13" t="s">
         <v>95</v>
       </c>
@@ -9207,7 +9331,7 @@
       <c r="G22" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H22" s="161"/>
+      <c r="H22" s="171"/>
       <c r="I22" s="159"/>
       <c r="J22" s="160"/>
     </row>
@@ -9224,7 +9348,7 @@
       <c r="J23" s="71"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="170" t="s">
+      <c r="A24" s="158" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="159"/>
@@ -9238,18 +9362,18 @@
       <c r="J24" s="160"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="170" t="s">
+      <c r="A25" s="158" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="159"/>
-      <c r="C25" s="162"/>
-      <c r="D25" s="161" t="s">
+      <c r="C25" s="161"/>
+      <c r="D25" s="171" t="s">
         <v>89</v>
       </c>
       <c r="E25" s="159"/>
       <c r="F25" s="159"/>
       <c r="G25" s="159"/>
-      <c r="H25" s="162"/>
+      <c r="H25" s="161"/>
       <c r="I25" s="11" t="s">
         <v>24</v>
       </c>
@@ -9258,11 +9382,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="170" t="s">
+      <c r="A26" s="158" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="159"/>
-      <c r="C26" s="162"/>
+      <c r="C26" s="161"/>
       <c r="D26" s="11" t="s">
         <v>26</v>
       </c>
@@ -9275,18 +9399,18 @@
       <c r="G26" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="158" t="s">
+      <c r="H26" s="172" t="s">
         <v>16</v>
       </c>
       <c r="I26" s="159"/>
       <c r="J26" s="160"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="163">
+      <c r="A27" s="173">
         <v>4</v>
       </c>
       <c r="B27" s="159"/>
-      <c r="C27" s="162"/>
+      <c r="C27" s="161"/>
       <c r="D27" s="13" t="s">
         <v>97</v>
       </c>
@@ -9297,21 +9421,21 @@
       <c r="G27" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H27" s="161"/>
+      <c r="H27" s="171"/>
       <c r="I27" s="159"/>
       <c r="J27" s="160"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A28" s="164"/>
-      <c r="B28" s="165"/>
-      <c r="C28" s="166"/>
+      <c r="A28" s="174"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="176"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
-      <c r="H28" s="167"/>
-      <c r="I28" s="168"/>
-      <c r="J28" s="169"/>
+      <c r="H28" s="177"/>
+      <c r="I28" s="178"/>
+      <c r="J28" s="179"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10292,6 +10416,28 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -10307,28 +10453,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10386,7 +10510,7 @@
         <v>53</v>
       </c>
       <c r="G2" s="153"/>
-      <c r="H2" s="175">
+      <c r="H2" s="166">
         <v>46189</v>
       </c>
       <c r="I2" s="135" t="s">
@@ -10419,23 +10543,23 @@
       <c r="J4" s="139"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="167" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="177"/>
+      <c r="B5" s="168"/>
       <c r="C5" s="151"/>
-      <c r="D5" s="178" t="s">
+      <c r="D5" s="169" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="179"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="170"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="158" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="159"/>
@@ -10449,16 +10573,16 @@
       <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="171"/>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
-      <c r="D7" s="172"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="172"/>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="173"/>
+      <c r="A7" s="162"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="164"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="144"/>
@@ -10470,7 +10594,7 @@
       <c r="G8" s="145"/>
       <c r="H8" s="145"/>
       <c r="I8" s="145"/>
-      <c r="J8" s="174"/>
+      <c r="J8" s="165"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="144"/>
@@ -10482,7 +10606,7 @@
       <c r="G9" s="145"/>
       <c r="H9" s="145"/>
       <c r="I9" s="145"/>
-      <c r="J9" s="174"/>
+      <c r="J9" s="165"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="144"/>
@@ -10494,7 +10618,7 @@
       <c r="G10" s="145"/>
       <c r="H10" s="145"/>
       <c r="I10" s="145"/>
-      <c r="J10" s="174"/>
+      <c r="J10" s="165"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="144"/>
@@ -10506,7 +10630,7 @@
       <c r="G11" s="145"/>
       <c r="H11" s="145"/>
       <c r="I11" s="145"/>
-      <c r="J11" s="174"/>
+      <c r="J11" s="165"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="144"/>
@@ -10518,7 +10642,7 @@
       <c r="G12" s="145"/>
       <c r="H12" s="145"/>
       <c r="I12" s="145"/>
-      <c r="J12" s="174"/>
+      <c r="J12" s="165"/>
     </row>
     <row r="13" spans="1:10" ht="41.25" customHeight="1">
       <c r="A13" s="144"/>
@@ -10530,10 +10654,10 @@
       <c r="G13" s="145"/>
       <c r="H13" s="145"/>
       <c r="I13" s="145"/>
-      <c r="J13" s="174"/>
+      <c r="J13" s="165"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="170" t="s">
+      <c r="A14" s="158" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="159"/>
@@ -10547,18 +10671,18 @@
       <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="170" t="s">
+      <c r="A15" s="158" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="159"/>
-      <c r="C15" s="162"/>
-      <c r="D15" s="161" t="s">
+      <c r="C15" s="161"/>
+      <c r="D15" s="171" t="s">
         <v>92</v>
       </c>
       <c r="E15" s="159"/>
       <c r="F15" s="159"/>
       <c r="G15" s="159"/>
-      <c r="H15" s="162"/>
+      <c r="H15" s="161"/>
       <c r="I15" s="11" t="s">
         <v>24</v>
       </c>
@@ -10567,11 +10691,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="170" t="s">
+      <c r="A16" s="158" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="159"/>
-      <c r="C16" s="162"/>
+      <c r="C16" s="161"/>
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
@@ -10584,18 +10708,18 @@
       <c r="G16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="172" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="159"/>
       <c r="J16" s="160"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="163">
+      <c r="A17" s="173">
         <v>1</v>
       </c>
       <c r="B17" s="159"/>
-      <c r="C17" s="162"/>
+      <c r="C17" s="161"/>
       <c r="D17" s="13" t="s">
         <v>95</v>
       </c>
@@ -10606,24 +10730,24 @@
       <c r="G17" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="161"/>
+      <c r="H17" s="171"/>
       <c r="I17" s="159"/>
       <c r="J17" s="160"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="163"/>
+      <c r="A18" s="173"/>
       <c r="B18" s="159"/>
-      <c r="C18" s="162"/>
+      <c r="C18" s="161"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="161"/>
+      <c r="H18" s="171"/>
       <c r="I18" s="159"/>
       <c r="J18" s="160"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="170" t="s">
+      <c r="A19" s="158" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="159"/>
@@ -10637,18 +10761,18 @@
       <c r="J19" s="160"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="170" t="s">
+      <c r="A20" s="158" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="159"/>
-      <c r="C20" s="162"/>
-      <c r="D20" s="161" t="s">
+      <c r="C20" s="161"/>
+      <c r="D20" s="171" t="s">
         <v>89</v>
       </c>
       <c r="E20" s="159"/>
       <c r="F20" s="159"/>
       <c r="G20" s="159"/>
-      <c r="H20" s="162"/>
+      <c r="H20" s="161"/>
       <c r="I20" s="11" t="s">
         <v>24</v>
       </c>
@@ -10657,11 +10781,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="170" t="s">
+      <c r="A21" s="158" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="159"/>
-      <c r="C21" s="162"/>
+      <c r="C21" s="161"/>
       <c r="D21" s="11" t="s">
         <v>26</v>
       </c>
@@ -10674,14 +10798,14 @@
       <c r="G21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="158" t="s">
+      <c r="H21" s="172" t="s">
         <v>16</v>
       </c>
       <c r="I21" s="159"/>
       <c r="J21" s="160"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A22" s="164">
+      <c r="A22" s="174">
         <v>2</v>
       </c>
       <c r="B22" s="180"/>
@@ -10696,7 +10820,7 @@
       <c r="G22" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="H22" s="167"/>
+      <c r="H22" s="177"/>
       <c r="I22" s="180"/>
       <c r="J22" s="182"/>
     </row>
@@ -11679,19 +11803,6 @@
     <row r="999" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11707,6 +11818,19 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D20:H20"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11726,7 +11850,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="194" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="142"/>
@@ -11737,14 +11861,14 @@
       <c r="G1" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
+      <c r="H1" s="168"/>
+      <c r="I1" s="168"/>
       <c r="J1" s="151"/>
       <c r="K1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
+      <c r="L1" s="168"/>
+      <c r="M1" s="168"/>
       <c r="N1" s="151"/>
       <c r="O1" s="150" t="s">
         <v>5</v>
@@ -11757,7 +11881,7 @@
       <c r="S1" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="179"/>
+      <c r="T1" s="170"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="144"/>
@@ -11769,23 +11893,23 @@
       <c r="G2" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
       <c r="J2" s="153"/>
       <c r="K2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
       <c r="N2" s="153"/>
-      <c r="O2" s="187"/>
+      <c r="O2" s="192"/>
       <c r="P2" s="153"/>
       <c r="Q2" s="152" t="s">
         <v>55</v>
       </c>
       <c r="R2" s="153"/>
       <c r="S2" s="152"/>
-      <c r="T2" s="173"/>
+      <c r="T2" s="164"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="144"/>
@@ -11807,7 +11931,7 @@
       <c r="Q3" s="154"/>
       <c r="R3" s="146"/>
       <c r="S3" s="154"/>
-      <c r="T3" s="174"/>
+      <c r="T3" s="165"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="147"/>
@@ -11829,42 +11953,42 @@
       <c r="Q4" s="155"/>
       <c r="R4" s="149"/>
       <c r="S4" s="155"/>
-      <c r="T4" s="188"/>
+      <c r="T4" s="193"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="177"/>
-      <c r="C5" s="177"/>
-      <c r="D5" s="177"/>
-      <c r="E5" s="177"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
       <c r="F5" s="151"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="177"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="177"/>
-      <c r="O5" s="177"/>
-      <c r="P5" s="177"/>
-      <c r="Q5" s="177"/>
-      <c r="R5" s="177"/>
-      <c r="S5" s="177"/>
-      <c r="T5" s="179"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="168"/>
+      <c r="K5" s="168"/>
+      <c r="L5" s="168"/>
+      <c r="M5" s="168"/>
+      <c r="N5" s="168"/>
+      <c r="O5" s="168"/>
+      <c r="P5" s="168"/>
+      <c r="Q5" s="168"/>
+      <c r="R5" s="168"/>
+      <c r="S5" s="168"/>
+      <c r="T5" s="170"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="158" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="159"/>
       <c r="C6" s="159"/>
       <c r="D6" s="159"/>
       <c r="E6" s="159"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="171"/>
       <c r="H6" s="159"/>
       <c r="I6" s="159"/>
       <c r="J6" s="159"/>
@@ -11880,15 +12004,15 @@
       <c r="T6" s="160"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="170" t="s">
+      <c r="A7" s="158" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="159"/>
       <c r="C7" s="159"/>
       <c r="D7" s="159"/>
       <c r="E7" s="159"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="161"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="171"/>
       <c r="H7" s="159"/>
       <c r="I7" s="159"/>
       <c r="J7" s="159"/>
@@ -12100,37 +12224,37 @@
       <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="170" t="s">
+      <c r="A15" s="158" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="162"/>
-      <c r="C15" s="193" t="s">
+      <c r="B15" s="161"/>
+      <c r="C15" s="191" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="162"/>
-      <c r="E15" s="158" t="s">
+      <c r="D15" s="161"/>
+      <c r="E15" s="172" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="162"/>
-      <c r="G15" s="158" t="s">
+      <c r="F15" s="161"/>
+      <c r="G15" s="172" t="s">
         <v>42</v>
       </c>
       <c r="H15" s="159"/>
-      <c r="I15" s="162"/>
-      <c r="J15" s="158" t="s">
+      <c r="I15" s="161"/>
+      <c r="J15" s="172" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="162"/>
-      <c r="L15" s="158" t="s">
+      <c r="K15" s="161"/>
+      <c r="L15" s="172" t="s">
         <v>44</v>
       </c>
       <c r="M15" s="159"/>
-      <c r="N15" s="162"/>
-      <c r="O15" s="158" t="s">
+      <c r="N15" s="161"/>
+      <c r="O15" s="172" t="s">
         <v>45</v>
       </c>
       <c r="P15" s="159"/>
-      <c r="Q15" s="162"/>
+      <c r="Q15" s="161"/>
       <c r="R15" s="11" t="s">
         <v>46</v>
       </c>
@@ -12142,25 +12266,25 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="191">
+      <c r="A16" s="183">
         <v>1</v>
       </c>
-      <c r="B16" s="162"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="192"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="183"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="184"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="184"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="190"/>
       <c r="H16" s="159"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="183"/>
-      <c r="K16" s="162"/>
-      <c r="L16" s="185"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="190"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="187"/>
       <c r="M16" s="159"/>
-      <c r="N16" s="162"/>
-      <c r="O16" s="185"/>
+      <c r="N16" s="161"/>
+      <c r="O16" s="187"/>
       <c r="P16" s="159"/>
-      <c r="Q16" s="162"/>
+      <c r="Q16" s="161"/>
       <c r="R16" s="29"/>
       <c r="S16" s="29"/>
       <c r="T16" s="30"/>
@@ -12172,25 +12296,25 @@
       <c r="Z16" s="31"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="191">
+      <c r="A17" s="183">
         <v>2</v>
       </c>
-      <c r="B17" s="162"/>
-      <c r="C17" s="192"/>
-      <c r="D17" s="162"/>
-      <c r="E17" s="192"/>
-      <c r="F17" s="162"/>
-      <c r="G17" s="183"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="184"/>
+      <c r="D17" s="161"/>
+      <c r="E17" s="184"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="190"/>
       <c r="H17" s="159"/>
-      <c r="I17" s="162"/>
-      <c r="J17" s="183"/>
-      <c r="K17" s="162"/>
-      <c r="L17" s="185"/>
+      <c r="I17" s="161"/>
+      <c r="J17" s="190"/>
+      <c r="K17" s="161"/>
+      <c r="L17" s="187"/>
       <c r="M17" s="159"/>
-      <c r="N17" s="162"/>
-      <c r="O17" s="185"/>
+      <c r="N17" s="161"/>
+      <c r="O17" s="187"/>
       <c r="P17" s="159"/>
-      <c r="Q17" s="162"/>
+      <c r="Q17" s="161"/>
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
       <c r="T17" s="30"/>
@@ -12202,23 +12326,23 @@
       <c r="Z17" s="31"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="191"/>
-      <c r="B18" s="162"/>
-      <c r="C18" s="192"/>
-      <c r="D18" s="162"/>
-      <c r="E18" s="192"/>
-      <c r="F18" s="162"/>
-      <c r="G18" s="183"/>
+      <c r="A18" s="183"/>
+      <c r="B18" s="161"/>
+      <c r="C18" s="184"/>
+      <c r="D18" s="161"/>
+      <c r="E18" s="184"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="190"/>
       <c r="H18" s="159"/>
-      <c r="I18" s="162"/>
-      <c r="J18" s="183"/>
-      <c r="K18" s="162"/>
-      <c r="L18" s="185"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="190"/>
+      <c r="K18" s="161"/>
+      <c r="L18" s="187"/>
       <c r="M18" s="159"/>
-      <c r="N18" s="162"/>
-      <c r="O18" s="185"/>
+      <c r="N18" s="161"/>
+      <c r="O18" s="187"/>
       <c r="P18" s="159"/>
-      <c r="Q18" s="162"/>
+      <c r="Q18" s="161"/>
       <c r="R18" s="29"/>
       <c r="S18" s="29"/>
       <c r="T18" s="30"/>
@@ -12230,23 +12354,23 @@
       <c r="Z18" s="31"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="191"/>
-      <c r="B19" s="162"/>
-      <c r="C19" s="192"/>
-      <c r="D19" s="162"/>
-      <c r="E19" s="192"/>
-      <c r="F19" s="162"/>
-      <c r="G19" s="183"/>
+      <c r="A19" s="183"/>
+      <c r="B19" s="161"/>
+      <c r="C19" s="184"/>
+      <c r="D19" s="161"/>
+      <c r="E19" s="184"/>
+      <c r="F19" s="161"/>
+      <c r="G19" s="190"/>
       <c r="H19" s="159"/>
-      <c r="I19" s="162"/>
-      <c r="J19" s="183"/>
-      <c r="K19" s="162"/>
-      <c r="L19" s="185"/>
+      <c r="I19" s="161"/>
+      <c r="J19" s="190"/>
+      <c r="K19" s="161"/>
+      <c r="L19" s="187"/>
       <c r="M19" s="159"/>
-      <c r="N19" s="162"/>
-      <c r="O19" s="185"/>
+      <c r="N19" s="161"/>
+      <c r="O19" s="187"/>
       <c r="P19" s="159"/>
-      <c r="Q19" s="162"/>
+      <c r="Q19" s="161"/>
       <c r="R19" s="29"/>
       <c r="S19" s="29"/>
       <c r="T19" s="30"/>
@@ -12258,23 +12382,23 @@
       <c r="Z19" s="31"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="191"/>
-      <c r="B20" s="162"/>
-      <c r="C20" s="192"/>
-      <c r="D20" s="162"/>
-      <c r="E20" s="192"/>
-      <c r="F20" s="162"/>
-      <c r="G20" s="183"/>
+      <c r="A20" s="183"/>
+      <c r="B20" s="161"/>
+      <c r="C20" s="184"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="190"/>
       <c r="H20" s="159"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="183"/>
-      <c r="K20" s="162"/>
-      <c r="L20" s="185"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="190"/>
+      <c r="K20" s="161"/>
+      <c r="L20" s="187"/>
       <c r="M20" s="159"/>
-      <c r="N20" s="162"/>
-      <c r="O20" s="185"/>
+      <c r="N20" s="161"/>
+      <c r="O20" s="187"/>
       <c r="P20" s="159"/>
-      <c r="Q20" s="162"/>
+      <c r="Q20" s="161"/>
       <c r="R20" s="29"/>
       <c r="S20" s="29"/>
       <c r="T20" s="30"/>
@@ -12286,23 +12410,23 @@
       <c r="Z20" s="31"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="191"/>
-      <c r="B21" s="162"/>
-      <c r="C21" s="192"/>
-      <c r="D21" s="162"/>
-      <c r="E21" s="192"/>
-      <c r="F21" s="162"/>
-      <c r="G21" s="183"/>
+      <c r="A21" s="183"/>
+      <c r="B21" s="161"/>
+      <c r="C21" s="184"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="190"/>
       <c r="H21" s="159"/>
-      <c r="I21" s="162"/>
-      <c r="J21" s="183"/>
-      <c r="K21" s="162"/>
-      <c r="L21" s="185"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="190"/>
+      <c r="K21" s="161"/>
+      <c r="L21" s="187"/>
       <c r="M21" s="159"/>
-      <c r="N21" s="162"/>
-      <c r="O21" s="185"/>
+      <c r="N21" s="161"/>
+      <c r="O21" s="187"/>
       <c r="P21" s="159"/>
-      <c r="Q21" s="162"/>
+      <c r="Q21" s="161"/>
       <c r="R21" s="29"/>
       <c r="S21" s="29"/>
       <c r="T21" s="30"/>
@@ -12314,23 +12438,23 @@
       <c r="Z21" s="31"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="191"/>
-      <c r="B22" s="162"/>
-      <c r="C22" s="192"/>
-      <c r="D22" s="162"/>
-      <c r="E22" s="192"/>
-      <c r="F22" s="162"/>
-      <c r="G22" s="183"/>
+      <c r="A22" s="183"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="184"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="190"/>
       <c r="H22" s="159"/>
-      <c r="I22" s="162"/>
-      <c r="J22" s="183"/>
-      <c r="K22" s="162"/>
-      <c r="L22" s="185"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="190"/>
+      <c r="K22" s="161"/>
+      <c r="L22" s="187"/>
       <c r="M22" s="159"/>
-      <c r="N22" s="162"/>
-      <c r="O22" s="185"/>
+      <c r="N22" s="161"/>
+      <c r="O22" s="187"/>
       <c r="P22" s="159"/>
-      <c r="Q22" s="162"/>
+      <c r="Q22" s="161"/>
       <c r="R22" s="29"/>
       <c r="S22" s="29"/>
       <c r="T22" s="30"/>
@@ -12342,23 +12466,23 @@
       <c r="Z22" s="31"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="191"/>
-      <c r="B23" s="162"/>
-      <c r="C23" s="192"/>
-      <c r="D23" s="162"/>
-      <c r="E23" s="192"/>
-      <c r="F23" s="162"/>
-      <c r="G23" s="183"/>
+      <c r="A23" s="183"/>
+      <c r="B23" s="161"/>
+      <c r="C23" s="184"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="190"/>
       <c r="H23" s="159"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="183"/>
-      <c r="K23" s="162"/>
-      <c r="L23" s="185"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="190"/>
+      <c r="K23" s="161"/>
+      <c r="L23" s="187"/>
       <c r="M23" s="159"/>
-      <c r="N23" s="162"/>
-      <c r="O23" s="185"/>
+      <c r="N23" s="161"/>
+      <c r="O23" s="187"/>
       <c r="P23" s="159"/>
-      <c r="Q23" s="162"/>
+      <c r="Q23" s="161"/>
       <c r="R23" s="29"/>
       <c r="S23" s="29"/>
       <c r="T23" s="30"/>
@@ -12370,23 +12494,23 @@
       <c r="Z23" s="31"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="191"/>
-      <c r="B24" s="162"/>
-      <c r="C24" s="192"/>
-      <c r="D24" s="162"/>
-      <c r="E24" s="192"/>
-      <c r="F24" s="162"/>
-      <c r="G24" s="183"/>
+      <c r="A24" s="183"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="184"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="190"/>
       <c r="H24" s="159"/>
-      <c r="I24" s="162"/>
-      <c r="J24" s="183"/>
-      <c r="K24" s="162"/>
-      <c r="L24" s="185"/>
+      <c r="I24" s="161"/>
+      <c r="J24" s="190"/>
+      <c r="K24" s="161"/>
+      <c r="L24" s="187"/>
       <c r="M24" s="159"/>
-      <c r="N24" s="162"/>
-      <c r="O24" s="185"/>
+      <c r="N24" s="161"/>
+      <c r="O24" s="187"/>
       <c r="P24" s="159"/>
-      <c r="Q24" s="162"/>
+      <c r="Q24" s="161"/>
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
       <c r="T24" s="30"/>
@@ -12398,23 +12522,23 @@
       <c r="Z24" s="31"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="191"/>
-      <c r="B25" s="162"/>
-      <c r="C25" s="192"/>
-      <c r="D25" s="162"/>
-      <c r="E25" s="192"/>
-      <c r="F25" s="162"/>
-      <c r="G25" s="183"/>
+      <c r="A25" s="183"/>
+      <c r="B25" s="161"/>
+      <c r="C25" s="184"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="190"/>
       <c r="H25" s="159"/>
-      <c r="I25" s="162"/>
-      <c r="J25" s="183"/>
-      <c r="K25" s="162"/>
-      <c r="L25" s="185"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="190"/>
+      <c r="K25" s="161"/>
+      <c r="L25" s="187"/>
       <c r="M25" s="159"/>
-      <c r="N25" s="162"/>
-      <c r="O25" s="185"/>
+      <c r="N25" s="161"/>
+      <c r="O25" s="187"/>
       <c r="P25" s="159"/>
-      <c r="Q25" s="162"/>
+      <c r="Q25" s="161"/>
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
       <c r="T25" s="30"/>
@@ -12426,23 +12550,23 @@
       <c r="Z25" s="31"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="191"/>
-      <c r="B26" s="162"/>
-      <c r="C26" s="192"/>
-      <c r="D26" s="162"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="162"/>
-      <c r="G26" s="183"/>
+      <c r="A26" s="183"/>
+      <c r="B26" s="161"/>
+      <c r="C26" s="184"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="161"/>
+      <c r="G26" s="190"/>
       <c r="H26" s="159"/>
-      <c r="I26" s="162"/>
-      <c r="J26" s="183"/>
-      <c r="K26" s="162"/>
-      <c r="L26" s="185"/>
+      <c r="I26" s="161"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="161"/>
+      <c r="L26" s="187"/>
       <c r="M26" s="159"/>
-      <c r="N26" s="162"/>
-      <c r="O26" s="185"/>
+      <c r="N26" s="161"/>
+      <c r="O26" s="187"/>
       <c r="P26" s="159"/>
-      <c r="Q26" s="162"/>
+      <c r="Q26" s="161"/>
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
       <c r="T26" s="30"/>
@@ -12454,23 +12578,23 @@
       <c r="Z26" s="31"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="191"/>
-      <c r="B27" s="162"/>
-      <c r="C27" s="192"/>
-      <c r="D27" s="162"/>
-      <c r="E27" s="192"/>
-      <c r="F27" s="162"/>
-      <c r="G27" s="183"/>
+      <c r="A27" s="183"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="184"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="184"/>
+      <c r="F27" s="161"/>
+      <c r="G27" s="190"/>
       <c r="H27" s="159"/>
-      <c r="I27" s="162"/>
-      <c r="J27" s="183"/>
-      <c r="K27" s="162"/>
-      <c r="L27" s="185"/>
+      <c r="I27" s="161"/>
+      <c r="J27" s="190"/>
+      <c r="K27" s="161"/>
+      <c r="L27" s="187"/>
       <c r="M27" s="159"/>
-      <c r="N27" s="162"/>
-      <c r="O27" s="185"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="187"/>
       <c r="P27" s="159"/>
-      <c r="Q27" s="162"/>
+      <c r="Q27" s="161"/>
       <c r="R27" s="29"/>
       <c r="S27" s="29"/>
       <c r="T27" s="30"/>
@@ -12482,23 +12606,23 @@
       <c r="Z27" s="31"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="191"/>
-      <c r="B28" s="162"/>
-      <c r="C28" s="192"/>
-      <c r="D28" s="162"/>
-      <c r="E28" s="192"/>
-      <c r="F28" s="162"/>
-      <c r="G28" s="183"/>
+      <c r="A28" s="183"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="184"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="184"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="190"/>
       <c r="H28" s="159"/>
-      <c r="I28" s="162"/>
-      <c r="J28" s="183"/>
-      <c r="K28" s="162"/>
-      <c r="L28" s="185"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="190"/>
+      <c r="K28" s="161"/>
+      <c r="L28" s="187"/>
       <c r="M28" s="159"/>
-      <c r="N28" s="162"/>
-      <c r="O28" s="185"/>
+      <c r="N28" s="161"/>
+      <c r="O28" s="187"/>
       <c r="P28" s="159"/>
-      <c r="Q28" s="162"/>
+      <c r="Q28" s="161"/>
       <c r="R28" s="29"/>
       <c r="S28" s="29"/>
       <c r="T28" s="30"/>
@@ -12510,23 +12634,23 @@
       <c r="Z28" s="31"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="191"/>
-      <c r="B29" s="162"/>
-      <c r="C29" s="192"/>
-      <c r="D29" s="162"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="162"/>
-      <c r="G29" s="183"/>
+      <c r="A29" s="183"/>
+      <c r="B29" s="161"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="190"/>
       <c r="H29" s="159"/>
-      <c r="I29" s="162"/>
-      <c r="J29" s="183"/>
-      <c r="K29" s="162"/>
-      <c r="L29" s="185"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="190"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="187"/>
       <c r="M29" s="159"/>
-      <c r="N29" s="162"/>
-      <c r="O29" s="185"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="187"/>
       <c r="P29" s="159"/>
-      <c r="Q29" s="162"/>
+      <c r="Q29" s="161"/>
       <c r="R29" s="29"/>
       <c r="S29" s="29"/>
       <c r="T29" s="30"/>
@@ -12538,23 +12662,23 @@
       <c r="Z29" s="31"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="191"/>
-      <c r="B30" s="162"/>
-      <c r="C30" s="192"/>
-      <c r="D30" s="162"/>
-      <c r="E30" s="192"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="183"/>
+      <c r="A30" s="183"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="184"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="184"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="190"/>
       <c r="H30" s="159"/>
-      <c r="I30" s="162"/>
-      <c r="J30" s="183"/>
-      <c r="K30" s="162"/>
-      <c r="L30" s="185"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="190"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="187"/>
       <c r="M30" s="159"/>
-      <c r="N30" s="162"/>
-      <c r="O30" s="185"/>
+      <c r="N30" s="161"/>
+      <c r="O30" s="187"/>
       <c r="P30" s="159"/>
-      <c r="Q30" s="162"/>
+      <c r="Q30" s="161"/>
       <c r="R30" s="29"/>
       <c r="S30" s="29"/>
       <c r="T30" s="30"/>
@@ -12566,21 +12690,21 @@
       <c r="Z30" s="31"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="194"/>
+      <c r="A31" s="185"/>
       <c r="B31" s="181"/>
-      <c r="C31" s="195"/>
+      <c r="C31" s="186"/>
       <c r="D31" s="181"/>
-      <c r="E31" s="195"/>
+      <c r="E31" s="186"/>
       <c r="F31" s="181"/>
-      <c r="G31" s="184"/>
+      <c r="G31" s="195"/>
       <c r="H31" s="180"/>
       <c r="I31" s="181"/>
-      <c r="J31" s="184"/>
+      <c r="J31" s="195"/>
       <c r="K31" s="181"/>
-      <c r="L31" s="186"/>
+      <c r="L31" s="188"/>
       <c r="M31" s="180"/>
       <c r="N31" s="181"/>
-      <c r="O31" s="186"/>
+      <c r="O31" s="188"/>
       <c r="P31" s="180"/>
       <c r="Q31" s="181"/>
       <c r="R31" s="32"/>
@@ -13580,6 +13704,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13604,118 +13840,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13738,70 +13862,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="216" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="206" t="s">
+      <c r="B1" s="216"/>
+      <c r="C1" s="217" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="207"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="209" t="s">
+      <c r="D1" s="218"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="220" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="211"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="222"/>
       <c r="N1" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="209" t="s">
+      <c r="O1" s="220" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="211"/>
+      <c r="P1" s="222"/>
       <c r="Q1" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="R1" s="209" t="s">
+      <c r="R1" s="220" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="211"/>
+      <c r="S1" s="222"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="205"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="206" t="s">
+      <c r="A2" s="216"/>
+      <c r="B2" s="216"/>
+      <c r="C2" s="217" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="207"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="211"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="219"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="221"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="221"/>
+      <c r="M2" s="222"/>
       <c r="N2" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="O2" s="212">
-        <v>46190</v>
-      </c>
-      <c r="P2" s="213"/>
+      <c r="O2" s="223">
+        <v>46199</v>
+      </c>
+      <c r="P2" s="224"/>
       <c r="Q2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="R2" s="214" t="s">
+      <c r="R2" s="225" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="215"/>
+      <c r="S2" s="226"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="36"/>
@@ -13831,1234 +13955,1056 @@
       <c r="B4" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="208" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="196" t="s">
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="208" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="197"/>
-      <c r="J4" s="197"/>
-      <c r="K4" s="197"/>
-      <c r="L4" s="197"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="196" t="s">
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="209"/>
+      <c r="M4" s="210"/>
+      <c r="N4" s="208" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="197"/>
-      <c r="P4" s="198"/>
+      <c r="O4" s="209"/>
+      <c r="P4" s="210"/>
       <c r="Q4" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="196" t="s">
+      <c r="R4" s="208" t="s">
         <v>72</v>
       </c>
-      <c r="S4" s="198"/>
+      <c r="S4" s="210"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1">
       <c r="A5" s="40">
         <v>1</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="199"/>
-      <c r="F5" s="199"/>
-      <c r="G5" s="199"/>
-      <c r="H5" s="199"/>
-      <c r="I5" s="199"/>
-      <c r="J5" s="199"/>
-      <c r="K5" s="199"/>
-      <c r="L5" s="199"/>
-      <c r="M5" s="199"/>
-      <c r="N5" s="200"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="202"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="203"/>
-      <c r="S5" s="204"/>
+      <c r="B5" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="204" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
+      <c r="F5" s="204"/>
+      <c r="G5" s="204"/>
+      <c r="H5" s="204" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="204"/>
+      <c r="J5" s="204"/>
+      <c r="K5" s="204"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="211" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" s="212"/>
+      <c r="P5" s="213"/>
+      <c r="Q5" s="41">
+        <v>46199</v>
+      </c>
+      <c r="R5" s="214"/>
+      <c r="S5" s="215"/>
     </row>
     <row r="6" spans="1:19" ht="33" customHeight="1">
       <c r="A6" s="42"/>
       <c r="B6" s="42"/>
-      <c r="C6" s="199"/>
-      <c r="D6" s="199"/>
-      <c r="E6" s="199"/>
-      <c r="F6" s="199"/>
-      <c r="G6" s="199"/>
-      <c r="H6" s="199"/>
-      <c r="I6" s="199"/>
-      <c r="J6" s="199"/>
-      <c r="K6" s="199"/>
-      <c r="L6" s="199"/>
-      <c r="M6" s="199"/>
-      <c r="N6" s="221"/>
-      <c r="O6" s="222"/>
-      <c r="P6" s="223"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="204"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="204"/>
+      <c r="G6" s="204"/>
+      <c r="H6" s="204"/>
+      <c r="I6" s="204"/>
+      <c r="J6" s="204"/>
+      <c r="K6" s="204"/>
+      <c r="L6" s="204"/>
+      <c r="M6" s="204"/>
+      <c r="N6" s="205"/>
+      <c r="O6" s="206"/>
+      <c r="P6" s="207"/>
       <c r="Q6" s="41"/>
-      <c r="R6" s="220"/>
-      <c r="S6" s="220"/>
+      <c r="R6" s="203"/>
+      <c r="S6" s="203"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="42"/>
       <c r="B7" s="42"/>
-      <c r="C7" s="199"/>
-      <c r="D7" s="199"/>
-      <c r="E7" s="199"/>
-      <c r="F7" s="199"/>
-      <c r="G7" s="199"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="221"/>
-      <c r="O7" s="218"/>
-      <c r="P7" s="219"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="204"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="204"/>
+      <c r="H7" s="196"/>
+      <c r="I7" s="196"/>
+      <c r="J7" s="196"/>
+      <c r="K7" s="196"/>
+      <c r="L7" s="196"/>
+      <c r="M7" s="196"/>
+      <c r="N7" s="205"/>
+      <c r="O7" s="201"/>
+      <c r="P7" s="202"/>
       <c r="Q7" s="41"/>
-      <c r="R7" s="220"/>
-      <c r="S7" s="220"/>
+      <c r="R7" s="203"/>
+      <c r="S7" s="203"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="42"/>
       <c r="B8" s="42"/>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
-      <c r="M8" s="216"/>
-      <c r="N8" s="217"/>
-      <c r="O8" s="218"/>
-      <c r="P8" s="219"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="196"/>
+      <c r="E8" s="196"/>
+      <c r="F8" s="196"/>
+      <c r="G8" s="196"/>
+      <c r="H8" s="196"/>
+      <c r="I8" s="196"/>
+      <c r="J8" s="196"/>
+      <c r="K8" s="196"/>
+      <c r="L8" s="196"/>
+      <c r="M8" s="196"/>
+      <c r="N8" s="200"/>
+      <c r="O8" s="201"/>
+      <c r="P8" s="202"/>
       <c r="Q8" s="43"/>
-      <c r="R8" s="220"/>
-      <c r="S8" s="220"/>
+      <c r="R8" s="203"/>
+      <c r="S8" s="203"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="42"/>
       <c r="B9" s="42"/>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="216"/>
-      <c r="H9" s="216"/>
-      <c r="I9" s="216"/>
-      <c r="J9" s="216"/>
-      <c r="K9" s="216"/>
-      <c r="L9" s="216"/>
-      <c r="M9" s="216"/>
-      <c r="N9" s="217"/>
-      <c r="O9" s="218"/>
-      <c r="P9" s="219"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="196"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="196"/>
+      <c r="H9" s="196"/>
+      <c r="I9" s="196"/>
+      <c r="J9" s="196"/>
+      <c r="K9" s="196"/>
+      <c r="L9" s="196"/>
+      <c r="M9" s="196"/>
+      <c r="N9" s="200"/>
+      <c r="O9" s="201"/>
+      <c r="P9" s="202"/>
       <c r="Q9" s="42"/>
-      <c r="R9" s="220"/>
-      <c r="S9" s="220"/>
+      <c r="R9" s="203"/>
+      <c r="S9" s="203"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="42"/>
       <c r="B10" s="42"/>
-      <c r="C10" s="216"/>
-      <c r="D10" s="216"/>
-      <c r="E10" s="216"/>
-      <c r="F10" s="216"/>
-      <c r="G10" s="216"/>
-      <c r="H10" s="224"/>
-      <c r="I10" s="225"/>
-      <c r="J10" s="225"/>
-      <c r="K10" s="225"/>
-      <c r="L10" s="225"/>
-      <c r="M10" s="226"/>
-      <c r="N10" s="217"/>
-      <c r="O10" s="218"/>
-      <c r="P10" s="219"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="196"/>
+      <c r="E10" s="196"/>
+      <c r="F10" s="196"/>
+      <c r="G10" s="196"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="198"/>
+      <c r="J10" s="198"/>
+      <c r="K10" s="198"/>
+      <c r="L10" s="198"/>
+      <c r="M10" s="199"/>
+      <c r="N10" s="200"/>
+      <c r="O10" s="201"/>
+      <c r="P10" s="202"/>
       <c r="Q10" s="43"/>
-      <c r="R10" s="220"/>
-      <c r="S10" s="220"/>
+      <c r="R10" s="203"/>
+      <c r="S10" s="203"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="42"/>
       <c r="B11" s="42"/>
-      <c r="C11" s="216"/>
-      <c r="D11" s="216"/>
-      <c r="E11" s="216"/>
-      <c r="F11" s="216"/>
-      <c r="G11" s="216"/>
-      <c r="H11" s="224"/>
-      <c r="I11" s="225"/>
-      <c r="J11" s="225"/>
-      <c r="K11" s="225"/>
-      <c r="L11" s="225"/>
-      <c r="M11" s="226"/>
-      <c r="N11" s="217"/>
-      <c r="O11" s="218"/>
-      <c r="P11" s="219"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="196"/>
+      <c r="E11" s="196"/>
+      <c r="F11" s="196"/>
+      <c r="G11" s="196"/>
+      <c r="H11" s="197"/>
+      <c r="I11" s="198"/>
+      <c r="J11" s="198"/>
+      <c r="K11" s="198"/>
+      <c r="L11" s="198"/>
+      <c r="M11" s="199"/>
+      <c r="N11" s="200"/>
+      <c r="O11" s="201"/>
+      <c r="P11" s="202"/>
       <c r="Q11" s="42"/>
-      <c r="R11" s="220"/>
-      <c r="S11" s="220"/>
+      <c r="R11" s="203"/>
+      <c r="S11" s="203"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="42"/>
       <c r="B12" s="42"/>
-      <c r="C12" s="216"/>
-      <c r="D12" s="216"/>
-      <c r="E12" s="216"/>
-      <c r="F12" s="216"/>
-      <c r="G12" s="216"/>
-      <c r="H12" s="224"/>
-      <c r="I12" s="225"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="225"/>
-      <c r="L12" s="225"/>
-      <c r="M12" s="226"/>
-      <c r="N12" s="217"/>
-      <c r="O12" s="218"/>
-      <c r="P12" s="219"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="196"/>
+      <c r="E12" s="196"/>
+      <c r="F12" s="196"/>
+      <c r="G12" s="196"/>
+      <c r="H12" s="197"/>
+      <c r="I12" s="198"/>
+      <c r="J12" s="198"/>
+      <c r="K12" s="198"/>
+      <c r="L12" s="198"/>
+      <c r="M12" s="199"/>
+      <c r="N12" s="200"/>
+      <c r="O12" s="201"/>
+      <c r="P12" s="202"/>
       <c r="Q12" s="42"/>
-      <c r="R12" s="220"/>
-      <c r="S12" s="220"/>
+      <c r="R12" s="203"/>
+      <c r="S12" s="203"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="42"/>
       <c r="B13" s="42"/>
-      <c r="C13" s="216"/>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="216"/>
-      <c r="G13" s="216"/>
-      <c r="H13" s="224"/>
-      <c r="I13" s="225"/>
-      <c r="J13" s="225"/>
-      <c r="K13" s="225"/>
-      <c r="L13" s="225"/>
-      <c r="M13" s="226"/>
-      <c r="N13" s="217"/>
-      <c r="O13" s="218"/>
-      <c r="P13" s="219"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="196"/>
+      <c r="E13" s="196"/>
+      <c r="F13" s="196"/>
+      <c r="G13" s="196"/>
+      <c r="H13" s="197"/>
+      <c r="I13" s="198"/>
+      <c r="J13" s="198"/>
+      <c r="K13" s="198"/>
+      <c r="L13" s="198"/>
+      <c r="M13" s="199"/>
+      <c r="N13" s="200"/>
+      <c r="O13" s="201"/>
+      <c r="P13" s="202"/>
       <c r="Q13" s="42"/>
-      <c r="R13" s="220"/>
-      <c r="S13" s="220"/>
+      <c r="R13" s="203"/>
+      <c r="S13" s="203"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="42"/>
       <c r="B14" s="42"/>
-      <c r="C14" s="216"/>
-      <c r="D14" s="216"/>
-      <c r="E14" s="216"/>
-      <c r="F14" s="216"/>
-      <c r="G14" s="216"/>
-      <c r="H14" s="224"/>
-      <c r="I14" s="225"/>
-      <c r="J14" s="225"/>
-      <c r="K14" s="225"/>
-      <c r="L14" s="225"/>
-      <c r="M14" s="226"/>
-      <c r="N14" s="217"/>
-      <c r="O14" s="218"/>
-      <c r="P14" s="219"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="196"/>
+      <c r="F14" s="196"/>
+      <c r="G14" s="196"/>
+      <c r="H14" s="197"/>
+      <c r="I14" s="198"/>
+      <c r="J14" s="198"/>
+      <c r="K14" s="198"/>
+      <c r="L14" s="198"/>
+      <c r="M14" s="199"/>
+      <c r="N14" s="200"/>
+      <c r="O14" s="201"/>
+      <c r="P14" s="202"/>
       <c r="Q14" s="42"/>
-      <c r="R14" s="220"/>
-      <c r="S14" s="220"/>
+      <c r="R14" s="203"/>
+      <c r="S14" s="203"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="42"/>
       <c r="B15" s="42"/>
-      <c r="C15" s="216"/>
-      <c r="D15" s="216"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="216"/>
-      <c r="G15" s="216"/>
-      <c r="H15" s="224"/>
-      <c r="I15" s="225"/>
-      <c r="J15" s="225"/>
-      <c r="K15" s="225"/>
-      <c r="L15" s="225"/>
-      <c r="M15" s="226"/>
-      <c r="N15" s="217"/>
-      <c r="O15" s="218"/>
-      <c r="P15" s="219"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="196"/>
+      <c r="E15" s="196"/>
+      <c r="F15" s="196"/>
+      <c r="G15" s="196"/>
+      <c r="H15" s="197"/>
+      <c r="I15" s="198"/>
+      <c r="J15" s="198"/>
+      <c r="K15" s="198"/>
+      <c r="L15" s="198"/>
+      <c r="M15" s="199"/>
+      <c r="N15" s="200"/>
+      <c r="O15" s="201"/>
+      <c r="P15" s="202"/>
       <c r="Q15" s="42"/>
-      <c r="R15" s="220"/>
-      <c r="S15" s="220"/>
+      <c r="R15" s="203"/>
+      <c r="S15" s="203"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="42"/>
       <c r="B16" s="42"/>
-      <c r="C16" s="216"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="216"/>
-      <c r="G16" s="216"/>
-      <c r="H16" s="224"/>
-      <c r="I16" s="225"/>
-      <c r="J16" s="225"/>
-      <c r="K16" s="225"/>
-      <c r="L16" s="225"/>
-      <c r="M16" s="226"/>
-      <c r="N16" s="217"/>
-      <c r="O16" s="218"/>
-      <c r="P16" s="219"/>
+      <c r="C16" s="196"/>
+      <c r="D16" s="196"/>
+      <c r="E16" s="196"/>
+      <c r="F16" s="196"/>
+      <c r="G16" s="196"/>
+      <c r="H16" s="197"/>
+      <c r="I16" s="198"/>
+      <c r="J16" s="198"/>
+      <c r="K16" s="198"/>
+      <c r="L16" s="198"/>
+      <c r="M16" s="199"/>
+      <c r="N16" s="200"/>
+      <c r="O16" s="201"/>
+      <c r="P16" s="202"/>
       <c r="Q16" s="42"/>
-      <c r="R16" s="220"/>
-      <c r="S16" s="220"/>
+      <c r="R16" s="203"/>
+      <c r="S16" s="203"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="42"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="216"/>
-      <c r="D17" s="216"/>
-      <c r="E17" s="216"/>
-      <c r="F17" s="216"/>
-      <c r="G17" s="216"/>
-      <c r="H17" s="224"/>
-      <c r="I17" s="225"/>
-      <c r="J17" s="225"/>
-      <c r="K17" s="225"/>
-      <c r="L17" s="225"/>
-      <c r="M17" s="226"/>
-      <c r="N17" s="217"/>
-      <c r="O17" s="218"/>
-      <c r="P17" s="219"/>
+      <c r="C17" s="196"/>
+      <c r="D17" s="196"/>
+      <c r="E17" s="196"/>
+      <c r="F17" s="196"/>
+      <c r="G17" s="196"/>
+      <c r="H17" s="197"/>
+      <c r="I17" s="198"/>
+      <c r="J17" s="198"/>
+      <c r="K17" s="198"/>
+      <c r="L17" s="198"/>
+      <c r="M17" s="199"/>
+      <c r="N17" s="200"/>
+      <c r="O17" s="201"/>
+      <c r="P17" s="202"/>
       <c r="Q17" s="42"/>
-      <c r="R17" s="220"/>
-      <c r="S17" s="220"/>
+      <c r="R17" s="203"/>
+      <c r="S17" s="203"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="42"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="216"/>
-      <c r="D18" s="216"/>
-      <c r="E18" s="216"/>
-      <c r="F18" s="216"/>
-      <c r="G18" s="216"/>
-      <c r="H18" s="224"/>
-      <c r="I18" s="225"/>
-      <c r="J18" s="225"/>
-      <c r="K18" s="225"/>
-      <c r="L18" s="225"/>
-      <c r="M18" s="226"/>
-      <c r="N18" s="217"/>
-      <c r="O18" s="218"/>
-      <c r="P18" s="219"/>
+      <c r="C18" s="196"/>
+      <c r="D18" s="196"/>
+      <c r="E18" s="196"/>
+      <c r="F18" s="196"/>
+      <c r="G18" s="196"/>
+      <c r="H18" s="197"/>
+      <c r="I18" s="198"/>
+      <c r="J18" s="198"/>
+      <c r="K18" s="198"/>
+      <c r="L18" s="198"/>
+      <c r="M18" s="199"/>
+      <c r="N18" s="200"/>
+      <c r="O18" s="201"/>
+      <c r="P18" s="202"/>
       <c r="Q18" s="42"/>
-      <c r="R18" s="220"/>
-      <c r="S18" s="220"/>
+      <c r="R18" s="203"/>
+      <c r="S18" s="203"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="42"/>
       <c r="B19" s="42"/>
-      <c r="C19" s="216"/>
-      <c r="D19" s="216"/>
-      <c r="E19" s="216"/>
-      <c r="F19" s="216"/>
-      <c r="G19" s="216"/>
-      <c r="H19" s="224"/>
-      <c r="I19" s="225"/>
-      <c r="J19" s="225"/>
-      <c r="K19" s="225"/>
-      <c r="L19" s="225"/>
-      <c r="M19" s="226"/>
-      <c r="N19" s="217"/>
-      <c r="O19" s="218"/>
-      <c r="P19" s="219"/>
+      <c r="C19" s="196"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="196"/>
+      <c r="G19" s="196"/>
+      <c r="H19" s="197"/>
+      <c r="I19" s="198"/>
+      <c r="J19" s="198"/>
+      <c r="K19" s="198"/>
+      <c r="L19" s="198"/>
+      <c r="M19" s="199"/>
+      <c r="N19" s="200"/>
+      <c r="O19" s="201"/>
+      <c r="P19" s="202"/>
       <c r="Q19" s="42"/>
-      <c r="R19" s="220"/>
-      <c r="S19" s="220"/>
+      <c r="R19" s="203"/>
+      <c r="S19" s="203"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="42"/>
       <c r="B20" s="42"/>
-      <c r="C20" s="216"/>
-      <c r="D20" s="216"/>
-      <c r="E20" s="216"/>
-      <c r="F20" s="216"/>
-      <c r="G20" s="216"/>
-      <c r="H20" s="224"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="225"/>
-      <c r="K20" s="225"/>
-      <c r="L20" s="225"/>
-      <c r="M20" s="226"/>
-      <c r="N20" s="217"/>
-      <c r="O20" s="218"/>
-      <c r="P20" s="219"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="196"/>
+      <c r="G20" s="196"/>
+      <c r="H20" s="197"/>
+      <c r="I20" s="198"/>
+      <c r="J20" s="198"/>
+      <c r="K20" s="198"/>
+      <c r="L20" s="198"/>
+      <c r="M20" s="199"/>
+      <c r="N20" s="200"/>
+      <c r="O20" s="201"/>
+      <c r="P20" s="202"/>
       <c r="Q20" s="42"/>
-      <c r="R20" s="220"/>
-      <c r="S20" s="220"/>
+      <c r="R20" s="203"/>
+      <c r="S20" s="203"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="42"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="216"/>
-      <c r="D21" s="216"/>
-      <c r="E21" s="216"/>
-      <c r="F21" s="216"/>
-      <c r="G21" s="216"/>
-      <c r="H21" s="224"/>
-      <c r="I21" s="225"/>
-      <c r="J21" s="225"/>
-      <c r="K21" s="225"/>
-      <c r="L21" s="225"/>
-      <c r="M21" s="226"/>
-      <c r="N21" s="217"/>
-      <c r="O21" s="218"/>
-      <c r="P21" s="219"/>
+      <c r="C21" s="196"/>
+      <c r="D21" s="196"/>
+      <c r="E21" s="196"/>
+      <c r="F21" s="196"/>
+      <c r="G21" s="196"/>
+      <c r="H21" s="197"/>
+      <c r="I21" s="198"/>
+      <c r="J21" s="198"/>
+      <c r="K21" s="198"/>
+      <c r="L21" s="198"/>
+      <c r="M21" s="199"/>
+      <c r="N21" s="200"/>
+      <c r="O21" s="201"/>
+      <c r="P21" s="202"/>
       <c r="Q21" s="42"/>
-      <c r="R21" s="220"/>
-      <c r="S21" s="220"/>
+      <c r="R21" s="203"/>
+      <c r="S21" s="203"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
-      <c r="C22" s="216"/>
-      <c r="D22" s="216"/>
-      <c r="E22" s="216"/>
-      <c r="F22" s="216"/>
-      <c r="G22" s="216"/>
-      <c r="H22" s="224"/>
-      <c r="I22" s="225"/>
-      <c r="J22" s="225"/>
-      <c r="K22" s="225"/>
-      <c r="L22" s="225"/>
-      <c r="M22" s="226"/>
-      <c r="N22" s="217"/>
-      <c r="O22" s="218"/>
-      <c r="P22" s="219"/>
+      <c r="C22" s="196"/>
+      <c r="D22" s="196"/>
+      <c r="E22" s="196"/>
+      <c r="F22" s="196"/>
+      <c r="G22" s="196"/>
+      <c r="H22" s="197"/>
+      <c r="I22" s="198"/>
+      <c r="J22" s="198"/>
+      <c r="K22" s="198"/>
+      <c r="L22" s="198"/>
+      <c r="M22" s="199"/>
+      <c r="N22" s="200"/>
+      <c r="O22" s="201"/>
+      <c r="P22" s="202"/>
       <c r="Q22" s="42"/>
-      <c r="R22" s="220"/>
-      <c r="S22" s="220"/>
+      <c r="R22" s="203"/>
+      <c r="S22" s="203"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="42"/>
       <c r="B23" s="42"/>
-      <c r="C23" s="216"/>
-      <c r="D23" s="216"/>
-      <c r="E23" s="216"/>
-      <c r="F23" s="216"/>
-      <c r="G23" s="216"/>
-      <c r="H23" s="224"/>
-      <c r="I23" s="225"/>
-      <c r="J23" s="225"/>
-      <c r="K23" s="225"/>
-      <c r="L23" s="225"/>
-      <c r="M23" s="226"/>
-      <c r="N23" s="217"/>
-      <c r="O23" s="218"/>
-      <c r="P23" s="219"/>
+      <c r="C23" s="196"/>
+      <c r="D23" s="196"/>
+      <c r="E23" s="196"/>
+      <c r="F23" s="196"/>
+      <c r="G23" s="196"/>
+      <c r="H23" s="197"/>
+      <c r="I23" s="198"/>
+      <c r="J23" s="198"/>
+      <c r="K23" s="198"/>
+      <c r="L23" s="198"/>
+      <c r="M23" s="199"/>
+      <c r="N23" s="200"/>
+      <c r="O23" s="201"/>
+      <c r="P23" s="202"/>
       <c r="Q23" s="42"/>
-      <c r="R23" s="220"/>
-      <c r="S23" s="220"/>
+      <c r="R23" s="203"/>
+      <c r="S23" s="203"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="42"/>
       <c r="B24" s="42"/>
-      <c r="C24" s="216"/>
-      <c r="D24" s="216"/>
-      <c r="E24" s="216"/>
-      <c r="F24" s="216"/>
-      <c r="G24" s="216"/>
-      <c r="H24" s="224"/>
-      <c r="I24" s="225"/>
-      <c r="J24" s="225"/>
-      <c r="K24" s="225"/>
-      <c r="L24" s="225"/>
-      <c r="M24" s="226"/>
-      <c r="N24" s="217"/>
-      <c r="O24" s="218"/>
-      <c r="P24" s="219"/>
+      <c r="C24" s="196"/>
+      <c r="D24" s="196"/>
+      <c r="E24" s="196"/>
+      <c r="F24" s="196"/>
+      <c r="G24" s="196"/>
+      <c r="H24" s="197"/>
+      <c r="I24" s="198"/>
+      <c r="J24" s="198"/>
+      <c r="K24" s="198"/>
+      <c r="L24" s="198"/>
+      <c r="M24" s="199"/>
+      <c r="N24" s="200"/>
+      <c r="O24" s="201"/>
+      <c r="P24" s="202"/>
       <c r="Q24" s="42"/>
-      <c r="R24" s="220"/>
-      <c r="S24" s="220"/>
+      <c r="R24" s="203"/>
+      <c r="S24" s="203"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="42"/>
       <c r="B25" s="42"/>
-      <c r="C25" s="216"/>
-      <c r="D25" s="216"/>
-      <c r="E25" s="216"/>
-      <c r="F25" s="216"/>
-      <c r="G25" s="216"/>
-      <c r="H25" s="224"/>
-      <c r="I25" s="225"/>
-      <c r="J25" s="225"/>
-      <c r="K25" s="225"/>
-      <c r="L25" s="225"/>
-      <c r="M25" s="226"/>
-      <c r="N25" s="217"/>
-      <c r="O25" s="218"/>
-      <c r="P25" s="219"/>
+      <c r="C25" s="196"/>
+      <c r="D25" s="196"/>
+      <c r="E25" s="196"/>
+      <c r="F25" s="196"/>
+      <c r="G25" s="196"/>
+      <c r="H25" s="197"/>
+      <c r="I25" s="198"/>
+      <c r="J25" s="198"/>
+      <c r="K25" s="198"/>
+      <c r="L25" s="198"/>
+      <c r="M25" s="199"/>
+      <c r="N25" s="200"/>
+      <c r="O25" s="201"/>
+      <c r="P25" s="202"/>
       <c r="Q25" s="42"/>
-      <c r="R25" s="220"/>
-      <c r="S25" s="220"/>
+      <c r="R25" s="203"/>
+      <c r="S25" s="203"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="216"/>
-      <c r="D26" s="216"/>
-      <c r="E26" s="216"/>
-      <c r="F26" s="216"/>
-      <c r="G26" s="216"/>
-      <c r="H26" s="224"/>
-      <c r="I26" s="225"/>
-      <c r="J26" s="225"/>
-      <c r="K26" s="225"/>
-      <c r="L26" s="225"/>
-      <c r="M26" s="226"/>
-      <c r="N26" s="217"/>
-      <c r="O26" s="218"/>
-      <c r="P26" s="219"/>
+      <c r="C26" s="196"/>
+      <c r="D26" s="196"/>
+      <c r="E26" s="196"/>
+      <c r="F26" s="196"/>
+      <c r="G26" s="196"/>
+      <c r="H26" s="197"/>
+      <c r="I26" s="198"/>
+      <c r="J26" s="198"/>
+      <c r="K26" s="198"/>
+      <c r="L26" s="198"/>
+      <c r="M26" s="199"/>
+      <c r="N26" s="200"/>
+      <c r="O26" s="201"/>
+      <c r="P26" s="202"/>
       <c r="Q26" s="42"/>
-      <c r="R26" s="220"/>
-      <c r="S26" s="220"/>
+      <c r="R26" s="203"/>
+      <c r="S26" s="203"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
-      <c r="C27" s="216"/>
-      <c r="D27" s="216"/>
-      <c r="E27" s="216"/>
-      <c r="F27" s="216"/>
-      <c r="G27" s="216"/>
-      <c r="H27" s="224"/>
-      <c r="I27" s="225"/>
-      <c r="J27" s="225"/>
-      <c r="K27" s="225"/>
-      <c r="L27" s="225"/>
-      <c r="M27" s="226"/>
-      <c r="N27" s="217"/>
-      <c r="O27" s="218"/>
-      <c r="P27" s="219"/>
+      <c r="C27" s="196"/>
+      <c r="D27" s="196"/>
+      <c r="E27" s="196"/>
+      <c r="F27" s="196"/>
+      <c r="G27" s="196"/>
+      <c r="H27" s="197"/>
+      <c r="I27" s="198"/>
+      <c r="J27" s="198"/>
+      <c r="K27" s="198"/>
+      <c r="L27" s="198"/>
+      <c r="M27" s="199"/>
+      <c r="N27" s="200"/>
+      <c r="O27" s="201"/>
+      <c r="P27" s="202"/>
       <c r="Q27" s="42"/>
-      <c r="R27" s="220"/>
-      <c r="S27" s="220"/>
+      <c r="R27" s="203"/>
+      <c r="S27" s="203"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="42"/>
       <c r="B28" s="42"/>
-      <c r="C28" s="216"/>
-      <c r="D28" s="216"/>
-      <c r="E28" s="216"/>
-      <c r="F28" s="216"/>
-      <c r="G28" s="216"/>
-      <c r="H28" s="224"/>
-      <c r="I28" s="225"/>
-      <c r="J28" s="225"/>
-      <c r="K28" s="225"/>
-      <c r="L28" s="225"/>
-      <c r="M28" s="226"/>
-      <c r="N28" s="217"/>
-      <c r="O28" s="218"/>
-      <c r="P28" s="219"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="196"/>
+      <c r="E28" s="196"/>
+      <c r="F28" s="196"/>
+      <c r="G28" s="196"/>
+      <c r="H28" s="197"/>
+      <c r="I28" s="198"/>
+      <c r="J28" s="198"/>
+      <c r="K28" s="198"/>
+      <c r="L28" s="198"/>
+      <c r="M28" s="199"/>
+      <c r="N28" s="200"/>
+      <c r="O28" s="201"/>
+      <c r="P28" s="202"/>
       <c r="Q28" s="42"/>
-      <c r="R28" s="220"/>
-      <c r="S28" s="220"/>
+      <c r="R28" s="203"/>
+      <c r="S28" s="203"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="42"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="216"/>
-      <c r="D29" s="216"/>
-      <c r="E29" s="216"/>
-      <c r="F29" s="216"/>
-      <c r="G29" s="216"/>
-      <c r="H29" s="224"/>
-      <c r="I29" s="225"/>
-      <c r="J29" s="225"/>
-      <c r="K29" s="225"/>
-      <c r="L29" s="225"/>
-      <c r="M29" s="226"/>
-      <c r="N29" s="217"/>
-      <c r="O29" s="218"/>
-      <c r="P29" s="219"/>
+      <c r="C29" s="196"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="196"/>
+      <c r="G29" s="196"/>
+      <c r="H29" s="197"/>
+      <c r="I29" s="198"/>
+      <c r="J29" s="198"/>
+      <c r="K29" s="198"/>
+      <c r="L29" s="198"/>
+      <c r="M29" s="199"/>
+      <c r="N29" s="200"/>
+      <c r="O29" s="201"/>
+      <c r="P29" s="202"/>
       <c r="Q29" s="42"/>
-      <c r="R29" s="220"/>
-      <c r="S29" s="220"/>
+      <c r="R29" s="203"/>
+      <c r="S29" s="203"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="42"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="216"/>
-      <c r="D30" s="216"/>
-      <c r="E30" s="216"/>
-      <c r="F30" s="216"/>
-      <c r="G30" s="216"/>
-      <c r="H30" s="224"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="225"/>
-      <c r="K30" s="225"/>
-      <c r="L30" s="225"/>
-      <c r="M30" s="226"/>
-      <c r="N30" s="217"/>
-      <c r="O30" s="218"/>
-      <c r="P30" s="219"/>
+      <c r="C30" s="196"/>
+      <c r="D30" s="196"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="196"/>
+      <c r="G30" s="196"/>
+      <c r="H30" s="197"/>
+      <c r="I30" s="198"/>
+      <c r="J30" s="198"/>
+      <c r="K30" s="198"/>
+      <c r="L30" s="198"/>
+      <c r="M30" s="199"/>
+      <c r="N30" s="200"/>
+      <c r="O30" s="201"/>
+      <c r="P30" s="202"/>
       <c r="Q30" s="42"/>
-      <c r="R30" s="220"/>
-      <c r="S30" s="220"/>
+      <c r="R30" s="203"/>
+      <c r="S30" s="203"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="42"/>
       <c r="B31" s="42"/>
-      <c r="C31" s="216"/>
-      <c r="D31" s="216"/>
-      <c r="E31" s="216"/>
-      <c r="F31" s="216"/>
-      <c r="G31" s="216"/>
-      <c r="H31" s="224"/>
-      <c r="I31" s="225"/>
-      <c r="J31" s="225"/>
-      <c r="K31" s="225"/>
-      <c r="L31" s="225"/>
-      <c r="M31" s="226"/>
-      <c r="N31" s="217"/>
-      <c r="O31" s="218"/>
-      <c r="P31" s="219"/>
+      <c r="C31" s="196"/>
+      <c r="D31" s="196"/>
+      <c r="E31" s="196"/>
+      <c r="F31" s="196"/>
+      <c r="G31" s="196"/>
+      <c r="H31" s="197"/>
+      <c r="I31" s="198"/>
+      <c r="J31" s="198"/>
+      <c r="K31" s="198"/>
+      <c r="L31" s="198"/>
+      <c r="M31" s="199"/>
+      <c r="N31" s="200"/>
+      <c r="O31" s="201"/>
+      <c r="P31" s="202"/>
       <c r="Q31" s="42"/>
-      <c r="R31" s="220"/>
-      <c r="S31" s="220"/>
+      <c r="R31" s="203"/>
+      <c r="S31" s="203"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="42"/>
       <c r="B32" s="42"/>
-      <c r="C32" s="216"/>
-      <c r="D32" s="216"/>
-      <c r="E32" s="216"/>
-      <c r="F32" s="216"/>
-      <c r="G32" s="216"/>
-      <c r="H32" s="224"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="225"/>
-      <c r="K32" s="225"/>
-      <c r="L32" s="225"/>
-      <c r="M32" s="226"/>
-      <c r="N32" s="217"/>
-      <c r="O32" s="218"/>
-      <c r="P32" s="219"/>
+      <c r="C32" s="196"/>
+      <c r="D32" s="196"/>
+      <c r="E32" s="196"/>
+      <c r="F32" s="196"/>
+      <c r="G32" s="196"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="198"/>
+      <c r="L32" s="198"/>
+      <c r="M32" s="199"/>
+      <c r="N32" s="200"/>
+      <c r="O32" s="201"/>
+      <c r="P32" s="202"/>
       <c r="Q32" s="42"/>
-      <c r="R32" s="220"/>
-      <c r="S32" s="220"/>
+      <c r="R32" s="203"/>
+      <c r="S32" s="203"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="42"/>
       <c r="B33" s="42"/>
-      <c r="C33" s="216"/>
-      <c r="D33" s="216"/>
-      <c r="E33" s="216"/>
-      <c r="F33" s="216"/>
-      <c r="G33" s="216"/>
-      <c r="H33" s="224"/>
-      <c r="I33" s="225"/>
-      <c r="J33" s="225"/>
-      <c r="K33" s="225"/>
-      <c r="L33" s="225"/>
-      <c r="M33" s="226"/>
-      <c r="N33" s="217"/>
-      <c r="O33" s="218"/>
-      <c r="P33" s="219"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="196"/>
+      <c r="E33" s="196"/>
+      <c r="F33" s="196"/>
+      <c r="G33" s="196"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="198"/>
+      <c r="J33" s="198"/>
+      <c r="K33" s="198"/>
+      <c r="L33" s="198"/>
+      <c r="M33" s="199"/>
+      <c r="N33" s="200"/>
+      <c r="O33" s="201"/>
+      <c r="P33" s="202"/>
       <c r="Q33" s="42"/>
-      <c r="R33" s="220"/>
-      <c r="S33" s="220"/>
+      <c r="R33" s="203"/>
+      <c r="S33" s="203"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="42"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="216"/>
-      <c r="D34" s="216"/>
-      <c r="E34" s="216"/>
-      <c r="F34" s="216"/>
-      <c r="G34" s="216"/>
-      <c r="H34" s="224"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
-      <c r="L34" s="225"/>
-      <c r="M34" s="226"/>
-      <c r="N34" s="217"/>
-      <c r="O34" s="218"/>
-      <c r="P34" s="219"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
+      <c r="E34" s="196"/>
+      <c r="F34" s="196"/>
+      <c r="G34" s="196"/>
+      <c r="H34" s="197"/>
+      <c r="I34" s="198"/>
+      <c r="J34" s="198"/>
+      <c r="K34" s="198"/>
+      <c r="L34" s="198"/>
+      <c r="M34" s="199"/>
+      <c r="N34" s="200"/>
+      <c r="O34" s="201"/>
+      <c r="P34" s="202"/>
       <c r="Q34" s="42"/>
-      <c r="R34" s="220"/>
-      <c r="S34" s="220"/>
+      <c r="R34" s="203"/>
+      <c r="S34" s="203"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="42"/>
       <c r="B35" s="42"/>
-      <c r="C35" s="216"/>
-      <c r="D35" s="216"/>
-      <c r="E35" s="216"/>
-      <c r="F35" s="216"/>
-      <c r="G35" s="216"/>
-      <c r="H35" s="224"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
-      <c r="L35" s="225"/>
-      <c r="M35" s="226"/>
-      <c r="N35" s="217"/>
-      <c r="O35" s="218"/>
-      <c r="P35" s="219"/>
+      <c r="C35" s="196"/>
+      <c r="D35" s="196"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="197"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="198"/>
+      <c r="K35" s="198"/>
+      <c r="L35" s="198"/>
+      <c r="M35" s="199"/>
+      <c r="N35" s="200"/>
+      <c r="O35" s="201"/>
+      <c r="P35" s="202"/>
       <c r="Q35" s="42"/>
-      <c r="R35" s="220"/>
-      <c r="S35" s="220"/>
+      <c r="R35" s="203"/>
+      <c r="S35" s="203"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="42"/>
       <c r="B36" s="42"/>
-      <c r="C36" s="216"/>
-      <c r="D36" s="216"/>
-      <c r="E36" s="216"/>
-      <c r="F36" s="216"/>
-      <c r="G36" s="216"/>
-      <c r="H36" s="224"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="225"/>
-      <c r="L36" s="225"/>
-      <c r="M36" s="226"/>
-      <c r="N36" s="217"/>
-      <c r="O36" s="218"/>
-      <c r="P36" s="219"/>
+      <c r="C36" s="196"/>
+      <c r="D36" s="196"/>
+      <c r="E36" s="196"/>
+      <c r="F36" s="196"/>
+      <c r="G36" s="196"/>
+      <c r="H36" s="197"/>
+      <c r="I36" s="198"/>
+      <c r="J36" s="198"/>
+      <c r="K36" s="198"/>
+      <c r="L36" s="198"/>
+      <c r="M36" s="199"/>
+      <c r="N36" s="200"/>
+      <c r="O36" s="201"/>
+      <c r="P36" s="202"/>
       <c r="Q36" s="42"/>
-      <c r="R36" s="220"/>
-      <c r="S36" s="220"/>
+      <c r="R36" s="203"/>
+      <c r="S36" s="203"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="42"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="216"/>
-      <c r="D37" s="216"/>
-      <c r="E37" s="216"/>
-      <c r="F37" s="216"/>
-      <c r="G37" s="216"/>
-      <c r="H37" s="224"/>
-      <c r="I37" s="225"/>
-      <c r="J37" s="225"/>
-      <c r="K37" s="225"/>
-      <c r="L37" s="225"/>
-      <c r="M37" s="226"/>
-      <c r="N37" s="217"/>
-      <c r="O37" s="218"/>
-      <c r="P37" s="219"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="196"/>
+      <c r="E37" s="196"/>
+      <c r="F37" s="196"/>
+      <c r="G37" s="196"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="198"/>
+      <c r="J37" s="198"/>
+      <c r="K37" s="198"/>
+      <c r="L37" s="198"/>
+      <c r="M37" s="199"/>
+      <c r="N37" s="200"/>
+      <c r="O37" s="201"/>
+      <c r="P37" s="202"/>
       <c r="Q37" s="42"/>
-      <c r="R37" s="220"/>
-      <c r="S37" s="220"/>
+      <c r="R37" s="203"/>
+      <c r="S37" s="203"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="42"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="216"/>
-      <c r="D38" s="216"/>
-      <c r="E38" s="216"/>
-      <c r="F38" s="216"/>
-      <c r="G38" s="216"/>
-      <c r="H38" s="224"/>
-      <c r="I38" s="225"/>
-      <c r="J38" s="225"/>
-      <c r="K38" s="225"/>
-      <c r="L38" s="225"/>
-      <c r="M38" s="226"/>
-      <c r="N38" s="217"/>
-      <c r="O38" s="218"/>
-      <c r="P38" s="219"/>
+      <c r="C38" s="196"/>
+      <c r="D38" s="196"/>
+      <c r="E38" s="196"/>
+      <c r="F38" s="196"/>
+      <c r="G38" s="196"/>
+      <c r="H38" s="197"/>
+      <c r="I38" s="198"/>
+      <c r="J38" s="198"/>
+      <c r="K38" s="198"/>
+      <c r="L38" s="198"/>
+      <c r="M38" s="199"/>
+      <c r="N38" s="200"/>
+      <c r="O38" s="201"/>
+      <c r="P38" s="202"/>
       <c r="Q38" s="42"/>
-      <c r="R38" s="220"/>
-      <c r="S38" s="220"/>
+      <c r="R38" s="203"/>
+      <c r="S38" s="203"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="42"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="216"/>
-      <c r="D39" s="216"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="216"/>
-      <c r="H39" s="224"/>
-      <c r="I39" s="225"/>
-      <c r="J39" s="225"/>
-      <c r="K39" s="225"/>
-      <c r="L39" s="225"/>
-      <c r="M39" s="226"/>
-      <c r="N39" s="217"/>
-      <c r="O39" s="218"/>
-      <c r="P39" s="219"/>
+      <c r="C39" s="196"/>
+      <c r="D39" s="196"/>
+      <c r="E39" s="196"/>
+      <c r="F39" s="196"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="198"/>
+      <c r="J39" s="198"/>
+      <c r="K39" s="198"/>
+      <c r="L39" s="198"/>
+      <c r="M39" s="199"/>
+      <c r="N39" s="200"/>
+      <c r="O39" s="201"/>
+      <c r="P39" s="202"/>
       <c r="Q39" s="42"/>
-      <c r="R39" s="220"/>
-      <c r="S39" s="220"/>
+      <c r="R39" s="203"/>
+      <c r="S39" s="203"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="42"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="216"/>
-      <c r="D40" s="216"/>
-      <c r="E40" s="216"/>
-      <c r="F40" s="216"/>
-      <c r="G40" s="216"/>
-      <c r="H40" s="224"/>
-      <c r="I40" s="225"/>
-      <c r="J40" s="225"/>
-      <c r="K40" s="225"/>
-      <c r="L40" s="225"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="217"/>
-      <c r="O40" s="218"/>
-      <c r="P40" s="219"/>
+      <c r="C40" s="196"/>
+      <c r="D40" s="196"/>
+      <c r="E40" s="196"/>
+      <c r="F40" s="196"/>
+      <c r="G40" s="196"/>
+      <c r="H40" s="197"/>
+      <c r="I40" s="198"/>
+      <c r="J40" s="198"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+      <c r="M40" s="199"/>
+      <c r="N40" s="200"/>
+      <c r="O40" s="201"/>
+      <c r="P40" s="202"/>
       <c r="Q40" s="42"/>
-      <c r="R40" s="220"/>
-      <c r="S40" s="220"/>
+      <c r="R40" s="203"/>
+      <c r="S40" s="203"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="42"/>
       <c r="B41" s="42"/>
-      <c r="C41" s="216"/>
-      <c r="D41" s="216"/>
-      <c r="E41" s="216"/>
-      <c r="F41" s="216"/>
-      <c r="G41" s="216"/>
-      <c r="H41" s="224"/>
-      <c r="I41" s="225"/>
-      <c r="J41" s="225"/>
-      <c r="K41" s="225"/>
-      <c r="L41" s="225"/>
-      <c r="M41" s="226"/>
-      <c r="N41" s="217"/>
-      <c r="O41" s="218"/>
-      <c r="P41" s="219"/>
+      <c r="C41" s="196"/>
+      <c r="D41" s="196"/>
+      <c r="E41" s="196"/>
+      <c r="F41" s="196"/>
+      <c r="G41" s="196"/>
+      <c r="H41" s="197"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="199"/>
+      <c r="N41" s="200"/>
+      <c r="O41" s="201"/>
+      <c r="P41" s="202"/>
       <c r="Q41" s="42"/>
-      <c r="R41" s="220"/>
-      <c r="S41" s="220"/>
+      <c r="R41" s="203"/>
+      <c r="S41" s="203"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="42"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="216"/>
-      <c r="D42" s="216"/>
-      <c r="E42" s="216"/>
-      <c r="F42" s="216"/>
-      <c r="G42" s="216"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="225"/>
-      <c r="J42" s="225"/>
-      <c r="K42" s="225"/>
-      <c r="L42" s="225"/>
-      <c r="M42" s="226"/>
-      <c r="N42" s="217"/>
-      <c r="O42" s="218"/>
-      <c r="P42" s="219"/>
+      <c r="C42" s="196"/>
+      <c r="D42" s="196"/>
+      <c r="E42" s="196"/>
+      <c r="F42" s="196"/>
+      <c r="G42" s="196"/>
+      <c r="H42" s="197"/>
+      <c r="I42" s="198"/>
+      <c r="J42" s="198"/>
+      <c r="K42" s="198"/>
+      <c r="L42" s="198"/>
+      <c r="M42" s="199"/>
+      <c r="N42" s="200"/>
+      <c r="O42" s="201"/>
+      <c r="P42" s="202"/>
       <c r="Q42" s="42"/>
-      <c r="R42" s="220"/>
-      <c r="S42" s="220"/>
+      <c r="R42" s="203"/>
+      <c r="S42" s="203"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="42"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="216"/>
-      <c r="D43" s="216"/>
-      <c r="E43" s="216"/>
-      <c r="F43" s="216"/>
-      <c r="G43" s="216"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="225"/>
-      <c r="J43" s="225"/>
-      <c r="K43" s="225"/>
-      <c r="L43" s="225"/>
-      <c r="M43" s="226"/>
-      <c r="N43" s="217"/>
-      <c r="O43" s="218"/>
-      <c r="P43" s="219"/>
+      <c r="C43" s="196"/>
+      <c r="D43" s="196"/>
+      <c r="E43" s="196"/>
+      <c r="F43" s="196"/>
+      <c r="G43" s="196"/>
+      <c r="H43" s="197"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="199"/>
+      <c r="N43" s="200"/>
+      <c r="O43" s="201"/>
+      <c r="P43" s="202"/>
       <c r="Q43" s="42"/>
-      <c r="R43" s="220"/>
-      <c r="S43" s="220"/>
+      <c r="R43" s="203"/>
+      <c r="S43" s="203"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="42"/>
       <c r="B44" s="42"/>
-      <c r="C44" s="216"/>
-      <c r="D44" s="216"/>
-      <c r="E44" s="216"/>
-      <c r="F44" s="216"/>
-      <c r="G44" s="216"/>
-      <c r="H44" s="224"/>
-      <c r="I44" s="225"/>
-      <c r="J44" s="225"/>
-      <c r="K44" s="225"/>
-      <c r="L44" s="225"/>
-      <c r="M44" s="226"/>
-      <c r="N44" s="217"/>
-      <c r="O44" s="218"/>
-      <c r="P44" s="219"/>
+      <c r="C44" s="196"/>
+      <c r="D44" s="196"/>
+      <c r="E44" s="196"/>
+      <c r="F44" s="196"/>
+      <c r="G44" s="196"/>
+      <c r="H44" s="197"/>
+      <c r="I44" s="198"/>
+      <c r="J44" s="198"/>
+      <c r="K44" s="198"/>
+      <c r="L44" s="198"/>
+      <c r="M44" s="199"/>
+      <c r="N44" s="200"/>
+      <c r="O44" s="201"/>
+      <c r="P44" s="202"/>
       <c r="Q44" s="42"/>
-      <c r="R44" s="220"/>
-      <c r="S44" s="220"/>
+      <c r="R44" s="203"/>
+      <c r="S44" s="203"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="42"/>
       <c r="B45" s="42"/>
-      <c r="C45" s="216"/>
-      <c r="D45" s="216"/>
-      <c r="E45" s="216"/>
-      <c r="F45" s="216"/>
-      <c r="G45" s="216"/>
-      <c r="H45" s="224"/>
-      <c r="I45" s="225"/>
-      <c r="J45" s="225"/>
-      <c r="K45" s="225"/>
-      <c r="L45" s="225"/>
-      <c r="M45" s="226"/>
-      <c r="N45" s="217"/>
-      <c r="O45" s="218"/>
-      <c r="P45" s="219"/>
+      <c r="C45" s="196"/>
+      <c r="D45" s="196"/>
+      <c r="E45" s="196"/>
+      <c r="F45" s="196"/>
+      <c r="G45" s="196"/>
+      <c r="H45" s="197"/>
+      <c r="I45" s="198"/>
+      <c r="J45" s="198"/>
+      <c r="K45" s="198"/>
+      <c r="L45" s="198"/>
+      <c r="M45" s="199"/>
+      <c r="N45" s="200"/>
+      <c r="O45" s="201"/>
+      <c r="P45" s="202"/>
       <c r="Q45" s="42"/>
-      <c r="R45" s="220"/>
-      <c r="S45" s="220"/>
+      <c r="R45" s="203"/>
+      <c r="S45" s="203"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="42"/>
       <c r="B46" s="42"/>
-      <c r="C46" s="216"/>
-      <c r="D46" s="216"/>
-      <c r="E46" s="216"/>
-      <c r="F46" s="216"/>
-      <c r="G46" s="216"/>
-      <c r="H46" s="224"/>
-      <c r="I46" s="225"/>
-      <c r="J46" s="225"/>
-      <c r="K46" s="225"/>
-      <c r="L46" s="225"/>
-      <c r="M46" s="226"/>
-      <c r="N46" s="217"/>
-      <c r="O46" s="218"/>
-      <c r="P46" s="219"/>
+      <c r="C46" s="196"/>
+      <c r="D46" s="196"/>
+      <c r="E46" s="196"/>
+      <c r="F46" s="196"/>
+      <c r="G46" s="196"/>
+      <c r="H46" s="197"/>
+      <c r="I46" s="198"/>
+      <c r="J46" s="198"/>
+      <c r="K46" s="198"/>
+      <c r="L46" s="198"/>
+      <c r="M46" s="199"/>
+      <c r="N46" s="200"/>
+      <c r="O46" s="201"/>
+      <c r="P46" s="202"/>
       <c r="Q46" s="42"/>
-      <c r="R46" s="220"/>
-      <c r="S46" s="220"/>
+      <c r="R46" s="203"/>
+      <c r="S46" s="203"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="42"/>
       <c r="B47" s="42"/>
-      <c r="C47" s="216"/>
-      <c r="D47" s="216"/>
-      <c r="E47" s="216"/>
-      <c r="F47" s="216"/>
-      <c r="G47" s="216"/>
-      <c r="H47" s="224"/>
-      <c r="I47" s="225"/>
-      <c r="J47" s="225"/>
-      <c r="K47" s="225"/>
-      <c r="L47" s="225"/>
-      <c r="M47" s="226"/>
-      <c r="N47" s="217"/>
-      <c r="O47" s="218"/>
-      <c r="P47" s="219"/>
+      <c r="C47" s="196"/>
+      <c r="D47" s="196"/>
+      <c r="E47" s="196"/>
+      <c r="F47" s="196"/>
+      <c r="G47" s="196"/>
+      <c r="H47" s="197"/>
+      <c r="I47" s="198"/>
+      <c r="J47" s="198"/>
+      <c r="K47" s="198"/>
+      <c r="L47" s="198"/>
+      <c r="M47" s="199"/>
+      <c r="N47" s="200"/>
+      <c r="O47" s="201"/>
+      <c r="P47" s="202"/>
       <c r="Q47" s="42"/>
-      <c r="R47" s="220"/>
-      <c r="S47" s="220"/>
+      <c r="R47" s="203"/>
+      <c r="S47" s="203"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="42"/>
       <c r="B48" s="42"/>
-      <c r="C48" s="216"/>
-      <c r="D48" s="216"/>
-      <c r="E48" s="216"/>
-      <c r="F48" s="216"/>
-      <c r="G48" s="216"/>
-      <c r="H48" s="224"/>
-      <c r="I48" s="225"/>
-      <c r="J48" s="225"/>
-      <c r="K48" s="225"/>
-      <c r="L48" s="225"/>
-      <c r="M48" s="226"/>
-      <c r="N48" s="217"/>
-      <c r="O48" s="218"/>
-      <c r="P48" s="219"/>
+      <c r="C48" s="196"/>
+      <c r="D48" s="196"/>
+      <c r="E48" s="196"/>
+      <c r="F48" s="196"/>
+      <c r="G48" s="196"/>
+      <c r="H48" s="197"/>
+      <c r="I48" s="198"/>
+      <c r="J48" s="198"/>
+      <c r="K48" s="198"/>
+      <c r="L48" s="198"/>
+      <c r="M48" s="199"/>
+      <c r="N48" s="200"/>
+      <c r="O48" s="201"/>
+      <c r="P48" s="202"/>
       <c r="Q48" s="42"/>
-      <c r="R48" s="220"/>
-      <c r="S48" s="220"/>
+      <c r="R48" s="203"/>
+      <c r="S48" s="203"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="42"/>
       <c r="B49" s="42"/>
-      <c r="C49" s="216"/>
-      <c r="D49" s="216"/>
-      <c r="E49" s="216"/>
-      <c r="F49" s="216"/>
-      <c r="G49" s="216"/>
-      <c r="H49" s="224"/>
-      <c r="I49" s="225"/>
-      <c r="J49" s="225"/>
-      <c r="K49" s="225"/>
-      <c r="L49" s="225"/>
-      <c r="M49" s="226"/>
-      <c r="N49" s="217"/>
-      <c r="O49" s="218"/>
-      <c r="P49" s="219"/>
+      <c r="C49" s="196"/>
+      <c r="D49" s="196"/>
+      <c r="E49" s="196"/>
+      <c r="F49" s="196"/>
+      <c r="G49" s="196"/>
+      <c r="H49" s="197"/>
+      <c r="I49" s="198"/>
+      <c r="J49" s="198"/>
+      <c r="K49" s="198"/>
+      <c r="L49" s="198"/>
+      <c r="M49" s="199"/>
+      <c r="N49" s="200"/>
+      <c r="O49" s="201"/>
+      <c r="P49" s="202"/>
       <c r="Q49" s="42"/>
-      <c r="R49" s="220"/>
-      <c r="S49" s="220"/>
+      <c r="R49" s="203"/>
+      <c r="S49" s="203"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="42"/>
       <c r="B50" s="42"/>
-      <c r="C50" s="216"/>
-      <c r="D50" s="216"/>
-      <c r="E50" s="216"/>
-      <c r="F50" s="216"/>
-      <c r="G50" s="216"/>
-      <c r="H50" s="224"/>
-      <c r="I50" s="225"/>
-      <c r="J50" s="225"/>
-      <c r="K50" s="225"/>
-      <c r="L50" s="225"/>
-      <c r="M50" s="226"/>
-      <c r="N50" s="217"/>
-      <c r="O50" s="218"/>
-      <c r="P50" s="219"/>
+      <c r="C50" s="196"/>
+      <c r="D50" s="196"/>
+      <c r="E50" s="196"/>
+      <c r="F50" s="196"/>
+      <c r="G50" s="196"/>
+      <c r="H50" s="197"/>
+      <c r="I50" s="198"/>
+      <c r="J50" s="198"/>
+      <c r="K50" s="198"/>
+      <c r="L50" s="198"/>
+      <c r="M50" s="199"/>
+      <c r="N50" s="200"/>
+      <c r="O50" s="201"/>
+      <c r="P50" s="202"/>
       <c r="Q50" s="42"/>
-      <c r="R50" s="220"/>
-      <c r="S50" s="220"/>
+      <c r="R50" s="203"/>
+      <c r="S50" s="203"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="42"/>
       <c r="B51" s="42"/>
-      <c r="C51" s="216"/>
-      <c r="D51" s="216"/>
-      <c r="E51" s="216"/>
-      <c r="F51" s="216"/>
-      <c r="G51" s="216"/>
-      <c r="H51" s="224"/>
-      <c r="I51" s="225"/>
-      <c r="J51" s="225"/>
-      <c r="K51" s="225"/>
-      <c r="L51" s="225"/>
-      <c r="M51" s="226"/>
-      <c r="N51" s="217"/>
-      <c r="O51" s="218"/>
-      <c r="P51" s="219"/>
+      <c r="C51" s="196"/>
+      <c r="D51" s="196"/>
+      <c r="E51" s="196"/>
+      <c r="F51" s="196"/>
+      <c r="G51" s="196"/>
+      <c r="H51" s="197"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="K51" s="198"/>
+      <c r="L51" s="198"/>
+      <c r="M51" s="199"/>
+      <c r="N51" s="200"/>
+      <c r="O51" s="201"/>
+      <c r="P51" s="202"/>
       <c r="Q51" s="42"/>
-      <c r="R51" s="220"/>
-      <c r="S51" s="220"/>
+      <c r="R51" s="203"/>
+      <c r="S51" s="203"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="42"/>
       <c r="B52" s="42"/>
-      <c r="C52" s="216"/>
-      <c r="D52" s="216"/>
-      <c r="E52" s="216"/>
-      <c r="F52" s="216"/>
-      <c r="G52" s="216"/>
-      <c r="H52" s="224"/>
-      <c r="I52" s="225"/>
-      <c r="J52" s="225"/>
-      <c r="K52" s="225"/>
-      <c r="L52" s="225"/>
-      <c r="M52" s="226"/>
-      <c r="N52" s="217"/>
-      <c r="O52" s="218"/>
-      <c r="P52" s="219"/>
+      <c r="C52" s="196"/>
+      <c r="D52" s="196"/>
+      <c r="E52" s="196"/>
+      <c r="F52" s="196"/>
+      <c r="G52" s="196"/>
+      <c r="H52" s="197"/>
+      <c r="I52" s="198"/>
+      <c r="J52" s="198"/>
+      <c r="K52" s="198"/>
+      <c r="L52" s="198"/>
+      <c r="M52" s="199"/>
+      <c r="N52" s="200"/>
+      <c r="O52" s="201"/>
+      <c r="P52" s="202"/>
       <c r="Q52" s="42"/>
-      <c r="R52" s="220"/>
-      <c r="S52" s="220"/>
+      <c r="R52" s="203"/>
+      <c r="S52" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -15076,6 +15022,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
@@ -15209,7 +15343,9 @@
       <c r="D5" s="228"/>
       <c r="E5" s="228"/>
       <c r="F5" s="229"/>
-      <c r="G5" s="233"/>
+      <c r="G5" s="233" t="s">
+        <v>112</v>
+      </c>
       <c r="H5" s="234"/>
       <c r="I5" s="234"/>
       <c r="J5" s="234"/>
@@ -16701,5 +16837,6 @@
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>